--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SmartOrder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5B6142-97C9-4367-80E3-4A6F24A27671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9568EC3-4989-41A5-9F46-4106A8ADA892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="заказ-order" sheetId="6" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="логист.данные  logistic dimenst" sheetId="4" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'заказ-order'!$A$4:$U$392</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'заказ-order'!$A$1:$G$404</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'заказ-order'!$A$4:$U$393</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'заказ-order'!$A$1:$G$405</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="434">
   <si>
     <t>№ з/п</t>
   </si>
@@ -1336,6 +1336,9 @@
   </si>
   <si>
     <t>Персик / Peach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шампун для волос 830 мл / Shampoo for hair 830 ml </t>
   </si>
 </sst>
 </file>
@@ -3081,7 +3084,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:U405"/>
+  <dimension ref="A1:U406"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="10.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.44140625" style="9" customWidth="1"/>
@@ -7367,7 +7370,7 @@
       <c r="N147" s="101"/>
       <c r="O147" s="98"/>
     </row>
-    <row r="148" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>3</v>
       </c>
@@ -8588,7 +8591,7 @@
         <v>3305900009</v>
       </c>
     </row>
-    <row r="199" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>2</v>
       </c>
@@ -8725,7 +8728,7 @@
         <v>3305900009</v>
       </c>
     </row>
-    <row r="205" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>2</v>
       </c>
@@ -9427,17 +9430,17 @@
       </c>
       <c r="C233" s="113"/>
       <c r="D233" s="113">
-        <f>SUM(D234:D241)</f>
+        <f>SUM(D234:D242)</f>
         <v>0</v>
       </c>
       <c r="E233" s="113">
-        <f>SUM(E234:E241)</f>
+        <f>SUM(E234:E242)</f>
         <v>0</v>
       </c>
       <c r="F233" s="123"/>
       <c r="G233" s="108"/>
       <c r="H233" s="209">
-        <f>SUM(H234:H241)</f>
+        <f>SUM(H234:H242)</f>
         <v>0</v>
       </c>
       <c r="I233" s="150" t="s">
@@ -9466,7 +9469,7 @@
         <v>1.36</v>
       </c>
       <c r="H234" s="136">
-        <f t="shared" ref="H234:H241" si="6">G234*D234</f>
+        <f t="shared" ref="H234:H242" si="6">G234*D234</f>
         <v>0</v>
       </c>
       <c r="I234" s="144">
@@ -9478,100 +9481,95 @@
         <v>2</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>56</v>
+        <v>433</v>
       </c>
       <c r="C235" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D235" s="8">
-        <f t="shared" ref="D235:D241" si="7">E235*C235</f>
+        <f>E235*C235</f>
         <v>0</v>
       </c>
       <c r="E235" s="39"/>
       <c r="F235" s="208">
-        <v>4780023327013</v>
+        <v>4780023326993</v>
       </c>
       <c r="G235" s="112">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="H235" s="136">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I235" s="144">
-        <v>3305900009</v>
-      </c>
-    </row>
-    <row r="236" spans="1:13" s="197" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A236" s="194">
+        <v>1.61</v>
+      </c>
+      <c r="H235" s="136"/>
+      <c r="I235" s="144"/>
+    </row>
+    <row r="236" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A236" s="2">
         <v>3</v>
       </c>
-      <c r="B236" s="195" t="s">
-        <v>317</v>
+      <c r="B236" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C236" s="2">
         <v>18</v>
       </c>
       <c r="D236" s="8">
-        <f>E236*C236</f>
-        <v>0</v>
-      </c>
-      <c r="E236" s="200"/>
+        <f t="shared" ref="D236:D242" si="7">E236*C236</f>
+        <v>0</v>
+      </c>
+      <c r="E236" s="39"/>
       <c r="F236" s="208">
-        <v>4780023328850</v>
-      </c>
-      <c r="G236" s="196">
-        <v>0.77</v>
+        <v>4780023327013</v>
+      </c>
+      <c r="G236" s="112">
+        <v>1.1200000000000001</v>
       </c>
       <c r="H236" s="136">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I236" s="144">
-        <v>3401300000</v>
-      </c>
-      <c r="K236" s="198"/>
-      <c r="L236" s="198"/>
-      <c r="M236" s="199"/>
-    </row>
-    <row r="237" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>3305900009</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" s="197" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>4</v>
       </c>
-      <c r="B237" s="3" t="s">
-        <v>57</v>
+      <c r="B237" s="195" t="s">
+        <v>317</v>
       </c>
       <c r="C237" s="2">
         <v>18</v>
       </c>
       <c r="D237" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E237" s="39"/>
+        <f>E237*C237</f>
+        <v>0</v>
+      </c>
+      <c r="E237" s="200"/>
       <c r="F237" s="208">
-        <v>4780023327037</v>
-      </c>
-      <c r="G237" s="112">
-        <v>0.94</v>
+        <v>4780023328850</v>
+      </c>
+      <c r="G237" s="196">
+        <v>0.77</v>
       </c>
       <c r="H237" s="136">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I237" s="144">
-        <v>3304990000</v>
-      </c>
+        <v>3401300000</v>
+      </c>
+      <c r="K237" s="198"/>
+      <c r="L237" s="198"/>
+      <c r="M237" s="199"/>
     </row>
     <row r="238" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>5</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C238" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D238" s="8">
         <f t="shared" si="7"/>
@@ -9579,28 +9577,28 @@
       </c>
       <c r="E238" s="39"/>
       <c r="F238" s="208">
-        <v>4780023327020</v>
+        <v>4780023327037</v>
       </c>
       <c r="G238" s="112">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="H238" s="136">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I238" s="144">
-        <v>3307900008</v>
+        <v>3304990000</v>
       </c>
     </row>
     <row r="239" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A239" s="194">
+      <c r="A239" s="2">
         <v>6</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C239" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D239" s="8">
         <f t="shared" si="7"/>
@@ -9608,17 +9606,17 @@
       </c>
       <c r="E239" s="39"/>
       <c r="F239" s="208">
-        <v>4780023327051</v>
+        <v>4780023327020</v>
       </c>
       <c r="G239" s="112">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="H239" s="136">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I239" s="144">
-        <v>3304990000</v>
+        <v>3307900008</v>
       </c>
     </row>
     <row r="240" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -9626,7 +9624,7 @@
         <v>7</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C240" s="2">
         <v>36</v>
@@ -9637,10 +9635,10 @@
       </c>
       <c r="E240" s="39"/>
       <c r="F240" s="208">
-        <v>4780023327044</v>
+        <v>4780023327051</v>
       </c>
       <c r="G240" s="112">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="H240" s="136">
         <f t="shared" si="6"/>
@@ -9655,7 +9653,7 @@
         <v>8</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C241" s="2">
         <v>36</v>
@@ -9666,10 +9664,10 @@
       </c>
       <c r="E241" s="39"/>
       <c r="F241" s="208">
-        <v>4780023327068</v>
+        <v>4780023327044</v>
       </c>
       <c r="G241" s="112">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="H241" s="136">
         <f t="shared" si="6"/>
@@ -9678,85 +9676,85 @@
       <c r="I241" s="144">
         <v>3304990000</v>
       </c>
-      <c r="J241" s="210"/>
     </row>
     <row r="242" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A242" s="2"/>
-      <c r="B242" s="3"/>
-      <c r="C242" s="2"/>
-      <c r="D242" s="8"/>
-      <c r="E242" s="18"/>
-      <c r="F242" s="120"/>
-      <c r="G242" s="112"/>
-      <c r="H242" s="136"/>
-      <c r="I242" s="148" t="s">
+      <c r="A242" s="2">
+        <v>9</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C242" s="2">
+        <v>36</v>
+      </c>
+      <c r="D242" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E242" s="39"/>
+      <c r="F242" s="208">
+        <v>4780023327068</v>
+      </c>
+      <c r="G242" s="112">
+        <v>0.7</v>
+      </c>
+      <c r="H242" s="136">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I242" s="144">
+        <v>3304990000</v>
+      </c>
+      <c r="J242" s="210"/>
+    </row>
+    <row r="243" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A243" s="2"/>
+      <c r="B243" s="3"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="8"/>
+      <c r="E243" s="18"/>
+      <c r="F243" s="120"/>
+      <c r="G243" s="112"/>
+      <c r="H243" s="136"/>
+      <c r="I243" s="148" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="36" x14ac:dyDescent="0.35">
-      <c r="A243" s="105" t="s">
+    <row r="244" spans="1:10" ht="36" x14ac:dyDescent="0.35">
+      <c r="A244" s="105" t="s">
         <v>90</v>
       </c>
-      <c r="B243" s="134" t="s">
+      <c r="B244" s="134" t="s">
         <v>226</v>
       </c>
-      <c r="C243" s="6"/>
-      <c r="D243" s="6">
-        <f>SUM(D244:D247)</f>
-        <v>0</v>
-      </c>
-      <c r="E243" s="6">
-        <f>SUM(E244:E247)</f>
-        <v>0</v>
-      </c>
-      <c r="F243" s="123"/>
-      <c r="G243" s="108"/>
-      <c r="H243" s="136">
-        <f>SUM(H244:H247)</f>
-        <v>0</v>
-      </c>
-      <c r="I243" s="150" t="s">
+      <c r="C244" s="6"/>
+      <c r="D244" s="6">
+        <f>SUM(D245:D248)</f>
+        <v>0</v>
+      </c>
+      <c r="E244" s="6">
+        <f>SUM(E245:E248)</f>
+        <v>0</v>
+      </c>
+      <c r="F244" s="123"/>
+      <c r="G244" s="108"/>
+      <c r="H244" s="136">
+        <f>SUM(H245:H248)</f>
+        <v>0</v>
+      </c>
+      <c r="I244" s="150" t="s">
         <v>234</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A244" s="2">
-        <v>1</v>
-      </c>
-      <c r="B244" s="102" t="s">
-        <v>173</v>
-      </c>
-      <c r="C244" s="2">
-        <v>16</v>
-      </c>
-      <c r="D244" s="8">
-        <f>E244*C244</f>
-        <v>0</v>
-      </c>
-      <c r="E244" s="39"/>
-      <c r="F244" s="208">
-        <v>4780023326825</v>
-      </c>
-      <c r="G244" s="112">
-        <v>0.85</v>
-      </c>
-      <c r="H244" s="136">
-        <f>G244*D244</f>
-        <v>0</v>
-      </c>
-      <c r="I244" s="144">
-        <v>3305100000</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B245" s="102" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C245" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D245" s="8">
         <f>E245*C245</f>
@@ -9764,28 +9762,28 @@
       </c>
       <c r="E245" s="39"/>
       <c r="F245" s="208">
-        <v>4780023326856</v>
+        <v>4780023326825</v>
       </c>
       <c r="G245" s="112">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="H245" s="136">
         <f>G245*D245</f>
         <v>0</v>
       </c>
       <c r="I245" s="144">
-        <v>3305900009</v>
+        <v>3305100000</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B246" s="102" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C246" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D246" s="8">
         <f>E246*C246</f>
@@ -9793,28 +9791,28 @@
       </c>
       <c r="E246" s="39"/>
       <c r="F246" s="208">
-        <v>4780023326832</v>
+        <v>4780023326856</v>
       </c>
       <c r="G246" s="112">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H246" s="136">
         <f>G246*D246</f>
         <v>0</v>
       </c>
       <c r="I246" s="144">
-        <v>3401300000</v>
+        <v>3305900009</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B247" s="102" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C247" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D247" s="8">
         <f>E247*C247</f>
@@ -9822,128 +9820,133 @@
       </c>
       <c r="E247" s="39"/>
       <c r="F247" s="208">
-        <v>4780023326849</v>
+        <v>4780023326832</v>
       </c>
       <c r="G247" s="112">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="H247" s="136">
         <f>G247*D247</f>
         <v>0</v>
       </c>
       <c r="I247" s="144">
+        <v>3401300000</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A248" s="2">
+        <v>4</v>
+      </c>
+      <c r="B248" s="102" t="s">
+        <v>176</v>
+      </c>
+      <c r="C248" s="2">
+        <v>20</v>
+      </c>
+      <c r="D248" s="8">
+        <f>E248*C248</f>
+        <v>0</v>
+      </c>
+      <c r="E248" s="39"/>
+      <c r="F248" s="208">
+        <v>4780023326849</v>
+      </c>
+      <c r="G248" s="112">
+        <v>0.7</v>
+      </c>
+      <c r="H248" s="136">
+        <f>G248*D248</f>
+        <v>0</v>
+      </c>
+      <c r="I248" s="144">
         <v>3307100000</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A248" s="160"/>
-      <c r="B248" s="161"/>
-      <c r="C248" s="161"/>
-      <c r="D248" s="182"/>
-      <c r="E248" s="182"/>
-      <c r="F248" s="124"/>
-      <c r="G248" s="112"/>
-      <c r="H248" s="136"/>
-      <c r="I248" s="150" t="s">
+    <row r="249" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A249" s="160"/>
+      <c r="B249" s="161"/>
+      <c r="C249" s="161"/>
+      <c r="D249" s="182"/>
+      <c r="E249" s="182"/>
+      <c r="F249" s="124"/>
+      <c r="G249" s="112"/>
+      <c r="H249" s="136"/>
+      <c r="I249" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="32.4" x14ac:dyDescent="0.35">
-      <c r="A249" s="40"/>
-      <c r="B249" s="106" t="s">
+    <row r="250" spans="1:10" ht="32.4" x14ac:dyDescent="0.35">
+      <c r="A250" s="40"/>
+      <c r="B250" s="106" t="s">
         <v>231</v>
       </c>
-      <c r="C249" s="106">
+      <c r="C250" s="106">
         <v>24</v>
       </c>
-      <c r="D249" s="166">
-        <f>+C249*E249</f>
-        <v>0</v>
-      </c>
-      <c r="E249" s="183"/>
-      <c r="F249" s="121">
+      <c r="D250" s="166">
+        <f>+C250*E250</f>
+        <v>0</v>
+      </c>
+      <c r="E250" s="183"/>
+      <c r="F250" s="121">
         <v>4780023326771</v>
       </c>
-      <c r="G249" s="139">
+      <c r="G250" s="139">
         <v>2.5</v>
       </c>
-      <c r="H249" s="136">
-        <f>G249*D249</f>
-        <v>0</v>
-      </c>
-      <c r="I249" s="144">
+      <c r="H250" s="136">
+        <f>G250*D250</f>
+        <v>0</v>
+      </c>
+      <c r="I250" s="144">
         <v>3305900009</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A250" s="168"/>
-      <c r="B250" s="169"/>
-      <c r="C250" s="169"/>
-      <c r="D250" s="170"/>
-      <c r="E250" s="169"/>
-      <c r="F250" s="171"/>
-      <c r="G250" s="112"/>
-      <c r="H250" s="136"/>
-      <c r="I250" s="150" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" ht="32.4" x14ac:dyDescent="0.35">
-      <c r="A251" s="5"/>
-      <c r="B251" s="104" t="s">
-        <v>325</v>
-      </c>
-      <c r="C251" s="104"/>
-      <c r="D251" s="104">
-        <f>D252+D253+D254+D255</f>
-        <v>0</v>
-      </c>
-      <c r="E251" s="104">
-        <f>E252+E253+E254+E255</f>
-        <v>0</v>
-      </c>
-      <c r="F251" s="121"/>
-      <c r="G251" s="139">
-        <v>0.95</v>
-      </c>
-      <c r="H251" s="136">
-        <f>G251*D251</f>
-        <v>0</v>
-      </c>
+    <row r="251" spans="1:10" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A251" s="168"/>
+      <c r="B251" s="169"/>
+      <c r="C251" s="169"/>
+      <c r="D251" s="170"/>
+      <c r="E251" s="169"/>
+      <c r="F251" s="171"/>
+      <c r="G251" s="112"/>
+      <c r="H251" s="136"/>
       <c r="I251" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A252" s="2">
-        <v>1</v>
-      </c>
-      <c r="B252" s="201" t="s">
-        <v>318</v>
-      </c>
-      <c r="C252" s="2">
-        <v>12</v>
-      </c>
-      <c r="D252" s="202">
-        <f>+E252*C252</f>
-        <v>0</v>
-      </c>
-      <c r="E252" s="39"/>
-      <c r="F252" s="211">
-        <v>4780023329192</v>
-      </c>
-      <c r="G252" s="112"/>
-      <c r="H252" s="136"/>
-      <c r="I252" s="144">
-        <v>3305900009</v>
+    <row r="252" spans="1:10" ht="32.4" x14ac:dyDescent="0.35">
+      <c r="A252" s="5"/>
+      <c r="B252" s="104" t="s">
+        <v>325</v>
+      </c>
+      <c r="C252" s="104"/>
+      <c r="D252" s="104">
+        <f>D253+D254+D255+D256</f>
+        <v>0</v>
+      </c>
+      <c r="E252" s="104">
+        <f>E253+E254+E255+E256</f>
+        <v>0</v>
+      </c>
+      <c r="F252" s="121"/>
+      <c r="G252" s="139">
+        <v>0.95</v>
+      </c>
+      <c r="H252" s="136">
+        <f>G252*D252</f>
+        <v>0</v>
+      </c>
+      <c r="I252" s="150" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A253" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B253" s="201" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C253" s="2">
         <v>12</v>
@@ -9954,7 +9957,7 @@
       </c>
       <c r="E253" s="39"/>
       <c r="F253" s="211">
-        <v>4780023329161</v>
+        <v>4780023329192</v>
       </c>
       <c r="G253" s="112"/>
       <c r="H253" s="136"/>
@@ -9964,10 +9967,10 @@
     </row>
     <row r="254" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B254" s="201" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C254" s="2">
         <v>12</v>
@@ -9978,7 +9981,7 @@
       </c>
       <c r="E254" s="39"/>
       <c r="F254" s="211">
-        <v>4780023329178</v>
+        <v>4780023329161</v>
       </c>
       <c r="G254" s="112"/>
       <c r="H254" s="136"/>
@@ -9988,10 +9991,10 @@
     </row>
     <row r="255" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B255" s="201" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C255" s="2">
         <v>12</v>
@@ -10002,7 +10005,7 @@
       </c>
       <c r="E255" s="39"/>
       <c r="F255" s="211">
-        <v>4780023329185</v>
+        <v>4780023329178</v>
       </c>
       <c r="G255" s="112"/>
       <c r="H255" s="136"/>
@@ -10010,75 +10013,75 @@
         <v>3305900009</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A256" s="173"/>
-      <c r="B256" s="46"/>
-      <c r="C256" s="46"/>
-      <c r="D256" s="184"/>
-      <c r="E256" s="184"/>
-      <c r="F256" s="171"/>
+    <row r="256" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A256" s="2">
+        <v>4</v>
+      </c>
+      <c r="B256" s="201" t="s">
+        <v>321</v>
+      </c>
+      <c r="C256" s="2">
+        <v>12</v>
+      </c>
+      <c r="D256" s="202">
+        <f>+E256*C256</f>
+        <v>0</v>
+      </c>
+      <c r="E256" s="39"/>
+      <c r="F256" s="211">
+        <v>4780023329185</v>
+      </c>
       <c r="G256" s="112"/>
       <c r="H256" s="136"/>
-      <c r="I256" s="150" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="257" spans="1:15" ht="32.4" x14ac:dyDescent="0.35">
-      <c r="A257" s="5"/>
-      <c r="B257" s="104" t="s">
-        <v>326</v>
-      </c>
-      <c r="C257" s="104"/>
-      <c r="D257" s="104">
-        <f>D258+D259</f>
-        <v>0</v>
-      </c>
-      <c r="E257" s="104">
-        <f>E258+E259</f>
-        <v>0</v>
-      </c>
-      <c r="F257" s="121"/>
-      <c r="G257" s="139">
-        <v>0.71</v>
-      </c>
-      <c r="H257" s="136">
-        <f>G257*D257</f>
-        <v>0</v>
-      </c>
+      <c r="I256" s="144">
+        <v>3305900009</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A257" s="173"/>
+      <c r="B257" s="46"/>
+      <c r="C257" s="46"/>
+      <c r="D257" s="184"/>
+      <c r="E257" s="184"/>
+      <c r="F257" s="171"/>
+      <c r="G257" s="112"/>
+      <c r="H257" s="136"/>
       <c r="I257" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="258" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A258" s="2">
-        <v>1</v>
-      </c>
-      <c r="B258" s="201" t="s">
-        <v>323</v>
-      </c>
-      <c r="C258" s="2">
-        <v>18</v>
-      </c>
-      <c r="D258" s="202">
-        <f>+E258*C258</f>
-        <v>0</v>
-      </c>
-      <c r="E258" s="39"/>
-      <c r="F258" s="211">
-        <v>4780023329239</v>
-      </c>
-      <c r="G258" s="112"/>
-      <c r="H258" s="136"/>
-      <c r="I258" s="144">
-        <v>3305900009</v>
+    <row r="258" spans="1:15" ht="32.4" x14ac:dyDescent="0.35">
+      <c r="A258" s="5"/>
+      <c r="B258" s="104" t="s">
+        <v>326</v>
+      </c>
+      <c r="C258" s="104"/>
+      <c r="D258" s="104">
+        <f>D259+D260</f>
+        <v>0</v>
+      </c>
+      <c r="E258" s="104">
+        <f>E259+E260</f>
+        <v>0</v>
+      </c>
+      <c r="F258" s="121"/>
+      <c r="G258" s="139">
+        <v>0.71</v>
+      </c>
+      <c r="H258" s="136">
+        <f>G258*D258</f>
+        <v>0</v>
+      </c>
+      <c r="I258" s="150" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="259" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B259" s="201" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C259" s="2">
         <v>18</v>
@@ -10089,7 +10092,7 @@
       </c>
       <c r="E259" s="39"/>
       <c r="F259" s="211">
-        <v>4780023329253</v>
+        <v>4780023329239</v>
       </c>
       <c r="G259" s="112"/>
       <c r="H259" s="136"/>
@@ -10097,77 +10100,77 @@
         <v>3305900009</v>
       </c>
     </row>
-    <row r="260" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A260" s="173"/>
-      <c r="B260" s="46"/>
-      <c r="C260" s="46"/>
-      <c r="D260" s="184"/>
-      <c r="E260" s="184"/>
-      <c r="F260" s="171"/>
+    <row r="260" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A260" s="2">
+        <v>2</v>
+      </c>
+      <c r="B260" s="201" t="s">
+        <v>322</v>
+      </c>
+      <c r="C260" s="2">
+        <v>18</v>
+      </c>
+      <c r="D260" s="202">
+        <f>+E260*C260</f>
+        <v>0</v>
+      </c>
+      <c r="E260" s="39"/>
+      <c r="F260" s="211">
+        <v>4780023329253</v>
+      </c>
       <c r="G260" s="112"/>
       <c r="H260" s="136"/>
-      <c r="I260" s="150" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="261" spans="1:15" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A261" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B261" s="191" t="s">
-        <v>240</v>
-      </c>
-      <c r="C261" s="113"/>
-      <c r="D261" s="113">
-        <f>SUM(D262:D266)</f>
-        <v>0</v>
-      </c>
-      <c r="E261" s="113">
-        <f>SUM(E262:E266)</f>
-        <v>0</v>
-      </c>
-      <c r="F261" s="123"/>
-      <c r="G261" s="139">
-        <v>1.6</v>
-      </c>
-      <c r="H261" s="137">
-        <f>G261*D261</f>
-        <v>0</v>
-      </c>
+      <c r="I260" s="144">
+        <v>3305900009</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A261" s="173"/>
+      <c r="B261" s="46"/>
+      <c r="C261" s="46"/>
+      <c r="D261" s="184"/>
+      <c r="E261" s="184"/>
+      <c r="F261" s="171"/>
+      <c r="G261" s="112"/>
+      <c r="H261" s="136"/>
       <c r="I261" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="262" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A262" s="2">
-        <v>1</v>
-      </c>
-      <c r="B262" s="102" t="s">
-        <v>242</v>
-      </c>
-      <c r="C262" s="2">
-        <v>15</v>
-      </c>
-      <c r="D262" s="8">
-        <f>E262*C262</f>
-        <v>0</v>
-      </c>
-      <c r="E262" s="39"/>
-      <c r="F262" s="208">
-        <v>4780023327709</v>
-      </c>
-      <c r="G262" s="112"/>
-      <c r="H262" s="136"/>
-      <c r="I262" s="144">
-        <v>3305900009</v>
+    <row r="262" spans="1:15" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A262" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B262" s="191" t="s">
+        <v>240</v>
+      </c>
+      <c r="C262" s="113"/>
+      <c r="D262" s="113">
+        <f>SUM(D263:D267)</f>
+        <v>0</v>
+      </c>
+      <c r="E262" s="113">
+        <f>SUM(E263:E267)</f>
+        <v>0</v>
+      </c>
+      <c r="F262" s="123"/>
+      <c r="G262" s="139">
+        <v>1.6</v>
+      </c>
+      <c r="H262" s="137">
+        <f>G262*D262</f>
+        <v>0</v>
+      </c>
+      <c r="I262" s="150" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="263" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A263" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B263" s="102" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C263" s="2">
         <v>15</v>
@@ -10178,7 +10181,7 @@
       </c>
       <c r="E263" s="39"/>
       <c r="F263" s="208">
-        <v>4780023327716</v>
+        <v>4780023327709</v>
       </c>
       <c r="G263" s="112"/>
       <c r="H263" s="136"/>
@@ -10188,10 +10191,10 @@
     </row>
     <row r="264" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A264" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B264" s="102" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C264" s="2">
         <v>15</v>
@@ -10202,7 +10205,7 @@
       </c>
       <c r="E264" s="39"/>
       <c r="F264" s="208">
-        <v>4780023327723</v>
+        <v>4780023327716</v>
       </c>
       <c r="G264" s="112"/>
       <c r="H264" s="136"/>
@@ -10212,10 +10215,10 @@
     </row>
     <row r="265" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A265" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B265" s="102" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C265" s="2">
         <v>15</v>
@@ -10226,7 +10229,7 @@
       </c>
       <c r="E265" s="39"/>
       <c r="F265" s="208">
-        <v>4780023327730</v>
+        <v>4780023327723</v>
       </c>
       <c r="G265" s="112"/>
       <c r="H265" s="136"/>
@@ -10236,10 +10239,10 @@
     </row>
     <row r="266" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A266" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B266" s="102" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C266" s="2">
         <v>15</v>
@@ -10250,7 +10253,7 @@
       </c>
       <c r="E266" s="39"/>
       <c r="F266" s="208">
-        <v>4780023327747</v>
+        <v>4780023327730</v>
       </c>
       <c r="G266" s="112"/>
       <c r="H266" s="136"/>
@@ -10259,74 +10262,68 @@
       </c>
     </row>
     <row r="267" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A267" s="2"/>
-      <c r="B267" s="102"/>
-      <c r="C267" s="62"/>
-      <c r="D267" s="8"/>
-      <c r="E267" s="18"/>
-      <c r="F267" s="120"/>
+      <c r="A267" s="2">
+        <v>5</v>
+      </c>
+      <c r="B267" s="102" t="s">
+        <v>245</v>
+      </c>
+      <c r="C267" s="2">
+        <v>15</v>
+      </c>
+      <c r="D267" s="8">
+        <f>E267*C267</f>
+        <v>0</v>
+      </c>
+      <c r="E267" s="39"/>
+      <c r="F267" s="208">
+        <v>4780023327747</v>
+      </c>
       <c r="G267" s="112"/>
       <c r="H267" s="136"/>
-      <c r="I267" s="149" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="268" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A268" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B268" s="104" t="s">
-        <v>246</v>
-      </c>
-      <c r="C268" s="113"/>
-      <c r="D268" s="113">
-        <f>+D269+D270+D271</f>
-        <v>0</v>
-      </c>
-      <c r="E268" s="113">
-        <f>+E269+E270+E271</f>
-        <v>0</v>
-      </c>
-      <c r="F268" s="123"/>
-      <c r="G268" s="139">
-        <v>0.83</v>
-      </c>
-      <c r="H268" s="137">
-        <f>G268*D268</f>
-        <v>0</v>
-      </c>
+      <c r="I267" s="144">
+        <v>3305900009</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A268" s="2"/>
+      <c r="B268" s="102"/>
+      <c r="C268" s="62"/>
+      <c r="D268" s="8"/>
+      <c r="E268" s="18"/>
+      <c r="F268" s="120"/>
+      <c r="G268" s="112"/>
+      <c r="H268" s="136"/>
       <c r="I268" s="149" t="s">
         <v>234</v>
       </c>
-      <c r="J268" s="98"/>
-      <c r="K268" s="98"/>
-      <c r="L268" s="100"/>
-      <c r="M268" s="100"/>
-      <c r="N268" s="101"/>
-      <c r="O268" s="98"/>
-    </row>
-    <row r="269" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A269" s="2">
-        <v>1</v>
-      </c>
-      <c r="B269" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C269" s="2">
-        <v>30</v>
-      </c>
-      <c r="D269" s="8">
-        <f>E269*C269</f>
-        <v>0</v>
-      </c>
-      <c r="E269" s="39"/>
-      <c r="F269" s="208">
-        <v>4780023327808</v>
-      </c>
-      <c r="G269" s="112"/>
-      <c r="H269" s="137"/>
-      <c r="I269" s="144">
-        <v>3304990000</v>
+    </row>
+    <row r="269" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A269" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B269" s="104" t="s">
+        <v>246</v>
+      </c>
+      <c r="C269" s="113"/>
+      <c r="D269" s="113">
+        <f>+D270+D271+D272</f>
+        <v>0</v>
+      </c>
+      <c r="E269" s="113">
+        <f>+E270+E271+E272</f>
+        <v>0</v>
+      </c>
+      <c r="F269" s="123"/>
+      <c r="G269" s="139">
+        <v>0.83</v>
+      </c>
+      <c r="H269" s="137">
+        <f>G269*D269</f>
+        <v>0</v>
+      </c>
+      <c r="I269" s="149" t="s">
+        <v>234</v>
       </c>
       <c r="J269" s="98"/>
       <c r="K269" s="98"/>
@@ -10337,10 +10334,10 @@
     </row>
     <row r="270" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A270" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C270" s="2">
         <v>30</v>
@@ -10351,7 +10348,7 @@
       </c>
       <c r="E270" s="39"/>
       <c r="F270" s="208">
-        <v>4780023327815</v>
+        <v>4780023327808</v>
       </c>
       <c r="G270" s="112"/>
       <c r="H270" s="137"/>
@@ -10367,10 +10364,10 @@
     </row>
     <row r="271" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A271" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C271" s="2">
         <v>30</v>
@@ -10381,7 +10378,7 @@
       </c>
       <c r="E271" s="39"/>
       <c r="F271" s="208">
-        <v>4780023327822</v>
+        <v>4780023327815</v>
       </c>
       <c r="G271" s="112"/>
       <c r="H271" s="137"/>
@@ -10396,16 +10393,27 @@
       <c r="O271" s="98"/>
     </row>
     <row r="272" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A272" s="2"/>
-      <c r="B272" s="3"/>
-      <c r="C272" s="2"/>
-      <c r="D272" s="8"/>
-      <c r="E272" s="193"/>
-      <c r="F272" s="120"/>
+      <c r="A272" s="2">
+        <v>3</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C272" s="2">
+        <v>30</v>
+      </c>
+      <c r="D272" s="8">
+        <f>E272*C272</f>
+        <v>0</v>
+      </c>
+      <c r="E272" s="39"/>
+      <c r="F272" s="208">
+        <v>4780023327822</v>
+      </c>
       <c r="G272" s="112"/>
       <c r="H272" s="137"/>
-      <c r="I272" s="149" t="s">
-        <v>234</v>
+      <c r="I272" s="144">
+        <v>3304990000</v>
       </c>
       <c r="J272" s="98"/>
       <c r="K272" s="98"/>
@@ -10414,70 +10422,60 @@
       <c r="N272" s="101"/>
       <c r="O272" s="98"/>
     </row>
-    <row r="273" spans="1:9" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A273" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B273" s="191" t="s">
-        <v>251</v>
-      </c>
-      <c r="C273" s="113"/>
-      <c r="D273" s="113">
-        <f>SUM(D274:D278)</f>
-        <v>0</v>
-      </c>
-      <c r="E273" s="113">
-        <f>SUM(E274:E278)</f>
-        <v>0</v>
-      </c>
-      <c r="F273" s="123"/>
-      <c r="G273" s="139"/>
-      <c r="H273" s="136">
-        <f>SUM(H274:H278)</f>
-        <v>0</v>
-      </c>
+    <row r="273" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A273" s="2"/>
+      <c r="B273" s="3"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="8"/>
+      <c r="E273" s="193"/>
+      <c r="F273" s="120"/>
+      <c r="G273" s="112"/>
+      <c r="H273" s="137"/>
       <c r="I273" s="149" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="274" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A274" s="2">
+      <c r="J273" s="98"/>
+      <c r="K273" s="98"/>
+      <c r="L273" s="100"/>
+      <c r="M273" s="100"/>
+      <c r="N273" s="101"/>
+      <c r="O273" s="98"/>
+    </row>
+    <row r="274" spans="1:15" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A274" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B274" s="191" t="s">
+        <v>251</v>
+      </c>
+      <c r="C274" s="113"/>
+      <c r="D274" s="113">
+        <f>SUM(D275:D279)</f>
+        <v>0</v>
+      </c>
+      <c r="E274" s="113">
+        <f>SUM(E275:E279)</f>
+        <v>0</v>
+      </c>
+      <c r="F274" s="123"/>
+      <c r="G274" s="139"/>
+      <c r="H274" s="136">
+        <f>SUM(H275:H279)</f>
+        <v>0</v>
+      </c>
+      <c r="I274" s="149" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A275" s="2">
         <v>1</v>
       </c>
-      <c r="B274" s="102" t="s">
+      <c r="B275" s="102" t="s">
         <v>252</v>
       </c>
-      <c r="C274" s="2">
+      <c r="C275" s="2">
         <v>18</v>
-      </c>
-      <c r="D274" s="8">
-        <f>E274*C274</f>
-        <v>0</v>
-      </c>
-      <c r="E274" s="39"/>
-      <c r="F274" s="208">
-        <v>4780023327617</v>
-      </c>
-      <c r="G274" s="112">
-        <v>0.81</v>
-      </c>
-      <c r="H274" s="136">
-        <f t="shared" ref="H274:H278" si="8">G274*D274</f>
-        <v>0</v>
-      </c>
-      <c r="I274" s="144">
-        <v>3305100000</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A275" s="2">
-        <v>2</v>
-      </c>
-      <c r="B275" s="102" t="s">
-        <v>253</v>
-      </c>
-      <c r="C275" s="2">
-        <v>20</v>
       </c>
       <c r="D275" s="8">
         <f>E275*C275</f>
@@ -10485,28 +10483,28 @@
       </c>
       <c r="E275" s="39"/>
       <c r="F275" s="208">
-        <v>4780023327631</v>
+        <v>4780023327617</v>
       </c>
       <c r="G275" s="112">
-        <v>1.58</v>
+        <v>0.81</v>
       </c>
       <c r="H275" s="136">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H275:H279" si="8">G275*D275</f>
         <v>0</v>
       </c>
       <c r="I275" s="144">
-        <v>3304990000</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+        <v>3305100000</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B276" s="102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C276" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D276" s="8">
         <f>E276*C276</f>
@@ -10514,10 +10512,10 @@
       </c>
       <c r="E276" s="39"/>
       <c r="F276" s="208">
-        <v>4780023327655</v>
+        <v>4780023327631</v>
       </c>
       <c r="G276" s="112">
-        <v>0.45</v>
+        <v>1.58</v>
       </c>
       <c r="H276" s="136">
         <f t="shared" si="8"/>
@@ -10527,15 +10525,15 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B277" s="102" t="s">
-        <v>371</v>
+        <v>254</v>
       </c>
       <c r="C277" s="2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D277" s="8">
         <f>E277*C277</f>
@@ -10543,10 +10541,10 @@
       </c>
       <c r="E277" s="39"/>
       <c r="F277" s="208">
-        <v>4780023327624</v>
+        <v>4780023327655</v>
       </c>
       <c r="G277" s="112">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="H277" s="136">
         <f t="shared" si="8"/>
@@ -10556,15 +10554,15 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B278" s="102" t="s">
-        <v>255</v>
+        <v>371</v>
       </c>
       <c r="C278" s="2">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D278" s="8">
         <f>E278*C278</f>
@@ -10572,101 +10570,106 @@
       </c>
       <c r="E278" s="39"/>
       <c r="F278" s="208">
-        <v>4780023327648</v>
+        <v>4780023327624</v>
       </c>
       <c r="G278" s="112">
-        <v>0.28999999999999998</v>
+        <v>0.66</v>
       </c>
       <c r="H278" s="136">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I278" s="144">
+        <v>3304990000</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A279" s="2">
+        <v>5</v>
+      </c>
+      <c r="B279" s="102" t="s">
+        <v>255</v>
+      </c>
+      <c r="C279" s="2">
+        <v>48</v>
+      </c>
+      <c r="D279" s="8">
+        <f>E279*C279</f>
+        <v>0</v>
+      </c>
+      <c r="E279" s="39"/>
+      <c r="F279" s="208">
+        <v>4780023327648</v>
+      </c>
+      <c r="G279" s="112">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H279" s="136">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I279" s="144">
         <v>3401110001</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A279" s="2"/>
-      <c r="B279" s="102"/>
-      <c r="C279" s="2"/>
-      <c r="D279" s="8"/>
-      <c r="E279" s="18"/>
-      <c r="F279" s="120"/>
-      <c r="G279" s="112"/>
-      <c r="H279" s="136"/>
-      <c r="I279" s="150" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9" ht="36" x14ac:dyDescent="0.3">
-      <c r="A280" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B280" s="134" t="s">
-        <v>294</v>
-      </c>
-      <c r="C280" s="113"/>
-      <c r="D280" s="113">
-        <f>SUM(D281:D292)</f>
-        <v>0</v>
-      </c>
-      <c r="E280" s="113">
-        <f>SUM(E281:E292)</f>
-        <v>0</v>
-      </c>
-      <c r="F280" s="123"/>
-      <c r="G280" s="108">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="H280" s="136">
-        <f>G280*D280</f>
-        <v>0</v>
-      </c>
+    <row r="280" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A280" s="2"/>
+      <c r="B280" s="102"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="8"/>
+      <c r="E280" s="18"/>
+      <c r="F280" s="120"/>
+      <c r="G280" s="112"/>
+      <c r="H280" s="136"/>
       <c r="I280" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A281" s="2">
+    <row r="281" spans="1:15" ht="36" x14ac:dyDescent="0.3">
+      <c r="A281" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B281" s="134" t="s">
+        <v>294</v>
+      </c>
+      <c r="C281" s="113"/>
+      <c r="D281" s="113">
+        <f>SUM(D282:D293)</f>
+        <v>0</v>
+      </c>
+      <c r="E281" s="113">
+        <f>SUM(E282:E293)</f>
+        <v>0</v>
+      </c>
+      <c r="F281" s="123"/>
+      <c r="G281" s="108">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H281" s="136">
+        <f>G281*D281</f>
+        <v>0</v>
+      </c>
+      <c r="I281" s="150" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A282" s="2">
         <v>1</v>
       </c>
-      <c r="B281" s="3" t="s">
+      <c r="B282" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C281" s="2">
+      <c r="C282" s="2">
         <v>15</v>
       </c>
-      <c r="D281" s="54">
-        <f t="shared" ref="D281:D289" si="9">E281*C281</f>
-        <v>0</v>
-      </c>
-      <c r="E281" s="44"/>
-      <c r="F281" s="205">
-        <v>4780023328980</v>
-      </c>
-      <c r="G281" s="110"/>
-      <c r="H281" s="136"/>
-      <c r="I281" s="144">
-        <v>3304990000</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A282" s="17">
-        <v>2</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C282" s="17">
-        <v>15</v>
-      </c>
       <c r="D282" s="54">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="D282:D290" si="9">E282*C282</f>
         <v>0</v>
       </c>
       <c r="E282" s="44"/>
       <c r="F282" s="205">
-        <v>4780023329000</v>
+        <v>4780023328980</v>
       </c>
       <c r="G282" s="110"/>
       <c r="H282" s="136"/>
@@ -10674,14 +10677,14 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A283" s="2">
-        <v>3</v>
+    <row r="283" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A283" s="17">
+        <v>2</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C283" s="2">
+        <v>296</v>
+      </c>
+      <c r="C283" s="17">
         <v>15</v>
       </c>
       <c r="D283" s="54">
@@ -10690,7 +10693,7 @@
       </c>
       <c r="E283" s="44"/>
       <c r="F283" s="205">
-        <v>4780023328997</v>
+        <v>4780023329000</v>
       </c>
       <c r="G283" s="110"/>
       <c r="H283" s="136"/>
@@ -10698,12 +10701,12 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A284" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C284" s="2">
         <v>15</v>
@@ -10714,7 +10717,7 @@
       </c>
       <c r="E284" s="44"/>
       <c r="F284" s="205">
-        <v>4780023329017</v>
+        <v>4780023328997</v>
       </c>
       <c r="G284" s="110"/>
       <c r="H284" s="136"/>
@@ -10722,14 +10725,14 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A285" s="17">
-        <v>5</v>
+    <row r="285" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A285" s="2">
+        <v>4</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C285" s="17">
+        <v>298</v>
+      </c>
+      <c r="C285" s="2">
         <v>15</v>
       </c>
       <c r="D285" s="54">
@@ -10738,7 +10741,7 @@
       </c>
       <c r="E285" s="44"/>
       <c r="F285" s="205">
-        <v>4780023328928</v>
+        <v>4780023329017</v>
       </c>
       <c r="G285" s="110"/>
       <c r="H285" s="136"/>
@@ -10746,14 +10749,14 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A286" s="2">
-        <v>6</v>
+    <row r="286" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A286" s="17">
+        <v>5</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C286" s="2">
+        <v>299</v>
+      </c>
+      <c r="C286" s="17">
         <v>15</v>
       </c>
       <c r="D286" s="54">
@@ -10762,7 +10765,7 @@
       </c>
       <c r="E286" s="44"/>
       <c r="F286" s="205">
-        <v>4780023328935</v>
+        <v>4780023328928</v>
       </c>
       <c r="G286" s="110"/>
       <c r="H286" s="136"/>
@@ -10770,12 +10773,12 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A287" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C287" s="2">
         <v>15</v>
@@ -10786,7 +10789,7 @@
       </c>
       <c r="E287" s="44"/>
       <c r="F287" s="205">
-        <v>4780023328942</v>
+        <v>4780023328935</v>
       </c>
       <c r="G287" s="110"/>
       <c r="H287" s="136"/>
@@ -10794,14 +10797,14 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A288" s="17">
-        <v>8</v>
+    <row r="288" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A288" s="2">
+        <v>7</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C288" s="17">
+        <v>301</v>
+      </c>
+      <c r="C288" s="2">
         <v>15</v>
       </c>
       <c r="D288" s="54">
@@ -10810,7 +10813,7 @@
       </c>
       <c r="E288" s="44"/>
       <c r="F288" s="205">
-        <v>4780023328959</v>
+        <v>4780023328942</v>
       </c>
       <c r="G288" s="110"/>
       <c r="H288" s="136"/>
@@ -10819,13 +10822,13 @@
       </c>
     </row>
     <row r="289" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A289" s="2">
-        <v>9</v>
+      <c r="A289" s="17">
+        <v>8</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C289" s="2">
+        <v>302</v>
+      </c>
+      <c r="C289" s="17">
         <v>15</v>
       </c>
       <c r="D289" s="54">
@@ -10834,7 +10837,7 @@
       </c>
       <c r="E289" s="44"/>
       <c r="F289" s="205">
-        <v>4780023328973</v>
+        <v>4780023328959</v>
       </c>
       <c r="G289" s="110"/>
       <c r="H289" s="136"/>
@@ -10844,21 +10847,21 @@
     </row>
     <row r="290" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A290" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C290" s="2">
         <v>15</v>
       </c>
       <c r="D290" s="54">
-        <f>E290*C290</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E290" s="44"/>
       <c r="F290" s="205">
-        <v>4780023329154</v>
+        <v>4780023328973</v>
       </c>
       <c r="G290" s="110"/>
       <c r="H290" s="136"/>
@@ -10867,22 +10870,22 @@
       </c>
     </row>
     <row r="291" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A291" s="17">
-        <v>11</v>
+      <c r="A291" s="2">
+        <v>10</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C291" s="17">
+        <v>304</v>
+      </c>
+      <c r="C291" s="2">
         <v>15</v>
       </c>
       <c r="D291" s="54">
-        <f t="shared" ref="D291:D292" si="10">E291*C291</f>
+        <f>E291*C291</f>
         <v>0</v>
       </c>
       <c r="E291" s="44"/>
       <c r="F291" s="205">
-        <v>4780023329147</v>
+        <v>4780023329154</v>
       </c>
       <c r="G291" s="110"/>
       <c r="H291" s="136"/>
@@ -10891,22 +10894,22 @@
       </c>
     </row>
     <row r="292" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A292" s="2">
-        <v>12</v>
+      <c r="A292" s="17">
+        <v>11</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C292" s="2">
+        <v>305</v>
+      </c>
+      <c r="C292" s="17">
         <v>15</v>
       </c>
       <c r="D292" s="54">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="D292:D293" si="10">E292*C292</f>
         <v>0</v>
       </c>
       <c r="E292" s="44"/>
       <c r="F292" s="205">
-        <v>4780023328966</v>
+        <v>4780023329147</v>
       </c>
       <c r="G292" s="110"/>
       <c r="H292" s="136"/>
@@ -10915,61 +10918,60 @@
       </c>
     </row>
     <row r="293" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A293" s="2"/>
-      <c r="B293" s="3"/>
-      <c r="C293" s="2"/>
-      <c r="D293" s="54"/>
-      <c r="E293" s="162"/>
-      <c r="F293" s="122"/>
+      <c r="A293" s="2">
+        <v>12</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C293" s="2">
+        <v>15</v>
+      </c>
+      <c r="D293" s="54">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E293" s="44"/>
+      <c r="F293" s="205">
+        <v>4780023328966</v>
+      </c>
       <c r="G293" s="110"/>
       <c r="H293" s="136"/>
-      <c r="I293" s="150" t="s">
+      <c r="I293" s="144">
+        <v>3304990000</v>
+      </c>
+    </row>
+    <row r="294" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A294" s="2"/>
+      <c r="B294" s="3"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="54"/>
+      <c r="E294" s="162"/>
+      <c r="F294" s="122"/>
+      <c r="G294" s="110"/>
+      <c r="H294" s="136"/>
+      <c r="I294" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="294" spans="1:15" ht="32.4" x14ac:dyDescent="0.35">
-      <c r="A294" s="40"/>
-      <c r="B294" s="106" t="s">
+    <row r="295" spans="1:15" ht="32.4" x14ac:dyDescent="0.35">
+      <c r="A295" s="40"/>
+      <c r="B295" s="106" t="s">
         <v>402</v>
       </c>
-      <c r="C294" s="104"/>
-      <c r="D294" s="113">
-        <f>+E294*C294</f>
-        <v>0</v>
-      </c>
-      <c r="E294" s="113">
-        <f>SUM(E295:E297)</f>
-        <v>0</v>
-      </c>
-      <c r="F294" s="121"/>
-      <c r="G294" s="139">
+      <c r="C295" s="104"/>
+      <c r="D295" s="113">
+        <f>+E295*C295</f>
+        <v>0</v>
+      </c>
+      <c r="E295" s="113">
+        <f>SUM(E296:E298)</f>
+        <v>0</v>
+      </c>
+      <c r="F295" s="121"/>
+      <c r="G295" s="139">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H294" s="136">
-        <f>G294*D294</f>
-        <v>0</v>
-      </c>
-      <c r="I294" s="144">
-        <v>3307100000</v>
-      </c>
-    </row>
-    <row r="295" spans="1:15" ht="48.6" x14ac:dyDescent="0.35">
-      <c r="A295" s="168"/>
-      <c r="B295" s="169" t="s">
-        <v>403</v>
-      </c>
-      <c r="C295" s="173">
-        <v>24</v>
-      </c>
-      <c r="D295" s="222">
-        <f>+E295*C295</f>
-        <v>0</v>
-      </c>
-      <c r="E295" s="56"/>
-      <c r="F295" s="205">
-        <v>4780023325699</v>
-      </c>
-      <c r="G295" s="112"/>
       <c r="H295" s="136">
         <f>G295*D295</f>
         <v>0</v>
@@ -10981,7 +10983,7 @@
     <row r="296" spans="1:15" ht="48.6" x14ac:dyDescent="0.35">
       <c r="A296" s="168"/>
       <c r="B296" s="169" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C296" s="173">
         <v>24</v>
@@ -10992,7 +10994,7 @@
       </c>
       <c r="E296" s="56"/>
       <c r="F296" s="205">
-        <v>4780141190957</v>
+        <v>4780023325699</v>
       </c>
       <c r="G296" s="112"/>
       <c r="H296" s="136">
@@ -11006,7 +11008,7 @@
     <row r="297" spans="1:15" ht="48.6" x14ac:dyDescent="0.35">
       <c r="A297" s="168"/>
       <c r="B297" s="169" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C297" s="173">
         <v>24</v>
@@ -11017,7 +11019,7 @@
       </c>
       <c r="E297" s="56"/>
       <c r="F297" s="205">
-        <v>4780141190940</v>
+        <v>4780141190957</v>
       </c>
       <c r="G297" s="112"/>
       <c r="H297" s="136">
@@ -11028,60 +11030,60 @@
         <v>3307100000</v>
       </c>
     </row>
-    <row r="298" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:15" ht="48.6" x14ac:dyDescent="0.35">
       <c r="A298" s="168"/>
-      <c r="B298" s="169"/>
-      <c r="C298" s="173"/>
-      <c r="D298" s="222"/>
-      <c r="E298" s="185"/>
-      <c r="F298" s="171"/>
+      <c r="B298" s="169" t="s">
+        <v>405</v>
+      </c>
+      <c r="C298" s="173">
+        <v>24</v>
+      </c>
+      <c r="D298" s="222">
+        <f>+E298*C298</f>
+        <v>0</v>
+      </c>
+      <c r="E298" s="56"/>
+      <c r="F298" s="205">
+        <v>4780141190940</v>
+      </c>
       <c r="G298" s="112"/>
-      <c r="H298" s="136"/>
-      <c r="I298" s="144"/>
-    </row>
-    <row r="299" spans="1:15" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A299" s="176"/>
-      <c r="B299" s="106" t="s">
+      <c r="H298" s="136">
+        <f>G298*D298</f>
+        <v>0</v>
+      </c>
+      <c r="I298" s="144">
+        <v>3307100000</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A299" s="168"/>
+      <c r="B299" s="169"/>
+      <c r="C299" s="173"/>
+      <c r="D299" s="222"/>
+      <c r="E299" s="185"/>
+      <c r="F299" s="171"/>
+      <c r="G299" s="112"/>
+      <c r="H299" s="136"/>
+      <c r="I299" s="144"/>
+    </row>
+    <row r="300" spans="1:15" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A300" s="176"/>
+      <c r="B300" s="106" t="s">
         <v>406</v>
       </c>
-      <c r="C299" s="104"/>
-      <c r="D299" s="113">
-        <f>+E299*C299</f>
-        <v>0</v>
-      </c>
-      <c r="E299" s="113">
-        <f>SUM(E300:E302)</f>
-        <v>0</v>
-      </c>
-      <c r="F299" s="121"/>
-      <c r="G299" s="139">
+      <c r="C300" s="104"/>
+      <c r="D300" s="113">
+        <f>+E300*C300</f>
+        <v>0</v>
+      </c>
+      <c r="E300" s="113">
+        <f>SUM(E301:E303)</f>
+        <v>0</v>
+      </c>
+      <c r="F300" s="121"/>
+      <c r="G300" s="139">
         <v>0.37</v>
       </c>
-      <c r="H299" s="136">
-        <f>G299*D299</f>
-        <v>0</v>
-      </c>
-      <c r="I299" s="144">
-        <v>3307100000</v>
-      </c>
-    </row>
-    <row r="300" spans="1:15" ht="48.6" x14ac:dyDescent="0.35">
-      <c r="A300" s="223"/>
-      <c r="B300" s="169" t="s">
-        <v>407</v>
-      </c>
-      <c r="C300" s="173">
-        <v>24</v>
-      </c>
-      <c r="D300" s="222">
-        <f>+E300*C300</f>
-        <v>0</v>
-      </c>
-      <c r="E300" s="56"/>
-      <c r="F300" s="205">
-        <v>4780023322155</v>
-      </c>
-      <c r="G300" s="112"/>
       <c r="H300" s="136">
         <f>G300*D300</f>
         <v>0</v>
@@ -11093,7 +11095,7 @@
     <row r="301" spans="1:15" ht="48.6" x14ac:dyDescent="0.35">
       <c r="A301" s="223"/>
       <c r="B301" s="169" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C301" s="173">
         <v>24</v>
@@ -11104,7 +11106,7 @@
       </c>
       <c r="E301" s="56"/>
       <c r="F301" s="205">
-        <v>4780141190964</v>
+        <v>4780023322155</v>
       </c>
       <c r="G301" s="112"/>
       <c r="H301" s="136">
@@ -11118,7 +11120,7 @@
     <row r="302" spans="1:15" ht="48.6" x14ac:dyDescent="0.35">
       <c r="A302" s="223"/>
       <c r="B302" s="169" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C302" s="173">
         <v>24</v>
@@ -11129,7 +11131,7 @@
       </c>
       <c r="E302" s="56"/>
       <c r="F302" s="205">
-        <v>4780141190971</v>
+        <v>4780141190964</v>
       </c>
       <c r="G302" s="112"/>
       <c r="H302" s="136">
@@ -11140,94 +11142,95 @@
         <v>3307100000</v>
       </c>
     </row>
-    <row r="303" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A303" s="168"/>
-      <c r="B303" s="169"/>
-      <c r="C303" s="168"/>
-      <c r="D303" s="168"/>
-      <c r="E303" s="185"/>
-      <c r="F303" s="171"/>
+    <row r="303" spans="1:15" ht="48.6" x14ac:dyDescent="0.35">
+      <c r="A303" s="223"/>
+      <c r="B303" s="169" t="s">
+        <v>409</v>
+      </c>
+      <c r="C303" s="173">
+        <v>24</v>
+      </c>
+      <c r="D303" s="222">
+        <f>+E303*C303</f>
+        <v>0</v>
+      </c>
+      <c r="E303" s="56"/>
+      <c r="F303" s="205">
+        <v>4780141190971</v>
+      </c>
       <c r="G303" s="112"/>
-      <c r="H303" s="137"/>
-      <c r="I303" s="149" t="s">
+      <c r="H303" s="136">
+        <f>G303*D303</f>
+        <v>0</v>
+      </c>
+      <c r="I303" s="144">
+        <v>3307100000</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A304" s="168"/>
+      <c r="B304" s="169"/>
+      <c r="C304" s="168"/>
+      <c r="D304" s="168"/>
+      <c r="E304" s="185"/>
+      <c r="F304" s="171"/>
+      <c r="G304" s="112"/>
+      <c r="H304" s="137"/>
+      <c r="I304" s="149" t="s">
         <v>234</v>
       </c>
-      <c r="J303" s="98"/>
-      <c r="K303" s="98"/>
-      <c r="L303" s="100"/>
-      <c r="M303" s="100"/>
-      <c r="N303" s="101"/>
-      <c r="O303" s="98"/>
-    </row>
-    <row r="304" spans="1:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="A304" s="104" t="s">
+      <c r="J304" s="98"/>
+      <c r="K304" s="98"/>
+      <c r="L304" s="100"/>
+      <c r="M304" s="100"/>
+      <c r="N304" s="101"/>
+      <c r="O304" s="98"/>
+    </row>
+    <row r="305" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+      <c r="A305" s="104" t="s">
         <v>157</v>
       </c>
-      <c r="B304" s="134" t="s">
+      <c r="B305" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="C304" s="113"/>
-      <c r="D304" s="113">
-        <f>SUM(D305:D314)</f>
-        <v>0</v>
-      </c>
-      <c r="E304" s="113">
-        <f>SUM(E305:E314)</f>
-        <v>0</v>
-      </c>
-      <c r="F304" s="123"/>
-      <c r="G304" s="108">
+      <c r="C305" s="113"/>
+      <c r="D305" s="113">
+        <f>SUM(D306:D315)</f>
+        <v>0</v>
+      </c>
+      <c r="E305" s="113">
+        <f>SUM(E306:E315)</f>
+        <v>0</v>
+      </c>
+      <c r="F305" s="123"/>
+      <c r="G305" s="108">
         <v>0.21</v>
       </c>
-      <c r="H304" s="136">
-        <f>G304*D304</f>
-        <v>0</v>
-      </c>
-      <c r="I304" s="150" t="s">
+      <c r="H305" s="136">
+        <f>G305*D305</f>
+        <v>0</v>
+      </c>
+      <c r="I305" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="305" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A305" s="2">
+    <row r="306" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A306" s="2">
         <v>1</v>
       </c>
-      <c r="B305" s="3" t="s">
+      <c r="B306" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C305" s="2">
+      <c r="C306" s="2">
         <v>50</v>
       </c>
-      <c r="D305" s="54">
-        <f t="shared" ref="D305:D313" si="11">E305*C305</f>
-        <v>0</v>
-      </c>
-      <c r="E305" s="44"/>
-      <c r="F305" s="205">
-        <v>4780023321578</v>
-      </c>
-      <c r="G305" s="110"/>
-      <c r="H305" s="136"/>
-      <c r="I305" s="144">
-        <v>3304990000</v>
-      </c>
-    </row>
-    <row r="306" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A306" s="17">
-        <v>2</v>
-      </c>
-      <c r="B306" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C306" s="17">
-        <v>50</v>
-      </c>
       <c r="D306" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="D306:D314" si="11">E306*C306</f>
         <v>0</v>
       </c>
       <c r="E306" s="44"/>
       <c r="F306" s="205">
-        <v>4780023321592</v>
+        <v>4780023321578</v>
       </c>
       <c r="G306" s="110"/>
       <c r="H306" s="136"/>
@@ -11236,13 +11239,13 @@
       </c>
     </row>
     <row r="307" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A307" s="2">
-        <v>3</v>
+      <c r="A307" s="17">
+        <v>2</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C307" s="2">
+        <v>23</v>
+      </c>
+      <c r="C307" s="17">
         <v>50</v>
       </c>
       <c r="D307" s="54">
@@ -11251,7 +11254,7 @@
       </c>
       <c r="E307" s="44"/>
       <c r="F307" s="205">
-        <v>4780023321660</v>
+        <v>4780023321592</v>
       </c>
       <c r="G307" s="110"/>
       <c r="H307" s="136"/>
@@ -11261,10 +11264,10 @@
     </row>
     <row r="308" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A308" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>24</v>
+        <v>337</v>
       </c>
       <c r="C308" s="2">
         <v>50</v>
@@ -11275,7 +11278,7 @@
       </c>
       <c r="E308" s="44"/>
       <c r="F308" s="205">
-        <v>4780023321684</v>
+        <v>4780023321660</v>
       </c>
       <c r="G308" s="110"/>
       <c r="H308" s="136"/>
@@ -11285,10 +11288,10 @@
     </row>
     <row r="309" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C309" s="2">
         <v>50</v>
@@ -11299,7 +11302,7 @@
       </c>
       <c r="E309" s="44"/>
       <c r="F309" s="205">
-        <v>4780023321721</v>
+        <v>4780023321684</v>
       </c>
       <c r="G309" s="110"/>
       <c r="H309" s="136"/>
@@ -11307,14 +11310,14 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="310" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A310" s="17">
-        <v>6</v>
+    <row r="310" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A310" s="2">
+        <v>5</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C310" s="17">
+        <v>25</v>
+      </c>
+      <c r="C310" s="2">
         <v>50</v>
       </c>
       <c r="D310" s="54">
@@ -11323,7 +11326,7 @@
       </c>
       <c r="E310" s="44"/>
       <c r="F310" s="205">
-        <v>4780023321707</v>
+        <v>4780023321721</v>
       </c>
       <c r="G310" s="110"/>
       <c r="H310" s="136"/>
@@ -11331,12 +11334,12 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="311" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A311" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C311" s="17">
         <v>50</v>
@@ -11347,7 +11350,7 @@
       </c>
       <c r="E311" s="44"/>
       <c r="F311" s="205">
-        <v>4780023321738</v>
+        <v>4780023321707</v>
       </c>
       <c r="G311" s="110"/>
       <c r="H311" s="136"/>
@@ -11357,10 +11360,10 @@
     </row>
     <row r="312" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A312" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C312" s="17">
         <v>50</v>
@@ -11371,7 +11374,7 @@
       </c>
       <c r="E312" s="44"/>
       <c r="F312" s="205">
-        <v>4780023321745</v>
+        <v>4780023321738</v>
       </c>
       <c r="G312" s="110"/>
       <c r="H312" s="136"/>
@@ -11381,10 +11384,10 @@
     </row>
     <row r="313" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A313" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C313" s="17">
         <v>50</v>
@@ -11395,7 +11398,7 @@
       </c>
       <c r="E313" s="44"/>
       <c r="F313" s="205">
-        <v>4780023321769</v>
+        <v>4780023321745</v>
       </c>
       <c r="G313" s="110"/>
       <c r="H313" s="136"/>
@@ -11403,23 +11406,23 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="314" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A314" s="2">
-        <v>10</v>
+    <row r="314" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A314" s="17">
+        <v>9</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C314" s="2">
+        <v>29</v>
+      </c>
+      <c r="C314" s="17">
         <v>50</v>
       </c>
       <c r="D314" s="54">
-        <f>E314*C314</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E314" s="44"/>
       <c r="F314" s="205">
-        <v>4780023321790</v>
+        <v>4780023321769</v>
       </c>
       <c r="G314" s="110"/>
       <c r="H314" s="136"/>
@@ -11427,75 +11430,69 @@
         <v>3304990000</v>
       </c>
     </row>
-    <row r="315" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A315" s="2"/>
-      <c r="B315" s="3"/>
-      <c r="C315" s="2"/>
-      <c r="D315" s="54"/>
-      <c r="E315" s="162"/>
-      <c r="F315" s="122"/>
+    <row r="315" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A315" s="2">
+        <v>10</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C315" s="2">
+        <v>50</v>
+      </c>
+      <c r="D315" s="54">
+        <f>E315*C315</f>
+        <v>0</v>
+      </c>
+      <c r="E315" s="44"/>
+      <c r="F315" s="205">
+        <v>4780023321790</v>
+      </c>
       <c r="G315" s="110"/>
       <c r="H315" s="136"/>
-      <c r="I315" s="150" t="s">
+      <c r="I315" s="144">
+        <v>3304990000</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A316" s="2"/>
+      <c r="B316" s="3"/>
+      <c r="C316" s="2"/>
+      <c r="D316" s="54"/>
+      <c r="E316" s="162"/>
+      <c r="F316" s="122"/>
+      <c r="G316" s="110"/>
+      <c r="H316" s="136"/>
+      <c r="I316" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="316" spans="1:15" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A316" s="105" t="s">
+    <row r="317" spans="1:15" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A317" s="105" t="s">
         <v>157</v>
       </c>
-      <c r="B316" s="105" t="s">
+      <c r="B317" s="105" t="s">
         <v>211</v>
       </c>
-      <c r="C316" s="115"/>
-      <c r="D316" s="115">
-        <f>SUM(D317:D318)</f>
-        <v>0</v>
-      </c>
-      <c r="E316" s="113">
-        <f>SUM(E317:E318)</f>
-        <v>0</v>
-      </c>
-      <c r="F316" s="123"/>
-      <c r="G316" s="140">
+      <c r="C317" s="115"/>
+      <c r="D317" s="115">
+        <f>SUM(D318:D319)</f>
+        <v>0</v>
+      </c>
+      <c r="E317" s="113">
+        <f>SUM(E318:E319)</f>
+        <v>0</v>
+      </c>
+      <c r="F317" s="123"/>
+      <c r="G317" s="140">
         <v>0.8</v>
       </c>
-      <c r="H316" s="137">
-        <f>G316*D316</f>
-        <v>0</v>
-      </c>
-      <c r="I316" s="149" t="s">
+      <c r="H317" s="137">
+        <f>G317*D317</f>
+        <v>0</v>
+      </c>
+      <c r="I317" s="149" t="s">
         <v>234</v>
-      </c>
-      <c r="J316" s="98"/>
-      <c r="K316" s="98"/>
-      <c r="L316" s="100"/>
-      <c r="M316" s="100"/>
-      <c r="N316" s="101"/>
-      <c r="O316" s="98"/>
-    </row>
-    <row r="317" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A317" s="57">
-        <v>1</v>
-      </c>
-      <c r="B317" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="C317" s="2">
-        <v>20</v>
-      </c>
-      <c r="D317" s="16">
-        <f>C317*E317</f>
-        <v>0</v>
-      </c>
-      <c r="E317" s="39"/>
-      <c r="F317" s="208">
-        <v>4780023321929</v>
-      </c>
-      <c r="G317" s="112"/>
-      <c r="H317" s="137"/>
-      <c r="I317" s="144">
-        <v>3307900008</v>
       </c>
       <c r="J317" s="98"/>
       <c r="K317" s="98"/>
@@ -11506,10 +11503,10 @@
     </row>
     <row r="318" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A318" s="57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B318" s="64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C318" s="2">
         <v>20</v>
@@ -11520,7 +11517,7 @@
       </c>
       <c r="E318" s="39"/>
       <c r="F318" s="208">
-        <v>4780023321912</v>
+        <v>4780023321929</v>
       </c>
       <c r="G318" s="112"/>
       <c r="H318" s="137"/>
@@ -11535,16 +11532,27 @@
       <c r="O318" s="98"/>
     </row>
     <row r="319" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A319" s="2"/>
-      <c r="B319" s="67"/>
-      <c r="C319" s="2"/>
-      <c r="D319" s="16"/>
-      <c r="E319" s="16"/>
-      <c r="F319" s="124"/>
+      <c r="A319" s="57">
+        <v>2</v>
+      </c>
+      <c r="B319" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C319" s="2">
+        <v>20</v>
+      </c>
+      <c r="D319" s="16">
+        <f>C319*E319</f>
+        <v>0</v>
+      </c>
+      <c r="E319" s="39"/>
+      <c r="F319" s="208">
+        <v>4780023321912</v>
+      </c>
       <c r="G319" s="112"/>
       <c r="H319" s="137"/>
-      <c r="I319" s="149" t="s">
-        <v>234</v>
+      <c r="I319" s="144">
+        <v>3307900008</v>
       </c>
       <c r="J319" s="98"/>
       <c r="K319" s="98"/>
@@ -11553,64 +11561,53 @@
       <c r="N319" s="101"/>
       <c r="O319" s="98"/>
     </row>
-    <row r="320" spans="1:15" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A320" s="105" t="s">
-        <v>157</v>
-      </c>
-      <c r="B320" s="105" t="s">
-        <v>212</v>
-      </c>
-      <c r="C320" s="115"/>
-      <c r="D320" s="115">
-        <f>SUM(D321:D322)</f>
-        <v>0</v>
-      </c>
-      <c r="E320" s="113">
-        <f>SUM(E321:E322)</f>
-        <v>0</v>
-      </c>
-      <c r="F320" s="123"/>
-      <c r="G320" s="140">
-        <v>0.63</v>
-      </c>
-      <c r="H320" s="137">
-        <f>G320*D320</f>
-        <v>0</v>
-      </c>
+    <row r="320" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A320" s="2"/>
+      <c r="B320" s="67"/>
+      <c r="C320" s="2"/>
+      <c r="D320" s="16"/>
+      <c r="E320" s="16"/>
+      <c r="F320" s="124"/>
+      <c r="G320" s="112"/>
+      <c r="H320" s="137"/>
       <c r="I320" s="149" t="s">
         <v>234</v>
       </c>
-      <c r="J320" s="206"/>
+      <c r="J320" s="98"/>
       <c r="K320" s="98"/>
       <c r="L320" s="100"/>
       <c r="M320" s="100"/>
       <c r="N320" s="101"/>
       <c r="O320" s="98"/>
     </row>
-    <row r="321" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A321" s="57">
-        <v>1</v>
-      </c>
-      <c r="B321" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="C321" s="2">
-        <v>30</v>
-      </c>
-      <c r="D321" s="16">
-        <f>C321*E321</f>
-        <v>0</v>
-      </c>
-      <c r="E321" s="203"/>
-      <c r="F321" s="207">
-        <v>4780023323770</v>
-      </c>
-      <c r="G321" s="112"/>
-      <c r="H321" s="137"/>
-      <c r="I321" s="144">
-        <v>3307900008</v>
-      </c>
-      <c r="J321" s="98"/>
+    <row r="321" spans="1:15" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A321" s="105" t="s">
+        <v>157</v>
+      </c>
+      <c r="B321" s="105" t="s">
+        <v>212</v>
+      </c>
+      <c r="C321" s="115"/>
+      <c r="D321" s="115">
+        <f>SUM(D322:D323)</f>
+        <v>0</v>
+      </c>
+      <c r="E321" s="113">
+        <f>SUM(E322:E323)</f>
+        <v>0</v>
+      </c>
+      <c r="F321" s="123"/>
+      <c r="G321" s="140">
+        <v>0.63</v>
+      </c>
+      <c r="H321" s="137">
+        <f>G321*D321</f>
+        <v>0</v>
+      </c>
+      <c r="I321" s="149" t="s">
+        <v>234</v>
+      </c>
+      <c r="J321" s="206"/>
       <c r="K321" s="98"/>
       <c r="L321" s="100"/>
       <c r="M321" s="100"/>
@@ -11619,10 +11616,10 @@
     </row>
     <row r="322" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A322" s="57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B322" s="64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C322" s="2">
         <v>30</v>
@@ -11631,9 +11628,9 @@
         <f>C322*E322</f>
         <v>0</v>
       </c>
-      <c r="E322" s="39"/>
+      <c r="E322" s="203"/>
       <c r="F322" s="207">
-        <v>4780023323787</v>
+        <v>4780023323770</v>
       </c>
       <c r="G322" s="112"/>
       <c r="H322" s="137"/>
@@ -11648,63 +11645,59 @@
       <c r="O322" s="98"/>
     </row>
     <row r="323" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A323" s="2"/>
-      <c r="B323" s="3"/>
-      <c r="C323" s="2"/>
-      <c r="D323" s="54"/>
-      <c r="E323" s="162"/>
-      <c r="F323" s="122"/>
-      <c r="G323" s="110"/>
-      <c r="H323" s="136"/>
-      <c r="I323" s="150" t="s">
+      <c r="A323" s="57">
+        <v>2</v>
+      </c>
+      <c r="B323" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="C323" s="2">
+        <v>30</v>
+      </c>
+      <c r="D323" s="16">
+        <f>C323*E323</f>
+        <v>0</v>
+      </c>
+      <c r="E323" s="39"/>
+      <c r="F323" s="207">
+        <v>4780023323787</v>
+      </c>
+      <c r="G323" s="112"/>
+      <c r="H323" s="137"/>
+      <c r="I323" s="144">
+        <v>3307900008</v>
+      </c>
+      <c r="J323" s="98"/>
+      <c r="K323" s="98"/>
+      <c r="L323" s="100"/>
+      <c r="M323" s="100"/>
+      <c r="N323" s="101"/>
+      <c r="O323" s="98"/>
+    </row>
+    <row r="324" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A324" s="2"/>
+      <c r="B324" s="3"/>
+      <c r="C324" s="2"/>
+      <c r="D324" s="54"/>
+      <c r="E324" s="162"/>
+      <c r="F324" s="122"/>
+      <c r="G324" s="110"/>
+      <c r="H324" s="136"/>
+      <c r="I324" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="324" spans="1:15" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A324" s="2"/>
-      <c r="B324" s="165" t="s">
+    <row r="325" spans="1:15" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="A325" s="2"/>
+      <c r="B325" s="165" t="s">
         <v>229</v>
       </c>
-      <c r="C324" s="2"/>
-      <c r="D324" s="8"/>
-      <c r="E324" s="162"/>
-      <c r="F324" s="120"/>
-      <c r="G324" s="112"/>
-      <c r="H324" s="137"/>
-      <c r="I324" s="149" t="s">
-        <v>234</v>
-      </c>
-      <c r="J324" s="98"/>
-      <c r="K324" s="98"/>
-      <c r="L324" s="100"/>
-      <c r="M324" s="100"/>
-      <c r="N324" s="101"/>
-      <c r="O324" s="98"/>
-    </row>
-    <row r="325" spans="1:15" ht="36" x14ac:dyDescent="0.3">
-      <c r="A325" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B325" s="134" t="s">
-        <v>210</v>
-      </c>
-      <c r="C325" s="113"/>
-      <c r="D325" s="113">
-        <f>SUM(D326:D330)</f>
-        <v>0</v>
-      </c>
-      <c r="E325" s="113">
-        <f>SUM(E326:E330)</f>
-        <v>0</v>
-      </c>
-      <c r="F325" s="121"/>
-      <c r="G325" s="139">
-        <v>0.84</v>
-      </c>
-      <c r="H325" s="137">
-        <f>G325*D325</f>
-        <v>0</v>
-      </c>
+      <c r="C325" s="2"/>
+      <c r="D325" s="8"/>
+      <c r="E325" s="162"/>
+      <c r="F325" s="120"/>
+      <c r="G325" s="112"/>
+      <c r="H325" s="137"/>
       <c r="I325" s="149" t="s">
         <v>234</v>
       </c>
@@ -11715,28 +11708,32 @@
       <c r="N325" s="101"/>
       <c r="O325" s="98"/>
     </row>
-    <row r="326" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
-      <c r="A326" s="2">
-        <v>1</v>
-      </c>
-      <c r="B326" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C326" s="2">
-        <v>15</v>
-      </c>
-      <c r="D326" s="8">
-        <f>E326*C326</f>
-        <v>0</v>
-      </c>
-      <c r="E326" s="127"/>
-      <c r="F326" s="208">
-        <v>4780023320458</v>
-      </c>
-      <c r="G326" s="112"/>
-      <c r="H326" s="137"/>
-      <c r="I326" s="144">
-        <v>3401209000</v>
+    <row r="326" spans="1:15" ht="36" x14ac:dyDescent="0.3">
+      <c r="A326" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B326" s="134" t="s">
+        <v>210</v>
+      </c>
+      <c r="C326" s="113"/>
+      <c r="D326" s="113">
+        <f>SUM(D327:D331)</f>
+        <v>0</v>
+      </c>
+      <c r="E326" s="113">
+        <f>SUM(E327:E331)</f>
+        <v>0</v>
+      </c>
+      <c r="F326" s="121"/>
+      <c r="G326" s="139">
+        <v>0.84</v>
+      </c>
+      <c r="H326" s="137">
+        <f>G326*D326</f>
+        <v>0</v>
+      </c>
+      <c r="I326" s="149" t="s">
+        <v>234</v>
       </c>
       <c r="J326" s="98"/>
       <c r="K326" s="98"/>
@@ -11747,10 +11744,10 @@
     </row>
     <row r="327" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A327" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C327" s="2">
         <v>15</v>
@@ -11761,7 +11758,7 @@
       </c>
       <c r="E327" s="127"/>
       <c r="F327" s="208">
-        <v>4780023320502</v>
+        <v>4780023320458</v>
       </c>
       <c r="G327" s="112"/>
       <c r="H327" s="137"/>
@@ -11777,10 +11774,10 @@
     </row>
     <row r="328" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C328" s="2">
         <v>15</v>
@@ -11791,7 +11788,7 @@
       </c>
       <c r="E328" s="127"/>
       <c r="F328" s="208">
-        <v>4780023320465</v>
+        <v>4780023320502</v>
       </c>
       <c r="G328" s="112"/>
       <c r="H328" s="137"/>
@@ -11807,10 +11804,10 @@
     </row>
     <row r="329" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A329" s="2">
-        <v>4</v>
-      </c>
-      <c r="B329" s="68" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C329" s="2">
         <v>15</v>
@@ -11821,7 +11818,7 @@
       </c>
       <c r="E329" s="127"/>
       <c r="F329" s="208">
-        <v>4780023320489</v>
+        <v>4780023320465</v>
       </c>
       <c r="G329" s="112"/>
       <c r="H329" s="137"/>
@@ -11837,10 +11834,10 @@
     </row>
     <row r="330" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
-        <v>5</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
+      </c>
+      <c r="B330" s="68" t="s">
+        <v>31</v>
       </c>
       <c r="C330" s="2">
         <v>15</v>
@@ -11851,7 +11848,7 @@
       </c>
       <c r="E330" s="127"/>
       <c r="F330" s="208">
-        <v>4780023320496</v>
+        <v>4780023320489</v>
       </c>
       <c r="G330" s="112"/>
       <c r="H330" s="137"/>
@@ -11865,17 +11862,28 @@
       <c r="N330" s="101"/>
       <c r="O330" s="98"/>
     </row>
-    <row r="331" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A331" s="2"/>
-      <c r="B331" s="3"/>
-      <c r="C331" s="2"/>
-      <c r="D331" s="8"/>
-      <c r="E331" s="186"/>
-      <c r="F331" s="120"/>
+    <row r="331" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
+      <c r="A331" s="2">
+        <v>5</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C331" s="2">
+        <v>15</v>
+      </c>
+      <c r="D331" s="8">
+        <f>E331*C331</f>
+        <v>0</v>
+      </c>
+      <c r="E331" s="127"/>
+      <c r="F331" s="208">
+        <v>4780023320496</v>
+      </c>
       <c r="G331" s="112"/>
       <c r="H331" s="137"/>
-      <c r="I331" s="148" t="s">
-        <v>234</v>
+      <c r="I331" s="144">
+        <v>3401209000</v>
       </c>
       <c r="J331" s="98"/>
       <c r="K331" s="98"/>
@@ -11884,29 +11892,16 @@
       <c r="N331" s="101"/>
       <c r="O331" s="98"/>
     </row>
-    <row r="332" spans="1:15" ht="36" x14ac:dyDescent="0.3">
-      <c r="A332" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B332" s="134" t="s">
-        <v>350</v>
-      </c>
-      <c r="C332" s="113"/>
-      <c r="D332" s="113">
-        <f>SUM(D333:D342)</f>
-        <v>0</v>
-      </c>
-      <c r="E332" s="113">
-        <f>SUM(E333:E342)</f>
-        <v>0</v>
-      </c>
-      <c r="F332" s="121"/>
-      <c r="G332" s="139"/>
-      <c r="H332" s="137">
-        <f>SUM(H333:H342)</f>
-        <v>0</v>
-      </c>
-      <c r="I332" s="149" t="s">
+    <row r="332" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A332" s="2"/>
+      <c r="B332" s="3"/>
+      <c r="C332" s="2"/>
+      <c r="D332" s="8"/>
+      <c r="E332" s="186"/>
+      <c r="F332" s="120"/>
+      <c r="G332" s="112"/>
+      <c r="H332" s="137"/>
+      <c r="I332" s="148" t="s">
         <v>234</v>
       </c>
       <c r="J332" s="98"/>
@@ -11916,33 +11911,30 @@
       <c r="N332" s="101"/>
       <c r="O332" s="98"/>
     </row>
-    <row r="333" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
-      <c r="A333" s="2">
-        <v>1</v>
-      </c>
-      <c r="B333" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C333" s="2">
-        <v>8</v>
-      </c>
-      <c r="D333" s="8">
-        <f t="shared" ref="D333:D342" si="12">E333*C333</f>
-        <v>0</v>
-      </c>
-      <c r="E333" s="127"/>
-      <c r="F333" s="208">
-        <v>4780141190605</v>
-      </c>
-      <c r="G333" s="112">
-        <v>0.64</v>
-      </c>
+    <row r="333" spans="1:15" ht="36" x14ac:dyDescent="0.3">
+      <c r="A333" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B333" s="134" t="s">
+        <v>350</v>
+      </c>
+      <c r="C333" s="113"/>
+      <c r="D333" s="113">
+        <f>SUM(D334:D343)</f>
+        <v>0</v>
+      </c>
+      <c r="E333" s="113">
+        <f>SUM(E334:E343)</f>
+        <v>0</v>
+      </c>
+      <c r="F333" s="121"/>
+      <c r="G333" s="139"/>
       <c r="H333" s="137">
-        <f t="shared" ref="H333:H342" si="13">G333*D333</f>
-        <v>0</v>
-      </c>
-      <c r="I333" s="144">
-        <v>3401209000</v>
+        <f>SUM(H334:H343)</f>
+        <v>0</v>
+      </c>
+      <c r="I333" s="149" t="s">
+        <v>234</v>
       </c>
       <c r="J333" s="98"/>
       <c r="K333" s="98"/>
@@ -11953,27 +11945,27 @@
     </row>
     <row r="334" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C334" s="2">
         <v>8</v>
       </c>
       <c r="D334" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D334:D343" si="12">E334*C334</f>
         <v>0</v>
       </c>
       <c r="E334" s="127"/>
       <c r="F334" s="208">
-        <v>4780141190599</v>
+        <v>4780141190605</v>
       </c>
       <c r="G334" s="112">
         <v>0.64</v>
       </c>
       <c r="H334" s="137">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="H334:H343" si="13">G334*D334</f>
         <v>0</v>
       </c>
       <c r="I334" s="144">
@@ -11988,10 +11980,10 @@
     </row>
     <row r="335" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A335" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C335" s="2">
         <v>8</v>
@@ -12002,7 +11994,7 @@
       </c>
       <c r="E335" s="127"/>
       <c r="F335" s="208">
-        <v>4780141190612</v>
+        <v>4780141190599</v>
       </c>
       <c r="G335" s="112">
         <v>0.64</v>
@@ -12023,10 +12015,10 @@
     </row>
     <row r="336" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
-        <v>4</v>
-      </c>
-      <c r="B336" s="68" t="s">
-        <v>354</v>
+        <v>3</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="C336" s="2">
         <v>8</v>
@@ -12037,7 +12029,7 @@
       </c>
       <c r="E336" s="127"/>
       <c r="F336" s="208">
-        <v>4780141190629</v>
+        <v>4780141190612</v>
       </c>
       <c r="G336" s="112">
         <v>0.64</v>
@@ -12058,10 +12050,10 @@
     </row>
     <row r="337" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A337" s="2">
-        <v>5</v>
-      </c>
-      <c r="B337" s="3" t="s">
-        <v>355</v>
+        <v>4</v>
+      </c>
+      <c r="B337" s="68" t="s">
+        <v>354</v>
       </c>
       <c r="C337" s="2">
         <v>8</v>
@@ -12072,7 +12064,7 @@
       </c>
       <c r="E337" s="127"/>
       <c r="F337" s="208">
-        <v>4780141190643</v>
+        <v>4780141190629</v>
       </c>
       <c r="G337" s="112">
         <v>0.64</v>
@@ -12093,10 +12085,10 @@
     </row>
     <row r="338" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C338" s="2">
         <v>8</v>
@@ -12107,7 +12099,7 @@
       </c>
       <c r="E338" s="127"/>
       <c r="F338" s="208">
-        <v>4780141190650</v>
+        <v>4780141190643</v>
       </c>
       <c r="G338" s="112">
         <v>0.64</v>
@@ -12128,27 +12120,27 @@
     </row>
     <row r="339" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A339" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C339" s="2">
         <v>8</v>
       </c>
       <c r="D339" s="8">
-        <f t="shared" ref="D339" si="14">E339*C339</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E339" s="127"/>
       <c r="F339" s="208">
-        <v>4780141190636</v>
+        <v>4780141190650</v>
       </c>
       <c r="G339" s="112">
         <v>0.64</v>
       </c>
       <c r="H339" s="137">
-        <f t="shared" ref="H339" si="15">G339*D339</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I339" s="144">
@@ -12163,27 +12155,27 @@
     </row>
     <row r="340" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A340" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>419</v>
+        <v>357</v>
       </c>
       <c r="C340" s="2">
         <v>8</v>
       </c>
       <c r="D340" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D340" si="14">E340*C340</f>
         <v>0</v>
       </c>
       <c r="E340" s="127"/>
       <c r="F340" s="208">
-        <v>4780141191138</v>
+        <v>4780141190636</v>
       </c>
       <c r="G340" s="112">
         <v>0.64</v>
       </c>
       <c r="H340" s="137">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="H340" si="15">G340*D340</f>
         <v>0</v>
       </c>
       <c r="I340" s="144">
@@ -12198,10 +12190,10 @@
     </row>
     <row r="341" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A341" s="2">
-        <v>9</v>
-      </c>
-      <c r="B341" s="68" t="s">
-        <v>358</v>
+        <v>8</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>419</v>
       </c>
       <c r="C341" s="2">
         <v>8</v>
@@ -12212,10 +12204,10 @@
       </c>
       <c r="E341" s="127"/>
       <c r="F341" s="208">
-        <v>4780141190681</v>
+        <v>4780141191138</v>
       </c>
       <c r="G341" s="112">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="H341" s="137">
         <f t="shared" si="13"/>
@@ -12233,10 +12225,10 @@
     </row>
     <row r="342" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A342" s="2">
-        <v>10</v>
-      </c>
-      <c r="B342" s="3" t="s">
-        <v>359</v>
+        <v>9</v>
+      </c>
+      <c r="B342" s="68" t="s">
+        <v>358</v>
       </c>
       <c r="C342" s="2">
         <v>8</v>
@@ -12247,7 +12239,7 @@
       </c>
       <c r="E342" s="127"/>
       <c r="F342" s="208">
-        <v>4780141190667</v>
+        <v>4780141190681</v>
       </c>
       <c r="G342" s="112">
         <v>0.77</v>
@@ -12266,17 +12258,33 @@
       <c r="N342" s="101"/>
       <c r="O342" s="98"/>
     </row>
-    <row r="343" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A343" s="2"/>
-      <c r="B343" s="3"/>
-      <c r="C343" s="2"/>
-      <c r="D343" s="8"/>
-      <c r="E343" s="186"/>
-      <c r="F343" s="120"/>
-      <c r="G343" s="112"/>
-      <c r="H343" s="137"/>
-      <c r="I343" s="148" t="s">
-        <v>234</v>
+    <row r="343" spans="1:15" ht="31.8" x14ac:dyDescent="0.35">
+      <c r="A343" s="2">
+        <v>10</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C343" s="2">
+        <v>8</v>
+      </c>
+      <c r="D343" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E343" s="127"/>
+      <c r="F343" s="208">
+        <v>4780141190667</v>
+      </c>
+      <c r="G343" s="112">
+        <v>0.77</v>
+      </c>
+      <c r="H343" s="137">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="I343" s="144">
+        <v>3401209000</v>
       </c>
       <c r="J343" s="98"/>
       <c r="K343" s="98"/>
@@ -12285,115 +12293,110 @@
       <c r="N343" s="101"/>
       <c r="O343" s="98"/>
     </row>
-    <row r="344" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A344" s="40"/>
-      <c r="B344" s="135" t="s">
+    <row r="344" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A344" s="2"/>
+      <c r="B344" s="3"/>
+      <c r="C344" s="2"/>
+      <c r="D344" s="8"/>
+      <c r="E344" s="186"/>
+      <c r="F344" s="120"/>
+      <c r="G344" s="112"/>
+      <c r="H344" s="137"/>
+      <c r="I344" s="148" t="s">
+        <v>234</v>
+      </c>
+      <c r="J344" s="98"/>
+      <c r="K344" s="98"/>
+      <c r="L344" s="100"/>
+      <c r="M344" s="100"/>
+      <c r="N344" s="101"/>
+      <c r="O344" s="98"/>
+    </row>
+    <row r="345" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="A345" s="40"/>
+      <c r="B345" s="135" t="s">
         <v>215</v>
       </c>
-      <c r="C344" s="117">
+      <c r="C345" s="117">
         <v>100</v>
       </c>
-      <c r="D344" s="117">
-        <f>C344*E344</f>
-        <v>0</v>
-      </c>
-      <c r="E344" s="183"/>
-      <c r="F344" s="123">
+      <c r="D345" s="117">
+        <f>C345*E345</f>
+        <v>0</v>
+      </c>
+      <c r="E345" s="183"/>
+      <c r="F345" s="123">
         <v>4780023322025</v>
       </c>
-      <c r="G344" s="139">
+      <c r="G345" s="139">
         <v>0.19</v>
       </c>
-      <c r="H344" s="136">
-        <f>G344*D344</f>
-        <v>0</v>
-      </c>
-      <c r="I344" s="144">
+      <c r="H345" s="136">
+        <f>G345*D345</f>
+        <v>0</v>
+      </c>
+      <c r="I345" s="144">
         <v>3401110001</v>
       </c>
     </row>
-    <row r="345" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A345" s="160"/>
-      <c r="B345" s="161"/>
-      <c r="C345" s="187"/>
-      <c r="D345" s="187"/>
-      <c r="E345" s="187"/>
-      <c r="F345" s="124"/>
-      <c r="G345" s="112"/>
-      <c r="H345" s="136"/>
-      <c r="I345" s="148" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="346" spans="1:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="A346" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B346" s="135" t="s">
-        <v>214</v>
-      </c>
-      <c r="C346" s="117"/>
-      <c r="D346" s="117">
-        <f>SUM(D347:D353)</f>
-        <v>0</v>
-      </c>
-      <c r="E346" s="117">
-        <f>SUM(E347:E353)</f>
-        <v>0</v>
-      </c>
-      <c r="F346" s="123"/>
-      <c r="G346" s="139">
-        <v>0.22</v>
-      </c>
-      <c r="H346" s="136">
-        <f>G346*D346</f>
-        <v>0</v>
-      </c>
+    <row r="346" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A346" s="160"/>
+      <c r="B346" s="161"/>
+      <c r="C346" s="187"/>
+      <c r="D346" s="187"/>
+      <c r="E346" s="187"/>
+      <c r="F346" s="124"/>
+      <c r="G346" s="112"/>
+      <c r="H346" s="136"/>
       <c r="I346" s="148" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="347" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A347" s="2">
-        <v>1</v>
-      </c>
-      <c r="B347" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C347" s="2">
-        <v>72</v>
-      </c>
-      <c r="D347" s="8">
-        <f t="shared" ref="D347:D353" si="16">E347*C347</f>
-        <v>0</v>
-      </c>
-      <c r="E347" s="39"/>
-      <c r="F347" s="207">
-        <v>4780023325217</v>
-      </c>
-      <c r="G347" s="112"/>
-      <c r="H347" s="136"/>
-      <c r="I347" s="144">
-        <v>3401110001</v>
+    <row r="347" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+      <c r="A347" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B347" s="135" t="s">
+        <v>214</v>
+      </c>
+      <c r="C347" s="117"/>
+      <c r="D347" s="117">
+        <f>SUM(D348:D354)</f>
+        <v>0</v>
+      </c>
+      <c r="E347" s="117">
+        <f>SUM(E348:E354)</f>
+        <v>0</v>
+      </c>
+      <c r="F347" s="123"/>
+      <c r="G347" s="139">
+        <v>0.22</v>
+      </c>
+      <c r="H347" s="136">
+        <f>G347*D347</f>
+        <v>0</v>
+      </c>
+      <c r="I347" s="148" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="348" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C348" s="2">
         <v>72</v>
       </c>
       <c r="D348" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="D348:D354" si="16">E348*C348</f>
         <v>0</v>
       </c>
       <c r="E348" s="39"/>
       <c r="F348" s="207">
-        <v>4780023325170</v>
+        <v>4780023325217</v>
       </c>
       <c r="G348" s="112"/>
       <c r="H348" s="136"/>
@@ -12403,10 +12406,10 @@
     </row>
     <row r="349" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A349" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C349" s="2">
         <v>72</v>
@@ -12417,7 +12420,7 @@
       </c>
       <c r="E349" s="39"/>
       <c r="F349" s="207">
-        <v>4780023325163</v>
+        <v>4780023325170</v>
       </c>
       <c r="G349" s="112"/>
       <c r="H349" s="136"/>
@@ -12427,10 +12430,10 @@
     </row>
     <row r="350" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A350" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C350" s="2">
         <v>72</v>
@@ -12441,7 +12444,7 @@
       </c>
       <c r="E350" s="39"/>
       <c r="F350" s="207">
-        <v>4780023325156</v>
+        <v>4780023325163</v>
       </c>
       <c r="G350" s="112"/>
       <c r="H350" s="136"/>
@@ -12451,10 +12454,10 @@
     </row>
     <row r="351" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A351" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C351" s="2">
         <v>72</v>
@@ -12465,7 +12468,7 @@
       </c>
       <c r="E351" s="39"/>
       <c r="F351" s="207">
-        <v>4780023325187</v>
+        <v>4780023325156</v>
       </c>
       <c r="G351" s="112"/>
       <c r="H351" s="136"/>
@@ -12475,10 +12478,10 @@
     </row>
     <row r="352" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A352" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C352" s="2">
         <v>72</v>
@@ -12489,7 +12492,7 @@
       </c>
       <c r="E352" s="39"/>
       <c r="F352" s="207">
-        <v>4780023325194</v>
+        <v>4780023325187</v>
       </c>
       <c r="G352" s="112"/>
       <c r="H352" s="136"/>
@@ -12499,10 +12502,10 @@
     </row>
     <row r="353" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A353" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C353" s="2">
         <v>72</v>
@@ -12513,7 +12516,7 @@
       </c>
       <c r="E353" s="39"/>
       <c r="F353" s="207">
-        <v>4780023325200</v>
+        <v>4780023325194</v>
       </c>
       <c r="G353" s="112"/>
       <c r="H353" s="136"/>
@@ -12522,76 +12525,76 @@
       </c>
     </row>
     <row r="354" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A354" s="160"/>
-      <c r="B354" s="161"/>
-      <c r="C354" s="161"/>
-      <c r="D354" s="182"/>
-      <c r="E354" s="182"/>
-      <c r="F354" s="124"/>
+      <c r="A354" s="2">
+        <v>7</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C354" s="2">
+        <v>72</v>
+      </c>
+      <c r="D354" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="E354" s="39"/>
+      <c r="F354" s="207">
+        <v>4780023325200</v>
+      </c>
       <c r="G354" s="112"/>
       <c r="H354" s="136"/>
-      <c r="I354" s="148" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A355" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B355" s="135" t="s">
-        <v>216</v>
-      </c>
-      <c r="C355" s="117"/>
-      <c r="D355" s="117">
-        <f>SUM(D356:D362)</f>
-        <v>0</v>
-      </c>
-      <c r="E355" s="117">
-        <f>SUM(E356:E362)</f>
-        <v>0</v>
-      </c>
-      <c r="F355" s="123"/>
-      <c r="G355" s="139">
-        <v>0.33</v>
-      </c>
-      <c r="H355" s="136">
-        <f>G355*D355</f>
-        <v>0</v>
-      </c>
+      <c r="I354" s="144">
+        <v>3401110001</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A355" s="160"/>
+      <c r="B355" s="161"/>
+      <c r="C355" s="161"/>
+      <c r="D355" s="182"/>
+      <c r="E355" s="182"/>
+      <c r="F355" s="124"/>
+      <c r="G355" s="112"/>
+      <c r="H355" s="136"/>
       <c r="I355" s="148" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A356" s="2">
-        <v>1</v>
-      </c>
-      <c r="B356" s="69" t="s">
-        <v>70</v>
-      </c>
-      <c r="C356" s="2">
-        <v>48</v>
-      </c>
-      <c r="D356" s="8">
-        <f>E356*C356</f>
-        <v>0</v>
-      </c>
-      <c r="E356" s="39"/>
-      <c r="F356" s="207">
-        <v>4780023325477</v>
-      </c>
-      <c r="G356" s="112"/>
-      <c r="H356" s="136"/>
-      <c r="I356" s="144">
-        <v>3401110001</v>
+    <row r="356" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A356" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B356" s="135" t="s">
+        <v>216</v>
+      </c>
+      <c r="C356" s="117"/>
+      <c r="D356" s="117">
+        <f>SUM(D357:D363)</f>
+        <v>0</v>
+      </c>
+      <c r="E356" s="117">
+        <f>SUM(E357:E363)</f>
+        <v>0</v>
+      </c>
+      <c r="F356" s="123"/>
+      <c r="G356" s="139">
+        <v>0.33</v>
+      </c>
+      <c r="H356" s="136">
+        <f>G356*D356</f>
+        <v>0</v>
+      </c>
+      <c r="I356" s="148" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="357" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A357" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B357" s="69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C357" s="2">
         <v>48</v>
@@ -12602,7 +12605,7 @@
       </c>
       <c r="E357" s="39"/>
       <c r="F357" s="207">
-        <v>4780023325491</v>
+        <v>4780023325477</v>
       </c>
       <c r="G357" s="112"/>
       <c r="H357" s="136"/>
@@ -12612,10 +12615,10 @@
     </row>
     <row r="358" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A358" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B358" s="69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C358" s="2">
         <v>48</v>
@@ -12626,7 +12629,7 @@
       </c>
       <c r="E358" s="39"/>
       <c r="F358" s="207">
-        <v>4780023325460</v>
+        <v>4780023325491</v>
       </c>
       <c r="G358" s="112"/>
       <c r="H358" s="136"/>
@@ -12636,10 +12639,10 @@
     </row>
     <row r="359" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A359" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B359" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C359" s="2">
         <v>48</v>
@@ -12650,7 +12653,7 @@
       </c>
       <c r="E359" s="39"/>
       <c r="F359" s="207">
-        <v>4780023325484</v>
+        <v>4780023325460</v>
       </c>
       <c r="G359" s="112"/>
       <c r="H359" s="136"/>
@@ -12660,10 +12663,10 @@
     </row>
     <row r="360" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A360" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B360" s="69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C360" s="2">
         <v>48</v>
@@ -12674,7 +12677,7 @@
       </c>
       <c r="E360" s="39"/>
       <c r="F360" s="207">
-        <v>4780023325446</v>
+        <v>4780023325484</v>
       </c>
       <c r="G360" s="112"/>
       <c r="H360" s="136"/>
@@ -12684,21 +12687,21 @@
     </row>
     <row r="361" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A361" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B361" s="69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C361" s="2">
         <v>48</v>
       </c>
       <c r="D361" s="8">
-        <f t="shared" ref="D361:D362" si="17">E361*C361</f>
+        <f>E361*C361</f>
         <v>0</v>
       </c>
       <c r="E361" s="39"/>
       <c r="F361" s="207">
-        <v>4780023325453</v>
+        <v>4780023325446</v>
       </c>
       <c r="G361" s="112"/>
       <c r="H361" s="136"/>
@@ -12708,21 +12711,21 @@
     </row>
     <row r="362" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A362" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B362" s="69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C362" s="2">
         <v>48</v>
       </c>
       <c r="D362" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="D362:D363" si="17">E362*C362</f>
         <v>0</v>
       </c>
       <c r="E362" s="39"/>
       <c r="F362" s="207">
-        <v>4780023325439</v>
+        <v>4780023325453</v>
       </c>
       <c r="G362" s="112"/>
       <c r="H362" s="136"/>
@@ -12731,87 +12734,87 @@
       </c>
     </row>
     <row r="363" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A363" s="160"/>
-      <c r="B363" s="161"/>
-      <c r="C363" s="161"/>
-      <c r="D363" s="182"/>
-      <c r="E363" s="182"/>
-      <c r="F363" s="124"/>
+      <c r="A363" s="2">
+        <v>7</v>
+      </c>
+      <c r="B363" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C363" s="2">
+        <v>48</v>
+      </c>
+      <c r="D363" s="8">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="E363" s="39"/>
+      <c r="F363" s="207">
+        <v>4780023325439</v>
+      </c>
       <c r="G363" s="112"/>
       <c r="H363" s="136"/>
-      <c r="I363" s="148" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A364" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B364" s="106" t="s">
-        <v>217</v>
-      </c>
-      <c r="C364" s="117"/>
-      <c r="D364" s="117">
-        <f>SUM(D365:D371)</f>
-        <v>0</v>
-      </c>
-      <c r="E364" s="126">
-        <f>SUM(E365:E371)</f>
-        <v>0</v>
-      </c>
-      <c r="F364" s="123"/>
-      <c r="G364" s="139">
-        <v>0.4</v>
-      </c>
-      <c r="H364" s="136">
-        <f>G364*D364</f>
-        <v>0</v>
-      </c>
+      <c r="I363" s="144">
+        <v>3401110001</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A364" s="160"/>
+      <c r="B364" s="161"/>
+      <c r="C364" s="161"/>
+      <c r="D364" s="182"/>
+      <c r="E364" s="182"/>
+      <c r="F364" s="124"/>
+      <c r="G364" s="112"/>
+      <c r="H364" s="136"/>
       <c r="I364" s="148" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A365" s="2">
-        <v>1</v>
-      </c>
-      <c r="B365" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C365" s="2">
-        <v>48</v>
-      </c>
-      <c r="D365" s="8">
-        <f t="shared" ref="D365:D370" si="18">E365*C365</f>
-        <v>0</v>
-      </c>
-      <c r="E365" s="39"/>
-      <c r="F365" s="207">
-        <v>4780023325101</v>
-      </c>
-      <c r="G365" s="112"/>
-      <c r="H365" s="136"/>
-      <c r="I365" s="144">
-        <v>3401110001</v>
+    <row r="365" spans="1:9" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A365" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B365" s="106" t="s">
+        <v>217</v>
+      </c>
+      <c r="C365" s="117"/>
+      <c r="D365" s="117">
+        <f>SUM(D366:D372)</f>
+        <v>0</v>
+      </c>
+      <c r="E365" s="126">
+        <f>SUM(E366:E372)</f>
+        <v>0</v>
+      </c>
+      <c r="F365" s="123"/>
+      <c r="G365" s="139">
+        <v>0.4</v>
+      </c>
+      <c r="H365" s="136">
+        <f>G365*D365</f>
+        <v>0</v>
+      </c>
+      <c r="I365" s="148" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="366" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A366" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C366" s="2">
         <v>48</v>
       </c>
       <c r="D366" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="D366:D371" si="18">E366*C366</f>
         <v>0</v>
       </c>
       <c r="E366" s="39"/>
       <c r="F366" s="207">
-        <v>4780023325088</v>
+        <v>4780023325101</v>
       </c>
       <c r="G366" s="112"/>
       <c r="H366" s="136"/>
@@ -12821,10 +12824,10 @@
     </row>
     <row r="367" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A367" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C367" s="2">
         <v>48</v>
@@ -12835,7 +12838,7 @@
       </c>
       <c r="E367" s="39"/>
       <c r="F367" s="207">
-        <v>4780023325118</v>
+        <v>4780023325088</v>
       </c>
       <c r="G367" s="112"/>
       <c r="H367" s="136"/>
@@ -12845,10 +12848,10 @@
     </row>
     <row r="368" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A368" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C368" s="2">
         <v>48</v>
@@ -12859,7 +12862,7 @@
       </c>
       <c r="E368" s="39"/>
       <c r="F368" s="207">
-        <v>4780023325149</v>
+        <v>4780023325118</v>
       </c>
       <c r="G368" s="112"/>
       <c r="H368" s="136"/>
@@ -12869,10 +12872,10 @@
     </row>
     <row r="369" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A369" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C369" s="2">
         <v>48</v>
@@ -12883,7 +12886,7 @@
       </c>
       <c r="E369" s="39"/>
       <c r="F369" s="207">
-        <v>4780023325095</v>
+        <v>4780023325149</v>
       </c>
       <c r="G369" s="112"/>
       <c r="H369" s="136"/>
@@ -12893,10 +12896,10 @@
     </row>
     <row r="370" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A370" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C370" s="2">
         <v>48</v>
@@ -12907,7 +12910,7 @@
       </c>
       <c r="E370" s="39"/>
       <c r="F370" s="207">
-        <v>4780023325132</v>
+        <v>4780023325095</v>
       </c>
       <c r="G370" s="112"/>
       <c r="H370" s="136"/>
@@ -12917,21 +12920,21 @@
     </row>
     <row r="371" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A371" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C371" s="2">
         <v>48</v>
       </c>
       <c r="D371" s="8">
-        <f>E371*C371</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="E371" s="39"/>
       <c r="F371" s="207">
-        <v>4780023325125</v>
+        <v>4780023325132</v>
       </c>
       <c r="G371" s="112"/>
       <c r="H371" s="136"/>
@@ -12940,87 +12943,87 @@
       </c>
     </row>
     <row r="372" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A372" s="160"/>
-      <c r="B372" s="161"/>
-      <c r="C372" s="161"/>
-      <c r="D372" s="182"/>
-      <c r="E372" s="182"/>
-      <c r="F372" s="124"/>
+      <c r="A372" s="2">
+        <v>7</v>
+      </c>
+      <c r="B372" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C372" s="2">
+        <v>48</v>
+      </c>
+      <c r="D372" s="8">
+        <f>E372*C372</f>
+        <v>0</v>
+      </c>
+      <c r="E372" s="39"/>
+      <c r="F372" s="207">
+        <v>4780023325125</v>
+      </c>
       <c r="G372" s="112"/>
       <c r="H372" s="136"/>
-      <c r="I372" s="148" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="373" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A373" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B373" s="106" t="s">
-        <v>307</v>
-      </c>
-      <c r="C373" s="117"/>
-      <c r="D373" s="117">
-        <f>SUM(D374:D378)</f>
-        <v>0</v>
-      </c>
-      <c r="E373" s="126">
-        <f>SUM(E374:E378)</f>
-        <v>0</v>
-      </c>
-      <c r="F373" s="123"/>
-      <c r="G373" s="139">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H373" s="136">
-        <f>G373*D373</f>
-        <v>0</v>
-      </c>
+      <c r="I372" s="144">
+        <v>3401110001</v>
+      </c>
+    </row>
+    <row r="373" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A373" s="160"/>
+      <c r="B373" s="161"/>
+      <c r="C373" s="161"/>
+      <c r="D373" s="182"/>
+      <c r="E373" s="182"/>
+      <c r="F373" s="124"/>
+      <c r="G373" s="112"/>
+      <c r="H373" s="136"/>
       <c r="I373" s="148" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="374" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A374" s="2">
-        <v>1</v>
-      </c>
-      <c r="B374" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C374" s="2">
-        <v>45</v>
-      </c>
-      <c r="D374" s="8">
-        <f>E374*C374</f>
-        <v>0</v>
-      </c>
-      <c r="E374" s="39"/>
-      <c r="F374" s="207">
-        <v>4780023328843</v>
-      </c>
-      <c r="G374" s="112"/>
-      <c r="H374" s="136"/>
-      <c r="I374" s="144">
-        <v>3401110001</v>
+    <row r="374" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A374" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B374" s="106" t="s">
+        <v>307</v>
+      </c>
+      <c r="C374" s="117"/>
+      <c r="D374" s="117">
+        <f>SUM(D375:D379)</f>
+        <v>0</v>
+      </c>
+      <c r="E374" s="126">
+        <f>SUM(E375:E379)</f>
+        <v>0</v>
+      </c>
+      <c r="F374" s="123"/>
+      <c r="G374" s="139">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H374" s="136">
+        <f>G374*D374</f>
+        <v>0</v>
+      </c>
+      <c r="I374" s="148" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="375" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A375" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C375" s="2">
         <v>45</v>
       </c>
       <c r="D375" s="8">
-        <f t="shared" ref="D375:D378" si="19">E375*C375</f>
+        <f>E375*C375</f>
         <v>0</v>
       </c>
       <c r="E375" s="39"/>
       <c r="F375" s="207">
-        <v>4780023328829</v>
+        <v>4780023328843</v>
       </c>
       <c r="G375" s="112"/>
       <c r="H375" s="136"/>
@@ -13030,21 +13033,21 @@
     </row>
     <row r="376" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A376" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C376" s="2">
         <v>45</v>
       </c>
       <c r="D376" s="8">
-        <f t="shared" ref="D376:D377" si="20">E376*C376</f>
+        <f t="shared" ref="D376:D379" si="19">E376*C376</f>
         <v>0</v>
       </c>
       <c r="E376" s="39"/>
       <c r="F376" s="207">
-        <v>4780023328836</v>
+        <v>4780023328829</v>
       </c>
       <c r="G376" s="112"/>
       <c r="H376" s="136"/>
@@ -13054,108 +13057,117 @@
     </row>
     <row r="377" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A377" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C377" s="2">
         <v>45</v>
       </c>
       <c r="D377" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D377:D378" si="20">E377*C377</f>
         <v>0</v>
       </c>
       <c r="E377" s="39"/>
       <c r="F377" s="207">
-        <v>4780023329208</v>
+        <v>4780023328836</v>
       </c>
       <c r="G377" s="112"/>
       <c r="H377" s="136"/>
-      <c r="I377" s="144"/>
+      <c r="I377" s="144">
+        <v>3401110001</v>
+      </c>
     </row>
     <row r="378" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A378" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>432</v>
+        <v>312</v>
       </c>
       <c r="C378" s="2">
         <v>45</v>
       </c>
       <c r="D378" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E378" s="39"/>
       <c r="F378" s="207">
-        <v>4780141191145</v>
+        <v>4780023329208</v>
       </c>
       <c r="G378" s="112"/>
       <c r="H378" s="136"/>
-      <c r="I378" s="144">
-        <v>3401110001</v>
-      </c>
+      <c r="I378" s="144"/>
     </row>
     <row r="379" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A379" s="160"/>
-      <c r="B379" s="161"/>
-      <c r="C379" s="161"/>
-      <c r="D379" s="182"/>
-      <c r="E379" s="182"/>
-      <c r="F379" s="124"/>
+      <c r="A379" s="2">
+        <v>5</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C379" s="2">
+        <v>45</v>
+      </c>
+      <c r="D379" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="E379" s="39"/>
+      <c r="F379" s="207">
+        <v>4780141191145</v>
+      </c>
       <c r="G379" s="112"/>
       <c r="H379" s="136"/>
-      <c r="I379" s="148" t="s">
+      <c r="I379" s="144">
+        <v>3401110001</v>
+      </c>
+    </row>
+    <row r="380" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A380" s="160"/>
+      <c r="B380" s="161"/>
+      <c r="C380" s="161"/>
+      <c r="D380" s="182"/>
+      <c r="E380" s="182"/>
+      <c r="F380" s="124"/>
+      <c r="G380" s="112"/>
+      <c r="H380" s="136"/>
+      <c r="I380" s="148" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="380" spans="1:15" ht="32.4" x14ac:dyDescent="0.35">
-      <c r="A380" s="40"/>
-      <c r="B380" s="106" t="s">
+    <row r="381" spans="1:15" ht="32.4" x14ac:dyDescent="0.35">
+      <c r="A381" s="40"/>
+      <c r="B381" s="106" t="s">
         <v>205</v>
       </c>
-      <c r="C380" s="117">
+      <c r="C381" s="117">
         <v>48</v>
       </c>
-      <c r="D380" s="117">
-        <f>E380*C380</f>
-        <v>0</v>
-      </c>
-      <c r="E380" s="117"/>
-      <c r="F380" s="121">
+      <c r="D381" s="117">
+        <f>E381*C381</f>
+        <v>0</v>
+      </c>
+      <c r="E381" s="117"/>
+      <c r="F381" s="121">
         <v>4780023320533</v>
       </c>
-      <c r="G380" s="139">
+      <c r="G381" s="139">
         <v>0.33</v>
       </c>
-      <c r="H380" s="136">
-        <f>G380*D380</f>
-        <v>0</v>
-      </c>
-      <c r="I380" s="144">
+      <c r="H381" s="136">
+        <f>G381*D381</f>
+        <v>0</v>
+      </c>
+      <c r="I381" s="144">
         <v>3401190000</v>
       </c>
     </row>
-    <row r="381" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A381" s="168"/>
-      <c r="B381" s="169"/>
-      <c r="C381" s="188"/>
-      <c r="D381" s="188"/>
-      <c r="E381" s="188"/>
-      <c r="F381" s="171"/>
-      <c r="G381" s="112"/>
-      <c r="H381" s="136"/>
-      <c r="I381" s="150" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="382" spans="1:15" ht="22.8" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A382" s="168"/>
-      <c r="B382" s="189" t="s">
-        <v>221</v>
-      </c>
+      <c r="B382" s="169"/>
       <c r="C382" s="188"/>
       <c r="D382" s="188"/>
       <c r="E382" s="188"/>
@@ -13166,65 +13178,45 @@
         <v>234</v>
       </c>
     </row>
-    <row r="383" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A383" s="104" t="s">
+    <row r="383" spans="1:15" ht="22.8" x14ac:dyDescent="0.35">
+      <c r="A383" s="168"/>
+      <c r="B383" s="189" t="s">
+        <v>221</v>
+      </c>
+      <c r="C383" s="188"/>
+      <c r="D383" s="188"/>
+      <c r="E383" s="188"/>
+      <c r="F383" s="171"/>
+      <c r="G383" s="112"/>
+      <c r="H383" s="136"/>
+      <c r="I383" s="150" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="384" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A384" s="104" t="s">
         <v>157</v>
       </c>
-      <c r="B383" s="104" t="s">
+      <c r="B384" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C383" s="114"/>
-      <c r="D383" s="113">
-        <f>SUM(D384:D385)</f>
-        <v>0</v>
-      </c>
-      <c r="E383" s="113">
-        <f>SUM(E384:E385)</f>
-        <v>0</v>
-      </c>
-      <c r="F383" s="123"/>
-      <c r="G383" s="108"/>
-      <c r="H383" s="137">
-        <f>-SUM(H384:H385)</f>
-        <v>0</v>
-      </c>
-      <c r="I383" s="149" t="s">
+      <c r="C384" s="114"/>
+      <c r="D384" s="113">
+        <f>SUM(D385:D386)</f>
+        <v>0</v>
+      </c>
+      <c r="E384" s="113">
+        <f>SUM(E385:E386)</f>
+        <v>0</v>
+      </c>
+      <c r="F384" s="123"/>
+      <c r="G384" s="108"/>
+      <c r="H384" s="137">
+        <f>-SUM(H385:H386)</f>
+        <v>0</v>
+      </c>
+      <c r="I384" s="149" t="s">
         <v>234</v>
-      </c>
-      <c r="J383" s="98"/>
-      <c r="K383" s="98"/>
-      <c r="L383" s="100"/>
-      <c r="M383" s="100"/>
-      <c r="N383" s="101"/>
-      <c r="O383" s="98"/>
-    </row>
-    <row r="384" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A384" s="45">
-        <v>1</v>
-      </c>
-      <c r="B384" s="164" t="s">
-        <v>237</v>
-      </c>
-      <c r="C384" s="45">
-        <v>20</v>
-      </c>
-      <c r="D384" s="178">
-        <f>C384*E384</f>
-        <v>0</v>
-      </c>
-      <c r="E384" s="44"/>
-      <c r="F384" s="208">
-        <v>4780023321837</v>
-      </c>
-      <c r="G384" s="112">
-        <v>0.93</v>
-      </c>
-      <c r="H384" s="145">
-        <f>G384*D384</f>
-        <v>0</v>
-      </c>
-      <c r="I384" s="146">
-        <v>3305200000</v>
       </c>
       <c r="J384" s="98"/>
       <c r="K384" s="98"/>
@@ -13233,32 +13225,32 @@
       <c r="N384" s="101"/>
       <c r="O384" s="98"/>
     </row>
-    <row r="385" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A385" s="2">
-        <v>2</v>
-      </c>
-      <c r="B385" s="190" t="s">
-        <v>160</v>
-      </c>
-      <c r="C385" s="2">
+    <row r="385" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A385" s="45">
+        <v>1</v>
+      </c>
+      <c r="B385" s="164" t="s">
+        <v>237</v>
+      </c>
+      <c r="C385" s="45">
         <v>20</v>
       </c>
-      <c r="D385" s="8">
+      <c r="D385" s="178">
         <f>C385*E385</f>
         <v>0</v>
       </c>
       <c r="E385" s="44"/>
       <c r="F385" s="208">
-        <v>4780023322568</v>
+        <v>4780023321837</v>
       </c>
       <c r="G385" s="112">
-        <v>0.82</v>
-      </c>
-      <c r="H385" s="137">
+        <v>0.93</v>
+      </c>
+      <c r="H385" s="145">
         <f>G385*D385</f>
         <v>0</v>
       </c>
-      <c r="I385" s="144">
+      <c r="I385" s="146">
         <v>3305200000</v>
       </c>
       <c r="J385" s="98"/>
@@ -13268,17 +13260,33 @@
       <c r="N385" s="101"/>
       <c r="O385" s="98"/>
     </row>
-    <row r="386" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A386" s="2"/>
-      <c r="B386" s="190"/>
-      <c r="C386" s="2"/>
-      <c r="D386" s="8"/>
-      <c r="E386" s="162"/>
-      <c r="F386" s="120"/>
-      <c r="G386" s="112"/>
-      <c r="H386" s="137"/>
-      <c r="I386" s="149" t="s">
-        <v>234</v>
+    <row r="386" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A386" s="2">
+        <v>2</v>
+      </c>
+      <c r="B386" s="190" t="s">
+        <v>160</v>
+      </c>
+      <c r="C386" s="2">
+        <v>20</v>
+      </c>
+      <c r="D386" s="8">
+        <f>C386*E386</f>
+        <v>0</v>
+      </c>
+      <c r="E386" s="44"/>
+      <c r="F386" s="208">
+        <v>4780023322568</v>
+      </c>
+      <c r="G386" s="112">
+        <v>0.82</v>
+      </c>
+      <c r="H386" s="137">
+        <f>G386*D386</f>
+        <v>0</v>
+      </c>
+      <c r="I386" s="144">
+        <v>3305200000</v>
       </c>
       <c r="J386" s="98"/>
       <c r="K386" s="98"/>
@@ -13287,67 +13295,57 @@
       <c r="N386" s="101"/>
       <c r="O386" s="98"/>
     </row>
-    <row r="387" spans="1:15" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A387" s="104" t="s">
+    <row r="387" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A387" s="2"/>
+      <c r="B387" s="190"/>
+      <c r="C387" s="2"/>
+      <c r="D387" s="8"/>
+      <c r="E387" s="162"/>
+      <c r="F387" s="120"/>
+      <c r="G387" s="112"/>
+      <c r="H387" s="137"/>
+      <c r="I387" s="149" t="s">
+        <v>234</v>
+      </c>
+      <c r="J387" s="98"/>
+      <c r="K387" s="98"/>
+      <c r="L387" s="100"/>
+      <c r="M387" s="100"/>
+      <c r="N387" s="101"/>
+      <c r="O387" s="98"/>
+    </row>
+    <row r="388" spans="1:15" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A388" s="104" t="s">
         <v>157</v>
       </c>
-      <c r="B387" s="191" t="s">
+      <c r="B388" s="191" t="s">
         <v>179</v>
       </c>
-      <c r="C387" s="113"/>
-      <c r="D387" s="113">
-        <f>SUM(D388:D392)</f>
-        <v>0</v>
-      </c>
-      <c r="E387" s="113">
-        <f>SUM(E388:E392)</f>
-        <v>0</v>
-      </c>
-      <c r="F387" s="123"/>
-      <c r="G387" s="139"/>
-      <c r="H387" s="136">
-        <f>SUM(H388:H392)</f>
-        <v>0</v>
-      </c>
-      <c r="I387" s="150" t="s">
+      <c r="C388" s="113"/>
+      <c r="D388" s="113">
+        <f>SUM(D389:D393)</f>
+        <v>0</v>
+      </c>
+      <c r="E388" s="113">
+        <f>SUM(E389:E393)</f>
+        <v>0</v>
+      </c>
+      <c r="F388" s="123"/>
+      <c r="G388" s="139"/>
+      <c r="H388" s="136">
+        <f>SUM(H389:H393)</f>
+        <v>0</v>
+      </c>
+      <c r="I388" s="150" t="s">
         <v>234</v>
-      </c>
-    </row>
-    <row r="388" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A388" s="2">
-        <v>1</v>
-      </c>
-      <c r="B388" s="102" t="s">
-        <v>62</v>
-      </c>
-      <c r="C388" s="62">
-        <v>12</v>
-      </c>
-      <c r="D388" s="8">
-        <f>E388*C388</f>
-        <v>0</v>
-      </c>
-      <c r="E388" s="39"/>
-      <c r="F388" s="208">
-        <v>4780023327600</v>
-      </c>
-      <c r="G388" s="112">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="H388" s="136">
-        <f>G388*D388</f>
-        <v>0</v>
-      </c>
-      <c r="I388" s="144">
-        <v>3402209000</v>
       </c>
     </row>
     <row r="389" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A389" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B389" s="102" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C389" s="62">
         <v>12</v>
@@ -13358,7 +13356,7 @@
       </c>
       <c r="E389" s="39"/>
       <c r="F389" s="208">
-        <v>4780023327594</v>
+        <v>4780023327600</v>
       </c>
       <c r="G389" s="112">
         <v>0.56999999999999995</v>
@@ -13373,10 +13371,10 @@
     </row>
     <row r="390" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A390" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B390" s="102" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C390" s="62">
         <v>12</v>
@@ -13387,10 +13385,10 @@
       </c>
       <c r="E390" s="39"/>
       <c r="F390" s="208">
-        <v>4780023327686</v>
+        <v>4780023327594</v>
       </c>
       <c r="G390" s="112">
-        <v>0.75</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="H390" s="136">
         <f>G390*D390</f>
@@ -13402,10 +13400,10 @@
     </row>
     <row r="391" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A391" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B391" s="102" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C391" s="62">
         <v>12</v>
@@ -13416,10 +13414,10 @@
       </c>
       <c r="E391" s="39"/>
       <c r="F391" s="208">
-        <v>4780023327679</v>
+        <v>4780023327686</v>
       </c>
       <c r="G391" s="112">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
       <c r="H391" s="136">
         <f>G391*D391</f>
@@ -13429,12 +13427,12 @@
         <v>3402209000</v>
       </c>
     </row>
-    <row r="392" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A392" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B392" s="102" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C392" s="62">
         <v>12</v>
@@ -13445,7 +13443,7 @@
       </c>
       <c r="E392" s="39"/>
       <c r="F392" s="208">
-        <v>4780023327662</v>
+        <v>4780023327679</v>
       </c>
       <c r="G392" s="112">
         <v>0.97</v>
@@ -13458,72 +13456,74 @@
         <v>3402209000</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="I393" s="150" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="394" spans="1:15" ht="40.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A394" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="B394" s="191" t="s">
-        <v>329</v>
-      </c>
-      <c r="C394" s="113"/>
-      <c r="D394" s="113">
-        <f>SUM(D395:D399)</f>
-        <v>0</v>
-      </c>
-      <c r="E394" s="113">
-        <f>SUM(E395:E399)</f>
-        <v>0</v>
-      </c>
-      <c r="F394" s="123"/>
-      <c r="G394" s="139">
-        <v>2.4</v>
-      </c>
-      <c r="H394" s="136">
-        <f>SUM(H395:H399)</f>
-        <v>0</v>
-      </c>
+    <row r="393" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A393" s="2">
+        <v>5</v>
+      </c>
+      <c r="B393" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="C393" s="62">
+        <v>12</v>
+      </c>
+      <c r="D393" s="8">
+        <f>E393*C393</f>
+        <v>0</v>
+      </c>
+      <c r="E393" s="39"/>
+      <c r="F393" s="208">
+        <v>4780023327662</v>
+      </c>
+      <c r="G393" s="112">
+        <v>0.97</v>
+      </c>
+      <c r="H393" s="136">
+        <f>G393*D393</f>
+        <v>0</v>
+      </c>
+      <c r="I393" s="144">
+        <v>3402209000</v>
+      </c>
+    </row>
+    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I394" s="150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="395" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A395" s="2">
-        <v>1</v>
-      </c>
-      <c r="B395" s="102" t="s">
-        <v>330</v>
-      </c>
-      <c r="C395" s="62">
-        <v>4</v>
-      </c>
-      <c r="D395" s="8">
-        <f>E395*C395</f>
-        <v>0</v>
-      </c>
-      <c r="E395" s="39"/>
-      <c r="F395" s="208">
-        <v>4780141190537</v>
-      </c>
-      <c r="G395" s="112"/>
+    <row r="395" spans="1:15" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A395" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="B395" s="191" t="s">
+        <v>329</v>
+      </c>
+      <c r="C395" s="113"/>
+      <c r="D395" s="113">
+        <f>SUM(D396:D400)</f>
+        <v>0</v>
+      </c>
+      <c r="E395" s="113">
+        <f>SUM(E396:E400)</f>
+        <v>0</v>
+      </c>
+      <c r="F395" s="123"/>
+      <c r="G395" s="139">
+        <v>2.4</v>
+      </c>
       <c r="H395" s="136">
-        <f>G395*D395</f>
-        <v>0</v>
-      </c>
-      <c r="I395" s="144">
-        <v>3402209000</v>
+        <f>SUM(H396:H400)</f>
+        <v>0</v>
+      </c>
+      <c r="I395" s="150" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="396" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A396" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B396" s="102" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C396" s="62">
         <v>4</v>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="E396" s="39"/>
       <c r="F396" s="208">
-        <v>4780141190551</v>
+        <v>4780141190537</v>
       </c>
       <c r="G396" s="112"/>
       <c r="H396" s="136">
@@ -13547,10 +13547,10 @@
     </row>
     <row r="397" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A397" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B397" s="102" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C397" s="62">
         <v>4</v>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="E397" s="39"/>
       <c r="F397" s="208">
-        <v>4780141190575</v>
+        <v>4780141190551</v>
       </c>
       <c r="G397" s="112"/>
       <c r="H397" s="136">
@@ -13572,97 +13572,124 @@
         <v>3402209000</v>
       </c>
     </row>
-    <row r="399" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="B399" s="125" t="s">
-        <v>333</v>
-      </c>
-      <c r="C399" s="10"/>
-      <c r="D399" s="12"/>
-      <c r="E399" s="12"/>
-      <c r="F399" s="4">
-        <f>E387+E383+E380+E364+E355+E346+E344+E325+E320+E316+E304+E257+E249+E243+E233+E211+E203+E194+E190+E153+E151+E141+E135+E128+E121+E116+E111+E79+E5+E373+E280+E273+E268+E261+E188+E157+E145+E251+E394+E197+E332+E161+E299+E294+E228+E223+E217+E183+E177+E171+E166</f>
-        <v>0</v>
-      </c>
-      <c r="G399" s="142"/>
+    <row r="398" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A398" s="2">
+        <v>3</v>
+      </c>
+      <c r="B398" s="102" t="s">
+        <v>332</v>
+      </c>
+      <c r="C398" s="62">
+        <v>4</v>
+      </c>
+      <c r="D398" s="8">
+        <f>E398*C398</f>
+        <v>0</v>
+      </c>
+      <c r="E398" s="39"/>
+      <c r="F398" s="208">
+        <v>4780141190575</v>
+      </c>
+      <c r="G398" s="112"/>
+      <c r="H398" s="136">
+        <f>G398*D398</f>
+        <v>0</v>
+      </c>
+      <c r="I398" s="144">
+        <v>3402209000</v>
+      </c>
     </row>
     <row r="400" spans="1:15" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B400" s="125" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C400" s="10"/>
       <c r="D400" s="12"/>
       <c r="E400" s="12"/>
       <c r="F400" s="4">
-        <f>D387+D383+D380+D364+D355+D346+D344+D325+D320+D316+D304+D299+D294+D257+D249+D243+D233+D211+D203+D194+D190+D153+D151+D141+D135+D128+D121+D116+D111+D79+D5+D373+D280+D273+D268+D261+D188+D157++D145+D251+D394+D197+D332+D161+D223+D217+D183+D177+D171+D166</f>
+        <f>E388+E384+E381+E365+E356+E347+E345+E326+E321+E317+E305+E258+E250+E244+E233+E211+E203+E194+E190+E153+E151+E141+E135+E128+E121+E116+E111+E79+E5+E374+E281+E274+E269+E262+E188+E157+E145+E252+E395+E197+E333+E161+E300+E295+E228+E223+E217+E183+E177+E171+E166</f>
         <v>0</v>
       </c>
       <c r="G400" s="142"/>
     </row>
     <row r="401" spans="2:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B401" s="125" t="s">
-        <v>224</v>
+        <v>334</v>
       </c>
       <c r="C401" s="10"/>
       <c r="D401" s="12"/>
       <c r="E401" s="12"/>
-      <c r="F401" s="132">
-        <f>'логист.данные  logistic dim'!K76</f>
+      <c r="F401" s="4">
+        <f>D388+D384+D381+D365+D356+D347+D345+D326+D321+D317+D305+D300+D295+D258+D250+D244+D233+D211+D203+D194+D190+D153+D151+D141+D135+D128+D121+D116+D111+D79+D5+D374+D281+D274+D269+D262+D188+D157++D145+D252+D395+D197+D333+D161+D223+D217+D183+D177+D171+D166</f>
         <v>0</v>
       </c>
       <c r="G401" s="142"/>
     </row>
     <row r="402" spans="2:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B402" s="125" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C402" s="10"/>
       <c r="D402" s="12"/>
       <c r="E402" s="12"/>
       <c r="F402" s="132">
-        <f>'логист.данные  logistic dim'!L76</f>
+        <f>'логист.данные  logistic dim'!K76</f>
         <v>0</v>
       </c>
       <c r="G402" s="142"/>
     </row>
     <row r="403" spans="2:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B403" s="125" t="s">
-        <v>11</v>
+        <v>225</v>
       </c>
       <c r="C403" s="10"/>
       <c r="D403" s="12"/>
       <c r="E403" s="12"/>
-      <c r="F403" s="63">
-        <f>'логист.данные  logistic dim'!M76</f>
+      <c r="F403" s="132">
+        <f>'логист.данные  logistic dim'!L76</f>
         <v>0</v>
       </c>
       <c r="G403" s="142"/>
     </row>
     <row r="404" spans="2:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B404" s="125" t="s">
-        <v>207</v>
+        <v>11</v>
       </c>
       <c r="C404" s="10"/>
       <c r="D404" s="12"/>
       <c r="E404" s="12"/>
       <c r="F404" s="63">
-        <f>H380+H364+H355+H346+H344+H387+H304+H257+H203+H141+H135+H153+H190+H151+H294+H299+H243+H233+H128+H211+H320+H316+H325+H194+H121+H383+H116+H111+H79+H5+H249+H373+H280+H273+H268+H261+H188++H157+H145+H394+H332+H251+H197+H161+H228+H223+H217+H183+H177+H171+H166</f>
+        <f>'логист.данные  logistic dim'!M76</f>
         <v>0</v>
       </c>
       <c r="G404" s="142"/>
     </row>
-    <row r="405" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:7" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="B405" s="125" t="s">
+        <v>207</v>
+      </c>
       <c r="C405" s="10"/>
       <c r="D405" s="12"/>
       <c r="E405" s="12"/>
-      <c r="F405" s="48"/>
+      <c r="F405" s="63">
+        <f>H381+H365+H356+H347+H345+H388+H305+H258+H203+H141+H135+H153+H190+H151+H295+H300+H244+H233+H128+H211+H321+H317+H326+H194+H121+H384+H116+H111+H79+H5+H250+H374+H281+H274+H269+H262+H188++H157+H145+H395+H333+H252+H197+H161+H228+H223+H217+H183+H177+H171+H166</f>
+        <v>0</v>
+      </c>
       <c r="G405" s="142"/>
+    </row>
+    <row r="406" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C406" s="10"/>
+      <c r="D406" s="12"/>
+      <c r="E406" s="12"/>
+      <c r="F406" s="48"/>
+      <c r="G406" s="142"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <protectedRanges>
-    <protectedRange password="CE0A" sqref="D1:E1 B1 D319 D136:D139" name="Диапазон1"/>
+    <protectedRange password="CE0A" sqref="D1:E1 B1 D320 D136:D139" name="Диапазон1"/>
   </protectedRanges>
-  <autoFilter ref="A4:U392" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:U393" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:D2"/>
@@ -15108,7 +15135,7 @@
         <v>9.84</v>
       </c>
       <c r="J33" s="84">
-        <f>'заказ-order'!E235</f>
+        <f>'заказ-order'!E236</f>
         <v>0</v>
       </c>
       <c r="K33" s="130">
@@ -15152,7 +15179,7 @@
         <v>3.58</v>
       </c>
       <c r="J34" s="84">
-        <f>'заказ-order'!E236</f>
+        <f>'заказ-order'!E237</f>
         <v>0</v>
       </c>
       <c r="K34" s="130">
@@ -15196,7 +15223,7 @@
         <v>3.04</v>
       </c>
       <c r="J35" s="84">
-        <f>'заказ-order'!E237</f>
+        <f>'заказ-order'!E238</f>
         <v>0</v>
       </c>
       <c r="K35" s="130">
@@ -15240,7 +15267,7 @@
         <v>2.56</v>
       </c>
       <c r="J36" s="84">
-        <f>'заказ-order'!E238</f>
+        <f>'заказ-order'!E239</f>
         <v>0</v>
       </c>
       <c r="K36" s="130">
@@ -15284,7 +15311,7 @@
         <v>6.4</v>
       </c>
       <c r="J37" s="84">
-        <f>'заказ-order'!E239</f>
+        <f>'заказ-order'!E240</f>
         <v>0</v>
       </c>
       <c r="K37" s="130">
@@ -15328,7 +15355,7 @@
         <v>6.4</v>
       </c>
       <c r="J38" s="84">
-        <f>'заказ-order'!E240</f>
+        <f>'заказ-order'!E241</f>
         <v>0</v>
       </c>
       <c r="K38" s="130">
@@ -15372,7 +15399,7 @@
         <v>3.52</v>
       </c>
       <c r="J39" s="84">
-        <f>'заказ-order'!E241</f>
+        <f>'заказ-order'!E242</f>
         <v>0</v>
       </c>
       <c r="K39" s="130">
@@ -15416,7 +15443,7 @@
         <v>7.04</v>
       </c>
       <c r="J40" s="84">
-        <f>'заказ-order'!E244</f>
+        <f>'заказ-order'!E245</f>
         <v>0</v>
       </c>
       <c r="K40" s="130">
@@ -15460,7 +15487,7 @@
         <v>5.46</v>
       </c>
       <c r="J41" s="84">
-        <f>'заказ-order'!E245</f>
+        <f>'заказ-order'!E246</f>
         <v>0</v>
       </c>
       <c r="K41" s="130">
@@ -15504,7 +15531,7 @@
         <v>4.4800000000000004</v>
       </c>
       <c r="J42" s="84">
-        <f>'заказ-order'!E246</f>
+        <f>'заказ-order'!E247</f>
         <v>0</v>
       </c>
       <c r="K42" s="130">
@@ -15548,7 +15575,7 @@
         <v>3.3200000000000003</v>
       </c>
       <c r="J43" s="84">
-        <f>'заказ-order'!E247</f>
+        <f>'заказ-order'!E248</f>
         <v>0</v>
       </c>
       <c r="K43" s="130">
@@ -15592,7 +15619,7 @@
         <v>3.1440000000000001</v>
       </c>
       <c r="J44" s="84">
-        <f>'заказ-order'!E249</f>
+        <f>'заказ-order'!E250</f>
         <v>0</v>
       </c>
       <c r="K44" s="130">
@@ -15636,7 +15663,7 @@
         <v>5.16</v>
       </c>
       <c r="J45" s="84">
-        <f>'заказ-order'!E251</f>
+        <f>'заказ-order'!E252</f>
         <v>0</v>
       </c>
       <c r="K45" s="130">
@@ -15680,7 +15707,7 @@
         <v>3.94</v>
       </c>
       <c r="J46" s="84">
-        <f>'заказ-order'!E257</f>
+        <f>'заказ-order'!E258</f>
         <v>0</v>
       </c>
       <c r="K46" s="130">
@@ -15724,7 +15751,7 @@
         <v>3.57</v>
       </c>
       <c r="J47" s="84">
-        <f>'заказ-order'!E252</f>
+        <f>'заказ-order'!E253</f>
         <v>0</v>
       </c>
       <c r="K47" s="130">
@@ -15768,7 +15795,7 @@
         <v>3.27</v>
       </c>
       <c r="J48" s="84">
-        <f>'заказ-order'!E254</f>
+        <f>'заказ-order'!E255</f>
         <v>0</v>
       </c>
       <c r="K48" s="130">
@@ -15812,7 +15839,7 @@
         <v>4.9320000000000004</v>
       </c>
       <c r="J49" s="84">
-        <f>'заказ-order'!E260</f>
+        <f>'заказ-order'!E261</f>
         <v>0</v>
       </c>
       <c r="K49" s="130">
@@ -15856,7 +15883,7 @@
         <v>3.64</v>
       </c>
       <c r="J50" s="84">
-        <f>'заказ-order'!E255</f>
+        <f>'заказ-order'!E256</f>
         <v>0</v>
       </c>
       <c r="K50" s="130">
@@ -15900,7 +15927,7 @@
         <v>2.359</v>
       </c>
       <c r="J51" s="84">
-        <f>'заказ-order'!E257</f>
+        <f>'заказ-order'!E258</f>
         <v>0</v>
       </c>
       <c r="K51" s="130">
@@ -15944,7 +15971,7 @@
         <v>2.9039999999999999</v>
       </c>
       <c r="J52" s="84">
-        <f>'заказ-order'!E263</f>
+        <f>'заказ-order'!E264</f>
         <v>0</v>
       </c>
       <c r="K52" s="130">
@@ -15988,7 +16015,7 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="J53" s="84">
-        <f>'заказ-order'!E258</f>
+        <f>'заказ-order'!E259</f>
         <v>0</v>
       </c>
       <c r="K53" s="130">
@@ -16032,7 +16059,7 @@
         <v>6.66</v>
       </c>
       <c r="J54" s="84">
-        <f>'заказ-order'!E280</f>
+        <f>'заказ-order'!E281</f>
         <v>0</v>
       </c>
       <c r="K54" s="130">
@@ -16076,7 +16103,7 @@
         <v>2.2080000000000002</v>
       </c>
       <c r="J55" s="84">
-        <f>'заказ-order'!E266</f>
+        <f>'заказ-order'!E267</f>
         <v>0</v>
       </c>
       <c r="K55" s="130">
@@ -16120,7 +16147,7 @@
         <v>1.536</v>
       </c>
       <c r="J56" s="84">
-        <f>'заказ-order'!E299</f>
+        <f>'заказ-order'!E300</f>
         <v>0</v>
       </c>
       <c r="K56" s="130">
@@ -16164,7 +16191,7 @@
         <v>2.5</v>
       </c>
       <c r="J57" s="84">
-        <f>'заказ-order'!E304</f>
+        <f>'заказ-order'!E305</f>
         <v>0</v>
       </c>
       <c r="K57" s="130">
@@ -16208,7 +16235,7 @@
         <v>3.38</v>
       </c>
       <c r="J58" s="84">
-        <f>'заказ-order'!E316</f>
+        <f>'заказ-order'!E317</f>
         <v>0</v>
       </c>
       <c r="K58" s="130">
@@ -16252,7 +16279,7 @@
         <v>2.92</v>
       </c>
       <c r="J59" s="84">
-        <f>'заказ-order'!E320</f>
+        <f>'заказ-order'!E321</f>
         <v>0</v>
       </c>
       <c r="K59" s="130">
@@ -16296,7 +16323,7 @@
         <v>7.9</v>
       </c>
       <c r="J60" s="84">
-        <f>'заказ-order'!E325</f>
+        <f>'заказ-order'!E326</f>
         <v>0</v>
       </c>
       <c r="K60" s="130">
@@ -16340,7 +16367,7 @@
         <v>7.2560000000000002</v>
       </c>
       <c r="J61" s="84">
-        <f>'заказ-order'!E332</f>
+        <f>'заказ-order'!E333</f>
         <v>0</v>
       </c>
       <c r="K61" s="130">
@@ -16384,7 +16411,7 @@
         <v>6.76</v>
       </c>
       <c r="J62" s="84">
-        <f>'заказ-order'!E344</f>
+        <f>'заказ-order'!E345</f>
         <v>0</v>
       </c>
       <c r="K62" s="130">
@@ -16428,7 +16455,7 @@
         <v>6.74</v>
       </c>
       <c r="J63" s="84">
-        <f>'заказ-order'!E346</f>
+        <f>'заказ-order'!E347</f>
         <v>0</v>
       </c>
       <c r="K63" s="130">
@@ -16472,7 +16499,7 @@
         <v>6.72</v>
       </c>
       <c r="J64" s="84">
-        <f>'заказ-order'!E355</f>
+        <f>'заказ-order'!E356</f>
         <v>0</v>
       </c>
       <c r="K64" s="130">
@@ -16516,7 +16543,7 @@
         <v>8.16</v>
       </c>
       <c r="J65" s="84">
-        <f>'заказ-order'!E364</f>
+        <f>'заказ-order'!E365</f>
         <v>0</v>
       </c>
       <c r="K65" s="130">
@@ -16560,7 +16587,7 @@
         <v>6.38</v>
       </c>
       <c r="J66" s="84">
-        <f>'заказ-order'!E373</f>
+        <f>'заказ-order'!E374</f>
         <v>0</v>
       </c>
       <c r="K66" s="130">
@@ -16604,7 +16631,7 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="J67" s="84">
-        <f>'заказ-order'!E380</f>
+        <f>'заказ-order'!E381</f>
         <v>0</v>
       </c>
       <c r="K67" s="130">
@@ -16648,7 +16675,7 @@
         <v>5.53</v>
       </c>
       <c r="J68" s="84">
-        <f>'заказ-order'!E384</f>
+        <f>'заказ-order'!E385</f>
         <v>0</v>
       </c>
       <c r="K68" s="130">
@@ -16692,7 +16719,7 @@
         <v>5.38</v>
       </c>
       <c r="J69" s="84">
-        <f>'заказ-order'!E385</f>
+        <f>'заказ-order'!E386</f>
         <v>0</v>
       </c>
       <c r="K69" s="130">
@@ -16736,7 +16763,7 @@
         <v>6.44</v>
       </c>
       <c r="J70" s="84">
-        <f>'заказ-order'!E388</f>
+        <f>'заказ-order'!E389</f>
         <v>0</v>
       </c>
       <c r="K70" s="130">
@@ -16780,7 +16807,7 @@
         <v>6.44</v>
       </c>
       <c r="J71" s="84">
-        <f>'заказ-order'!E389</f>
+        <f>'заказ-order'!E390</f>
         <v>0</v>
       </c>
       <c r="K71" s="130">
@@ -16824,7 +16851,7 @@
         <v>6.84</v>
       </c>
       <c r="J72" s="84">
-        <f>'заказ-order'!E390</f>
+        <f>'заказ-order'!E391</f>
         <v>0</v>
       </c>
       <c r="K72" s="130">
@@ -16868,7 +16895,7 @@
         <v>6.84</v>
       </c>
       <c r="J73" s="84">
-        <f>'заказ-order'!E391</f>
+        <f>'заказ-order'!E392</f>
         <v>0</v>
       </c>
       <c r="K73" s="130">
@@ -16912,7 +16939,7 @@
         <v>6.84</v>
       </c>
       <c r="J74" s="84">
-        <f>'заказ-order'!E391</f>
+        <f>'заказ-order'!E392</f>
         <v>0</v>
       </c>
       <c r="K74" s="130">
@@ -16956,7 +16983,7 @@
         <v>6.42</v>
       </c>
       <c r="J75" s="84">
-        <f>'заказ-order'!E392</f>
+        <f>'заказ-order'!E393</f>
         <v>0</v>
       </c>
       <c r="K75" s="130">
@@ -17266,7 +17293,7 @@
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="60" t="str">
-        <f>+'заказ-order'!B304</f>
+        <f>+'заказ-order'!B305</f>
         <v xml:space="preserve">Кремы «Éclair», в тубах по 44 мл / Сreams «Éclair» in tubes </v>
       </c>
       <c r="D7" s="27"/>
@@ -17386,7 +17413,7 @@
       </c>
       <c r="B13" s="26"/>
       <c r="C13" s="61" t="str">
-        <f>+'заказ-order'!B257</f>
+        <f>+'заказ-order'!B258</f>
         <v xml:space="preserve"> Мицеллярная вода "ELETT" «Éclair», 200 мл /                                                     Micellar water "ELETT" «Éclair», 200 ml.</v>
       </c>
       <c r="D13" s="27"/>
@@ -17466,7 +17493,7 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="61" t="str">
-        <f>+'заказ-order'!B302</f>
+        <f>+'заказ-order'!B303</f>
         <v>Крем после бритья BRIO for men мягкая и чистая кожа "С АКТИВИРОВАННЫМ УГЛЕМ" / After shave cream BRIO for men «Éclair» 50 ml in tubes</v>
       </c>
       <c r="D17" s="27"/>
@@ -17570,7 +17597,7 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="60" t="str">
-        <f>+'заказ-order'!B235</f>
+        <f>+'заказ-order'!B236</f>
         <v xml:space="preserve">Бальзам для волос 500 мл / Hair balm 500 ml </v>
       </c>
       <c r="D22" s="27"/>
@@ -17590,7 +17617,7 @@
       </c>
       <c r="B23" s="26"/>
       <c r="C23" s="60" t="str">
-        <f>+'заказ-order'!B237</f>
+        <f>+'заказ-order'!B238</f>
         <v>Скраб для лица, в тубах по 150 мл / Face scrub 150 ml in tubes</v>
       </c>
       <c r="D23" s="27"/>
@@ -17610,7 +17637,7 @@
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="60" t="str">
-        <f>+'заказ-order'!B238</f>
+        <f>+'заказ-order'!B239</f>
         <v>Крем для депиляции в тубах по 100 мл / Depilatory cream 100 ml in tubes</v>
       </c>
       <c r="D24" s="41"/>
@@ -17630,7 +17657,7 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="60" t="str">
-        <f>+'заказ-order'!B239</f>
+        <f>+'заказ-order'!B240</f>
         <v>Крем для лица в баночках по 150 мл / Face cream 150 ml in jars</v>
       </c>
       <c r="D25" s="41"/>
@@ -17650,7 +17677,7 @@
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="60" t="str">
-        <f>+'заказ-order'!B240</f>
+        <f>+'заказ-order'!B241</f>
         <v>Крем для рук в баночках  по 150 мл / Hand cream 150 ml in jars</v>
       </c>
       <c r="D26" s="41"/>
@@ -17670,7 +17697,7 @@
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="60" t="str">
-        <f>+'заказ-order'!B241</f>
+        <f>+'заказ-order'!B242</f>
         <v>Крем для ног в баночках 75 мл / Foot cream 75 ml in jars</v>
       </c>
       <c r="D27" s="41"/>
@@ -17790,7 +17817,7 @@
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="60" t="str">
-        <f>+'заказ-order'!B325</f>
+        <f>+'заказ-order'!B326</f>
         <v xml:space="preserve">Антибактериальное жидкое мыло «Éclair» 500 мл                                                                                  Antibacterial Liquid soap «Éclair» </v>
       </c>
       <c r="D33" s="41"/>
@@ -17994,7 +18021,7 @@
       </c>
       <c r="B43" s="26"/>
       <c r="C43" s="60" t="str">
-        <f>+'заказ-order'!B316</f>
+        <f>+'заказ-order'!B317</f>
         <v>Крем - депилятор «Éclair», в тубах по 125 мл /                                                         Cream - depilatory «Éclair», in tubes</v>
       </c>
       <c r="D43" s="41"/>
@@ -18014,7 +18041,7 @@
       </c>
       <c r="B44" s="26"/>
       <c r="C44" s="60" t="str">
-        <f>+'заказ-order'!B320</f>
+        <f>+'заказ-order'!B321</f>
         <v>Крем - депилятор «Éclair», в тубах по 75 мл /                                                      Cream - depilatory «Éclair», in tubes</v>
       </c>
       <c r="D44" s="27"/>
@@ -18094,7 +18121,7 @@
       </c>
       <c r="B48" s="26"/>
       <c r="C48" s="60" t="str">
-        <f>+'заказ-order'!B384</f>
+        <f>+'заказ-order'!B385</f>
         <v>Средство химической завивки для волос "Extra LOCK ON" «Éclair» (средство -  полимерный флакон 100мл, фиксирующая эмульсия -  полимерный флакон 100мл, губка и косынка) / Curling Perm "Extra LOCK ON" «Éclair» (means - polymer bottle 100ml, fixing emulsion - polymer bottle 100ml, sponge ans scarf)</v>
       </c>
       <c r="D48" s="27"/>
@@ -18114,7 +18141,7 @@
       </c>
       <c r="B49" s="26"/>
       <c r="C49" s="60" t="str">
-        <f>+'заказ-order'!B385</f>
+        <f>+'заказ-order'!B386</f>
         <v xml:space="preserve">Средство для химимической завивки «Éclair» "Extra LOCK ON", 240 мл  /                   Curling Perm «Éclair» "Extra LOCK ON", 240 ml </v>
       </c>
       <c r="D49" s="27"/>
@@ -18174,7 +18201,7 @@
       </c>
       <c r="B52" s="26"/>
       <c r="C52" s="61" t="str">
-        <f>+'заказ-order'!B344</f>
+        <f>+'заказ-order'!B345</f>
         <v>Туалетные мыла «Éclair»  70 г  / Toilet soaps «Éclair»</v>
       </c>
       <c r="D52" s="27"/>
@@ -18194,7 +18221,7 @@
       </c>
       <c r="B53" s="26"/>
       <c r="C53" s="61" t="str">
-        <f>+'заказ-order'!B346</f>
+        <f>+'заказ-order'!B347</f>
         <v>Туалетные мыла «Éclair»  90 г  / Toilet soaps «Éclair»</v>
       </c>
       <c r="D53" s="27"/>
@@ -18214,7 +18241,7 @@
       </c>
       <c r="B54" s="26"/>
       <c r="C54" s="61" t="str">
-        <f>+'заказ-order'!B355</f>
+        <f>+'заказ-order'!B356</f>
         <v>Туалетные мыла «Éclair»  140 г  / Toilet soaps «Éclair»</v>
       </c>
       <c r="D54" s="27"/>
@@ -18234,7 +18261,7 @@
       </c>
       <c r="B55" s="26"/>
       <c r="C55" s="61" t="str">
-        <f>+'заказ-order'!B364</f>
+        <f>+'заказ-order'!B365</f>
         <v>Туалетные мыла «Éclair»  170 г  / Toilet soaps «Éclair»</v>
       </c>
       <c r="D55" s="27"/>
@@ -18254,7 +18281,7 @@
       </c>
       <c r="B56" s="26"/>
       <c r="C56" s="61" t="str">
-        <f>+'заказ-order'!B380</f>
+        <f>+'заказ-order'!B381</f>
         <v>Универсальное хозяйственное мыло «Éclair» "BARG" 175 гр  /                          Universal Laundry soap «Éclair» "BARG"</v>
       </c>
       <c r="D56" s="27"/>
@@ -18394,7 +18421,7 @@
       </c>
       <c r="B63" s="26"/>
       <c r="C63" s="61" t="str">
-        <f>+'заказ-order'!B244</f>
+        <f>+'заказ-order'!B245</f>
         <v>Шампунь для волос "Двойная сила для интенсивного ухода" 400 мл /                         Hair shampoo "Double strength for intensive care" 400 ml</v>
       </c>
       <c r="D63" s="27"/>
@@ -18414,7 +18441,7 @@
       </c>
       <c r="B64" s="26"/>
       <c r="C64" s="61" t="str">
-        <f>+'заказ-order'!B246</f>
+        <f>+'заказ-order'!B247</f>
         <v>Гель для душа "Комфортное очищение для волос и тела" 250 мл /                              Shower gel "Comfortable cleansing for hair and body" 250 ml</v>
       </c>
       <c r="D64" s="27"/>
@@ -18434,7 +18461,7 @@
       </c>
       <c r="B65" s="26"/>
       <c r="C65" s="61" t="str">
-        <f>+'заказ-order'!B245</f>
+        <f>+'заказ-order'!B246</f>
         <v>Бальзам-ополаскиватель для поврежденных и туслых волос 240 мл  /                             Balm -conditioner for damaged and dull hair 240 ml</v>
       </c>
       <c r="D65" s="27"/>
@@ -18454,7 +18481,7 @@
       </c>
       <c r="B66" s="26"/>
       <c r="C66" s="61" t="str">
-        <f>+'заказ-order'!B247</f>
+        <f>+'заказ-order'!B248</f>
         <v xml:space="preserve">Бальзам после бритья "Увлажнение и питание" 140 мл /                                                After shave balm "Moisturizing and nutrition" 140 ml </v>
       </c>
       <c r="D66" s="27"/>
@@ -18474,7 +18501,7 @@
       </c>
       <c r="B67" s="26"/>
       <c r="C67" s="61" t="str">
-        <f>+'заказ-order'!B388</f>
+        <f>+'заказ-order'!B389</f>
         <v>Средство для мытья посуды "Лимон" 500 мл / Dishwashing liquid "Lemon" 500 ml</v>
       </c>
       <c r="D67" s="27"/>
@@ -18494,7 +18521,7 @@
       </c>
       <c r="B68" s="26"/>
       <c r="C68" s="61" t="str">
-        <f>+'заказ-order'!B389</f>
+        <f>+'заказ-order'!B390</f>
         <v>Средство для мытья посуды "Яблоко" 500 мл / Dishwashing liquid "Apple" 500 ml</v>
       </c>
       <c r="D68" s="27"/>
@@ -18514,7 +18541,7 @@
       </c>
       <c r="B69" s="26"/>
       <c r="C69" s="61" t="str">
-        <f>+'заказ-order'!B390</f>
+        <f>+'заказ-order'!B391</f>
         <v>Средство для очистки стекол и зеркал 500 мл / Glass and mirror cleaner 500 ml</v>
       </c>
       <c r="D69" s="27"/>
@@ -18534,7 +18561,7 @@
       </c>
       <c r="B70" s="26"/>
       <c r="C70" s="61" t="str">
-        <f>+'заказ-order'!B391</f>
+        <f>+'заказ-order'!B392</f>
         <v>Универсальное средство для кухни 500 мл / Universal kitchen cleaner 500 ml</v>
       </c>
       <c r="D70" s="27"/>
@@ -18554,7 +18581,7 @@
       </c>
       <c r="B71" s="26"/>
       <c r="C71" s="61" t="str">
-        <f>+'заказ-order'!B392</f>
+        <f>+'заказ-order'!B393</f>
         <v>Средство для удаления жира, нагара и копоти "Анти-жир Чистый казан" 500 мл  / Grease, soot and soot remover "Анти-жир Чистый казан"  500 ml</v>
       </c>
       <c r="D71" s="27"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SmartOrder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9568EC3-4989-41A5-9F46-4106A8ADA892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D802C81-CB81-4956-A8B6-535BCF2DCF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9492,12 +9492,15 @@
       </c>
       <c r="E235" s="39"/>
       <c r="F235" s="208">
-        <v>4780023326993</v>
+        <v>4780141191114</v>
       </c>
       <c r="G235" s="112">
         <v>1.61</v>
       </c>
-      <c r="H235" s="136"/>
+      <c r="H235" s="136">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="I235" s="144"/>
     </row>
     <row r="236" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">

--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr showInkAnnotation="0" codeName="ЭтаКнига" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SmartOrder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46169F1-D949-4FDE-B310-BEF9AEBB73F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3997615-5A2B-4F31-9995-7ABA7253EF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="432">
   <si>
     <t>№ з/п</t>
   </si>
@@ -1327,9 +1327,6 @@
   </si>
   <si>
     <t>Антибактериальное жидкое мыло «Éclair» 830 мл / Antibacterial Liquid soap «Éclair» 830 ml</t>
-  </si>
-  <si>
-    <t>Стойкая крем краска для волос «Éclair» «3D», в саше по 50 мл / Permanent hair color cream «Éclair» «3D», in sachet 50 ml</t>
   </si>
   <si>
     <t>Персик / Peach</t>
@@ -8481,7 +8478,7 @@
         <v>2</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C203" s="2">
         <v>17</v>
@@ -9016,7 +9013,7 @@
         <v>3305900009</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>4</v>
       </c>
@@ -9964,7 +9961,7 @@
       </c>
       <c r="C263" s="104"/>
       <c r="D263" s="113">
-        <f>+E263*C263</f>
+        <f>SUM(D264:D266)</f>
         <v>0</v>
       </c>
       <c r="E263" s="113">
@@ -10000,10 +9997,7 @@
         <v>4780023325699</v>
       </c>
       <c r="G264" s="112"/>
-      <c r="H264" s="136">
-        <f>G264*D264</f>
-        <v>0</v>
-      </c>
+      <c r="H264" s="136"/>
       <c r="I264" s="144">
         <v>3307100000</v>
       </c>
@@ -10025,10 +10019,7 @@
         <v>4780141190957</v>
       </c>
       <c r="G265" s="112"/>
-      <c r="H265" s="136">
-        <f>G265*D265</f>
-        <v>0</v>
-      </c>
+      <c r="H265" s="136"/>
       <c r="I265" s="144">
         <v>3307100000</v>
       </c>
@@ -10050,10 +10041,7 @@
         <v>4780141190940</v>
       </c>
       <c r="G266" s="112"/>
-      <c r="H266" s="136">
-        <f>G266*D266</f>
-        <v>0</v>
-      </c>
+      <c r="H266" s="136"/>
       <c r="I266" s="144">
         <v>3307100000</v>
       </c>
@@ -10076,7 +10064,7 @@
       </c>
       <c r="C268" s="104"/>
       <c r="D268" s="113">
-        <f>+E268*C268</f>
+        <f>SUM(D269:D271)</f>
         <v>0</v>
       </c>
       <c r="E268" s="113">
@@ -10112,10 +10100,7 @@
         <v>4780023322155</v>
       </c>
       <c r="G269" s="112"/>
-      <c r="H269" s="136">
-        <f>G269*D269</f>
-        <v>0</v>
-      </c>
+      <c r="H269" s="136"/>
       <c r="I269" s="144">
         <v>3307100000</v>
       </c>
@@ -10137,10 +10122,7 @@
         <v>4780141190964</v>
       </c>
       <c r="G270" s="112"/>
-      <c r="H270" s="136">
-        <f>G270*D270</f>
-        <v>0</v>
-      </c>
+      <c r="H270" s="136"/>
       <c r="I270" s="144">
         <v>3307100000</v>
       </c>
@@ -10162,10 +10144,7 @@
         <v>4780141190971</v>
       </c>
       <c r="G271" s="112"/>
-      <c r="H271" s="136">
-        <f>G271*D271</f>
-        <v>0</v>
-      </c>
+      <c r="H271" s="136"/>
       <c r="I271" s="144">
         <v>3307100000</v>
       </c>
@@ -12109,7 +12088,7 @@
         <v>5</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C347" s="2">
         <v>45</v>
@@ -12215,7 +12194,7 @@
       <c r="F352" s="123"/>
       <c r="G352" s="108"/>
       <c r="H352" s="137">
-        <f>-SUM(H353:H354)</f>
+        <f>SUM(H353:H354)</f>
         <v>0</v>
       </c>
       <c r="I352" s="149" t="s">
@@ -12502,11 +12481,11 @@
       </c>
       <c r="C363" s="113"/>
       <c r="D363" s="113">
-        <f>SUM(D364:D368)</f>
+        <f>SUM(D364:D366)</f>
         <v>0</v>
       </c>
       <c r="E363" s="113">
-        <f>SUM(E364:E368)</f>
+        <f>SUM(E364:E366)</f>
         <v>0</v>
       </c>
       <c r="F363" s="123"/>
@@ -12514,7 +12493,7 @@
         <v>2.4</v>
       </c>
       <c r="H363" s="136">
-        <f>SUM(H364:H368)</f>
+        <f>D363*G363</f>
         <v>0</v>
       </c>
       <c r="I363" s="150" t="s">
@@ -12540,10 +12519,7 @@
         <v>4780141190537</v>
       </c>
       <c r="G364" s="112"/>
-      <c r="H364" s="136">
-        <f>G364*D364</f>
-        <v>0</v>
-      </c>
+      <c r="H364" s="136"/>
       <c r="I364" s="144">
         <v>3402209000</v>
       </c>
@@ -12567,10 +12543,7 @@
         <v>4780141190551</v>
       </c>
       <c r="G365" s="112"/>
-      <c r="H365" s="136">
-        <f>G365*D365</f>
-        <v>0</v>
-      </c>
+      <c r="H365" s="136"/>
       <c r="I365" s="144">
         <v>3402209000</v>
       </c>
@@ -12594,10 +12567,7 @@
         <v>4780141190575</v>
       </c>
       <c r="G366" s="112"/>
-      <c r="H366" s="136">
-        <f>G366*D366</f>
-        <v>0</v>
-      </c>
+      <c r="H366" s="136"/>
       <c r="I366" s="144">
         <v>3402209000</v>
       </c>
@@ -12635,9 +12605,9 @@
       <c r="C370" s="10"/>
       <c r="D370" s="12"/>
       <c r="E370" s="12"/>
-      <c r="F370" s="132" t="e">
-        <f>'логист.данные  logistic dim'!K76</f>
-        <v>#REF!</v>
+      <c r="F370" s="132">
+        <f>'логист.данные  logistic dim'!K75</f>
+        <v>0</v>
       </c>
       <c r="G370" s="142"/>
     </row>
@@ -12648,9 +12618,9 @@
       <c r="C371" s="10"/>
       <c r="D371" s="12"/>
       <c r="E371" s="12"/>
-      <c r="F371" s="132" t="e">
-        <f>'логист.данные  logistic dim'!L76</f>
-        <v>#REF!</v>
+      <c r="F371" s="132">
+        <f>'логист.данные  logistic dim'!L75</f>
+        <v>0</v>
       </c>
       <c r="G371" s="142"/>
     </row>
@@ -12661,9 +12631,9 @@
       <c r="C372" s="10"/>
       <c r="D372" s="12"/>
       <c r="E372" s="12"/>
-      <c r="F372" s="63" t="e">
-        <f>'логист.данные  logistic dim'!M76</f>
-        <v>#REF!</v>
+      <c r="F372" s="63">
+        <f>'логист.данные  logistic dim'!M75</f>
+        <v>0</v>
       </c>
       <c r="G372" s="142"/>
     </row>
@@ -12714,7 +12684,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.5546875" style="70" customWidth="1"/>
@@ -12840,7 +12810,7 @@
       </c>
       <c r="B4" s="87"/>
       <c r="C4" s="80" t="s">
-        <v>430</v>
+        <v>180</v>
       </c>
       <c r="D4" s="79">
         <v>0.28999999999999998</v>
@@ -12852,7 +12822,7 @@
         <v>0.17199999999999999</v>
       </c>
       <c r="G4" s="89">
-        <f t="shared" ref="G4" si="0">ROUND(D4*E4*F4,4)</f>
+        <f t="shared" ref="G4:G5" si="0">ROUND(D4*E4*F4,4)</f>
         <v>9.4999999999999998E-3</v>
       </c>
       <c r="H4" s="86">
@@ -12861,338 +12831,338 @@
       <c r="I4" s="86">
         <v>2.448</v>
       </c>
-      <c r="J4" s="84" t="e">
-        <f>'заказ-order'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K4" s="130" t="e">
-        <f t="shared" ref="K4" si="1">H4*J4</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L4" s="130" t="e">
-        <f t="shared" ref="L4" si="2">I4*J4</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M4" s="83" t="e">
-        <f t="shared" ref="M4" si="3">J4*D4*E4*F4</f>
-        <v>#REF!</v>
+      <c r="J4" s="84">
+        <f>'заказ-order'!E47</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="130">
+        <f t="shared" ref="K4:K7" si="1">H4*J4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="130">
+        <f t="shared" ref="L4:L72" si="2">I4*J4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="83">
+        <f t="shared" ref="M4:M7" si="3">J4*D4*E4*F4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="87"/>
       <c r="C5" s="80" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="D5" s="79">
-        <v>0.28999999999999998</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="E5" s="79">
-        <v>0.19</v>
-      </c>
-      <c r="F5" s="79">
-        <v>0.17199999999999999</v>
+        <v>0.11</v>
+      </c>
+      <c r="F5" s="86">
+        <v>0.75</v>
       </c>
       <c r="G5" s="89">
-        <f t="shared" ref="G5:G6" si="4">ROUND(D5*E5*F5,4)</f>
-        <v>9.4999999999999998E-3</v>
+        <f t="shared" si="0"/>
+        <v>1.44E-2</v>
       </c>
       <c r="H5" s="86">
-        <v>2.58</v>
+        <v>1.8</v>
       </c>
       <c r="I5" s="86">
-        <v>2.448</v>
+        <v>1.68</v>
       </c>
       <c r="J5" s="84">
-        <f>'заказ-order'!E47</f>
+        <f>'заказ-order'!E79</f>
         <v>0</v>
       </c>
       <c r="K5" s="130">
-        <f t="shared" ref="K5:K8" si="5">H5*J5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L5" s="130">
-        <f t="shared" ref="L5:L73" si="6">I5*J5</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M5" s="83">
-        <f t="shared" ref="M5:M8" si="7">J5*D5*E5*F5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="87"/>
       <c r="C6" s="80" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="D6" s="79">
-        <v>0.17499999999999999</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="E6" s="79">
-        <v>0.11</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F6" s="86">
-        <v>0.75</v>
+        <v>0.18</v>
       </c>
       <c r="G6" s="89">
-        <f t="shared" si="4"/>
-        <v>1.44E-2</v>
+        <f t="shared" ref="G6:G7" si="4">ROUND(D6*E6*F6,4)</f>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="H6" s="86">
-        <v>1.8</v>
+        <v>3.48</v>
       </c>
       <c r="I6" s="86">
-        <v>1.68</v>
+        <v>3.22</v>
       </c>
       <c r="J6" s="84">
-        <f>'заказ-order'!E79</f>
+        <f>'заказ-order'!E85</f>
         <v>0</v>
       </c>
       <c r="K6" s="130">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L6" s="130">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M6" s="83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="87"/>
       <c r="C7" s="80" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D7" s="79">
-        <v>0.41499999999999998</v>
+        <v>0.33</v>
       </c>
       <c r="E7" s="79">
-        <v>0.28000000000000003</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="F7" s="86">
         <v>0.18</v>
       </c>
       <c r="G7" s="89">
-        <f t="shared" ref="G7:G8" si="8">ROUND(D7*E7*F7,4)</f>
-        <v>2.0899999999999998E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.4E-2</v>
       </c>
       <c r="H7" s="86">
-        <v>3.48</v>
+        <v>2.3159999999999998</v>
       </c>
       <c r="I7" s="86">
-        <v>3.22</v>
+        <v>2.12</v>
       </c>
       <c r="J7" s="84">
-        <f>'заказ-order'!E85</f>
+        <f>'заказ-order'!E86</f>
         <v>0</v>
       </c>
       <c r="K7" s="130">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L7" s="130">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M7" s="83">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="87"/>
       <c r="C8" s="80" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="79">
+        <v>43</v>
+      </c>
+      <c r="D8" s="88">
         <v>0.33</v>
       </c>
-      <c r="E8" s="79">
-        <v>0.23499999999999999</v>
-      </c>
-      <c r="F8" s="86">
-        <v>0.18</v>
+      <c r="E8" s="88">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="F8" s="85">
+        <v>0.255</v>
       </c>
       <c r="G8" s="89">
-        <f t="shared" si="8"/>
-        <v>1.4E-2</v>
-      </c>
-      <c r="H8" s="86">
-        <v>2.3159999999999998</v>
-      </c>
-      <c r="I8" s="86">
-        <v>2.12</v>
+        <f t="shared" ref="G8:G71" si="5">ROUND(D8*E8*F8,4)</f>
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="H8" s="85">
+        <v>8.02</v>
+      </c>
+      <c r="I8" s="85">
+        <v>7.84</v>
       </c>
       <c r="J8" s="84">
-        <f>'заказ-order'!E86</f>
+        <f>'заказ-order'!E89</f>
         <v>0</v>
       </c>
       <c r="K8" s="130">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K8:K58" si="6">H8*J8</f>
         <v>0</v>
       </c>
       <c r="L8" s="130">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L8:L63" si="7">I8*J8</f>
         <v>0</v>
       </c>
       <c r="M8" s="83">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="M8:M67" si="8">J8*D8*E8*F8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="87"/>
       <c r="C9" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="88">
-        <v>0.33</v>
-      </c>
-      <c r="E9" s="88">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="F9" s="85">
-        <v>0.255</v>
+        <v>191</v>
+      </c>
+      <c r="D9" s="79">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="E9" s="79">
+        <v>0.26</v>
+      </c>
+      <c r="F9" s="86">
+        <v>0.216</v>
       </c>
       <c r="G9" s="89">
-        <f t="shared" ref="G9:G72" si="9">ROUND(D9*E9*F9,4)</f>
-        <v>1.3899999999999999E-2</v>
-      </c>
-      <c r="H9" s="85">
-        <v>8.02</v>
-      </c>
-      <c r="I9" s="85">
-        <v>7.84</v>
+        <f t="shared" si="5"/>
+        <v>1.49E-2</v>
+      </c>
+      <c r="H9" s="86">
+        <v>7.78</v>
+      </c>
+      <c r="I9" s="86">
+        <v>7.56</v>
       </c>
       <c r="J9" s="84">
-        <f>'заказ-order'!E89</f>
+        <f>'заказ-order'!E96</f>
         <v>0</v>
       </c>
       <c r="K9" s="130">
-        <f t="shared" ref="K9:K59" si="10">H9*J9</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L9" s="130">
-        <f t="shared" ref="L9:L64" si="11">I9*J9</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M9" s="83">
-        <f t="shared" ref="M9:M68" si="12">J9*D9*E9*F9</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="82">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="87"/>
       <c r="C10" s="80" t="s">
-        <v>191</v>
-      </c>
-      <c r="D10" s="79">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="E10" s="79">
-        <v>0.26</v>
-      </c>
-      <c r="F10" s="86">
-        <v>0.216</v>
+        <v>94</v>
+      </c>
+      <c r="D10" s="88">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="E10" s="88">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="F10" s="85">
+        <v>0.22</v>
       </c>
       <c r="G10" s="89">
-        <f t="shared" si="9"/>
-        <v>1.49E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.37E-2</v>
       </c>
       <c r="H10" s="86">
-        <v>7.78</v>
+        <v>8.14</v>
       </c>
       <c r="I10" s="86">
-        <v>7.56</v>
+        <v>7.96</v>
       </c>
       <c r="J10" s="84">
-        <f>'заказ-order'!E96</f>
+        <f>'заказ-order'!E103</f>
         <v>0</v>
       </c>
       <c r="K10" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L10" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M10" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="82">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="87"/>
       <c r="C11" s="80" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
       <c r="D11" s="88">
-        <v>0.26200000000000001</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="E11" s="88">
-        <v>0.23699999999999999</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="F11" s="85">
-        <v>0.22</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="G11" s="89">
-        <f t="shared" si="9"/>
-        <v>1.37E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="H11" s="86">
-        <v>8.14</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="I11" s="86">
-        <v>7.96</v>
+        <v>8.68</v>
       </c>
       <c r="J11" s="84">
-        <f>'заказ-order'!E103</f>
+        <f>'заказ-order'!E109</f>
         <v>0</v>
       </c>
       <c r="K11" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L11" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M11" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12" s="82">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="87"/>
       <c r="C12" s="80" t="s">
-        <v>190</v>
+        <v>285</v>
       </c>
       <c r="D12" s="88">
         <v>0.32400000000000001</v>
@@ -13204,7 +13174,7 @@
         <v>0.29299999999999998</v>
       </c>
       <c r="G12" s="89">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="G12" si="9">ROUND(D12*E12*F12,4)</f>
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="H12" s="86">
@@ -13214,227 +13184,227 @@
         <v>8.68</v>
       </c>
       <c r="J12" s="84">
-        <f>'заказ-order'!E109</f>
+        <f>'заказ-order'!E113</f>
         <v>0</v>
       </c>
       <c r="K12" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K12" si="10">H12*J12</f>
         <v>0</v>
       </c>
       <c r="L12" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="L12" si="11">I12*J12</f>
         <v>0</v>
       </c>
       <c r="M12" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="M12" si="12">J12*D12*E12*F12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="82">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="87"/>
       <c r="C13" s="80" t="s">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="D13" s="88">
-        <v>0.32400000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="E13" s="88">
-        <v>0.16400000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="F13" s="85">
-        <v>0.29299999999999998</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="G13" s="89">
-        <f t="shared" ref="G13" si="13">ROUND(D13*E13*F13,4)</f>
-        <v>1.5599999999999999E-2</v>
-      </c>
-      <c r="H13" s="86">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="I13" s="86">
-        <v>8.68</v>
+        <f t="shared" si="5"/>
+        <v>1.49E-2</v>
+      </c>
+      <c r="H13" s="85">
+        <v>8.16</v>
+      </c>
+      <c r="I13" s="85">
+        <v>7.98</v>
       </c>
       <c r="J13" s="84">
-        <f>'заказ-order'!E113</f>
+        <f>'заказ-order'!E119</f>
         <v>0</v>
       </c>
       <c r="K13" s="130">
-        <f t="shared" ref="K13" si="14">H13*J13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L13" s="130">
-        <f t="shared" ref="L13" si="15">I13*J13</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M13" s="83">
-        <f t="shared" ref="M13" si="16">J13*D13*E13*F13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A14" s="82">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="87"/>
       <c r="C14" s="80" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="88">
-        <v>0.255</v>
-      </c>
-      <c r="E14" s="88">
-        <v>0.24</v>
-      </c>
-      <c r="F14" s="85">
-        <v>0.24299999999999999</v>
+        <v>233</v>
+      </c>
+      <c r="D14" s="79">
+        <v>0.31</v>
+      </c>
+      <c r="E14" s="79">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="F14" s="86">
+        <v>0.193</v>
       </c>
       <c r="G14" s="89">
-        <f t="shared" si="9"/>
-        <v>1.49E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.06E-2</v>
       </c>
       <c r="H14" s="85">
-        <v>8.16</v>
+        <v>5.62</v>
       </c>
       <c r="I14" s="85">
-        <v>7.98</v>
+        <v>5.44</v>
       </c>
       <c r="J14" s="84">
-        <f>'заказ-order'!E119</f>
+        <f>'заказ-order'!E121</f>
         <v>0</v>
       </c>
       <c r="K14" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L14" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M14" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="220" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="82">
-        <v>12</v>
-      </c>
-      <c r="B15" s="87"/>
-      <c r="C15" s="80" t="s">
-        <v>233</v>
-      </c>
-      <c r="D15" s="79">
-        <v>0.31</v>
-      </c>
-      <c r="E15" s="79">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="F15" s="86">
-        <v>0.193</v>
-      </c>
-      <c r="G15" s="89">
-        <f t="shared" si="9"/>
-        <v>1.06E-2</v>
-      </c>
-      <c r="H15" s="85">
-        <v>5.62</v>
-      </c>
-      <c r="I15" s="85">
-        <v>5.44</v>
-      </c>
-      <c r="J15" s="84">
-        <f>'заказ-order'!E121</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="130">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="130">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" s="220" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="211"/>
+      <c r="C15" s="212" t="s">
+        <v>292</v>
+      </c>
+      <c r="D15" s="213">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="E15" s="213">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="F15" s="214">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G15" s="215">
+        <f t="shared" ref="G15" si="13">ROUND(D15*E15*F15,4)</f>
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="H15" s="216">
+        <v>5.34</v>
+      </c>
+      <c r="I15" s="216">
+        <v>5.2</v>
+      </c>
+      <c r="J15" s="217">
+        <f>'заказ-order'!E125</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="218">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="218">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="219">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="82">
-        <v>13</v>
-      </c>
-      <c r="B16" s="211"/>
-      <c r="C16" s="212" t="s">
-        <v>292</v>
-      </c>
-      <c r="D16" s="213">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="E16" s="213">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="F16" s="214">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G16" s="215">
-        <f t="shared" ref="G16" si="17">ROUND(D16*E16*F16,4)</f>
-        <v>9.4000000000000004E-3</v>
-      </c>
-      <c r="H16" s="216">
-        <v>5.34</v>
-      </c>
-      <c r="I16" s="216">
-        <v>5.2</v>
-      </c>
-      <c r="J16" s="217">
-        <f>'заказ-order'!E125</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="218">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="218">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="219">
-        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="87"/>
+      <c r="C16" s="80" t="s">
+        <v>360</v>
+      </c>
+      <c r="D16" s="79">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="E16" s="79">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="F16" s="86">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="G16" s="89">
+        <f t="shared" si="5"/>
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="H16" s="85">
+        <v>8.7880000000000003</v>
+      </c>
+      <c r="I16" s="85">
+        <v>9</v>
+      </c>
+      <c r="J16" s="84">
+        <f>'заказ-order'!E129</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="130">
+        <f t="shared" ref="K16" si="14">H16*J16</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="130">
+        <f t="shared" ref="L16" si="15">I16*J16</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="83">
+        <f t="shared" ref="M16" si="16">J16*D16*E16*F16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="82">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="87"/>
       <c r="C17" s="80" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="D17" s="79">
-        <v>0.32400000000000001</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="E17" s="79">
-        <v>0.16400000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="F17" s="86">
-        <v>0.29299999999999998</v>
+        <v>0.313</v>
       </c>
       <c r="G17" s="89">
-        <f t="shared" si="9"/>
-        <v>1.5599999999999999E-2</v>
+        <f t="shared" ref="G17" si="17">ROUND(D17*E17*F17,4)</f>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H17" s="85">
-        <v>8.7880000000000003</v>
+        <v>9.74</v>
       </c>
       <c r="I17" s="85">
-        <v>9</v>
+        <v>9.5039999999999996</v>
       </c>
       <c r="J17" s="84">
-        <f>'заказ-order'!E129</f>
+        <f>'заказ-order'!E134</f>
         <v>0</v>
       </c>
       <c r="K17" s="130">
@@ -13452,55 +13422,55 @@
     </row>
     <row r="18" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="82">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="87"/>
       <c r="C18" s="80" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="D18" s="79">
-        <v>0.27200000000000002</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="E18" s="79">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F18" s="86">
-        <v>0.313</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="G18" s="89">
-        <f t="shared" ref="G18" si="21">ROUND(D18*E18*F18,4)</f>
-        <v>1.7000000000000001E-2</v>
+        <f t="shared" ref="G18:G19" si="21">ROUND(D18*E18*F18,4)</f>
+        <v>1.55E-2</v>
       </c>
       <c r="H18" s="85">
-        <v>9.74</v>
+        <v>8.23</v>
       </c>
       <c r="I18" s="85">
-        <v>9.5039999999999996</v>
+        <v>8.0739999999999998</v>
       </c>
       <c r="J18" s="84">
-        <f>'заказ-order'!E134</f>
+        <f>'заказ-order'!E139</f>
         <v>0</v>
       </c>
       <c r="K18" s="130">
-        <f t="shared" ref="K18" si="22">H18*J18</f>
+        <f t="shared" ref="K18:K19" si="22">H18*J18</f>
         <v>0</v>
       </c>
       <c r="L18" s="130">
-        <f t="shared" ref="L18" si="23">I18*J18</f>
+        <f t="shared" ref="L18:L19" si="23">I18*J18</f>
         <v>0</v>
       </c>
       <c r="M18" s="83">
-        <f t="shared" ref="M18" si="24">J18*D18*E18*F18</f>
+        <f t="shared" ref="M18:M19" si="24">J18*D18*E18*F18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="82">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" s="87"/>
       <c r="C19" s="80" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D19" s="79">
         <v>0.28699999999999998</v>
@@ -13512,39 +13482,39 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="G19" s="89">
-        <f t="shared" ref="G19:G20" si="25">ROUND(D19*E19*F19,4)</f>
+        <f t="shared" si="21"/>
         <v>1.55E-2</v>
       </c>
       <c r="H19" s="85">
-        <v>8.23</v>
+        <v>8.26</v>
       </c>
       <c r="I19" s="85">
-        <v>8.0739999999999998</v>
+        <v>8.06</v>
       </c>
       <c r="J19" s="84">
-        <f>'заказ-order'!E139</f>
+        <f>'заказ-order'!E145</f>
         <v>0</v>
       </c>
       <c r="K19" s="130">
-        <f t="shared" ref="K19:K20" si="26">H19*J19</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L19" s="130">
-        <f t="shared" ref="L19:L20" si="27">I19*J19</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M19" s="83">
-        <f t="shared" ref="M19:M20" si="28">J19*D19*E19*F19</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A20" s="82">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="87"/>
       <c r="C20" s="80" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D20" s="79">
         <v>0.28699999999999998</v>
@@ -13556,105 +13526,105 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="G20" s="89">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G20" si="25">ROUND(D20*E20*F20,4)</f>
         <v>1.55E-2</v>
       </c>
       <c r="H20" s="85">
-        <v>8.26</v>
+        <v>8.24</v>
       </c>
       <c r="I20" s="85">
         <v>8.06</v>
       </c>
       <c r="J20" s="84">
-        <f>'заказ-order'!E145</f>
+        <f>'заказ-order'!E151</f>
         <v>0</v>
       </c>
       <c r="K20" s="130">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="K20" si="26">H20*J20</f>
         <v>0</v>
       </c>
       <c r="L20" s="130">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="L20" si="27">I20*J20</f>
         <v>0</v>
       </c>
       <c r="M20" s="83">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="M20" si="28">J20*D20*E20*F20</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="82">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="87"/>
       <c r="C21" s="80" t="s">
-        <v>387</v>
+        <v>187</v>
       </c>
       <c r="D21" s="79">
-        <v>0.28699999999999998</v>
+        <v>0.375</v>
       </c>
       <c r="E21" s="79">
+        <v>0.495</v>
+      </c>
+      <c r="F21" s="86">
         <v>0.19</v>
       </c>
-      <c r="F21" s="86">
-        <v>0.28499999999999998</v>
-      </c>
       <c r="G21" s="89">
-        <f t="shared" ref="G21" si="29">ROUND(D21*E21*F21,4)</f>
-        <v>1.55E-2</v>
-      </c>
-      <c r="H21" s="85">
-        <v>8.24</v>
-      </c>
-      <c r="I21" s="85">
-        <v>8.06</v>
+        <f>ROUND(D21*E21*F21,4)</f>
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="H21" s="86">
+        <v>12.34</v>
+      </c>
+      <c r="I21" s="86">
+        <v>11.6</v>
       </c>
       <c r="J21" s="84">
-        <f>'заказ-order'!E151</f>
+        <f>'заказ-order'!E156</f>
         <v>0</v>
       </c>
       <c r="K21" s="130">
-        <f t="shared" ref="K21" si="30">H21*J21</f>
+        <f>H21*J21</f>
         <v>0</v>
       </c>
       <c r="L21" s="130">
-        <f t="shared" ref="L21" si="31">I21*J21</f>
+        <f>I21*J21</f>
         <v>0</v>
       </c>
       <c r="M21" s="83">
-        <f t="shared" ref="M21" si="32">J21*D21*E21*F21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f>J21*D21*E21*F21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A22" s="82">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="87"/>
       <c r="C22" s="80" t="s">
-        <v>187</v>
+        <v>290</v>
       </c>
       <c r="D22" s="79">
-        <v>0.375</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E22" s="79">
-        <v>0.495</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="F22" s="86">
-        <v>0.19</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="G22" s="89">
         <f>ROUND(D22*E22*F22,4)</f>
-        <v>3.5299999999999998E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="H22" s="86">
-        <v>12.34</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I22" s="86">
-        <v>11.6</v>
+        <v>4.68</v>
       </c>
       <c r="J22" s="84">
-        <f>'заказ-order'!E156</f>
+        <f>'заказ-order'!E159</f>
         <v>0</v>
       </c>
       <c r="K22" s="130">
@@ -13672,11 +13642,11 @@
     </row>
     <row r="23" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A23" s="82">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="87"/>
       <c r="C23" s="80" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="D23" s="79">
         <v>0.32800000000000001</v>
@@ -13698,7 +13668,7 @@
         <v>4.68</v>
       </c>
       <c r="J23" s="84">
-        <f>'заказ-order'!E159</f>
+        <f>'заказ-order'!E160</f>
         <v>0</v>
       </c>
       <c r="K23" s="130">
@@ -13714,35 +13684,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="82">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="87"/>
       <c r="C24" s="80" t="s">
-        <v>316</v>
-      </c>
-      <c r="D24" s="79">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="E24" s="79">
-        <v>0.19400000000000001</v>
-      </c>
-      <c r="F24" s="86">
-        <v>0.25900000000000001</v>
+        <v>192</v>
+      </c>
+      <c r="D24" s="88">
+        <v>0.33</v>
+      </c>
+      <c r="E24" s="88">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="F24" s="85">
+        <v>0.255</v>
       </c>
       <c r="G24" s="89">
         <f>ROUND(D24*E24*F24,4)</f>
-        <v>1.6500000000000001E-2</v>
+        <v>1.3899999999999999E-2</v>
       </c>
       <c r="H24" s="86">
-        <v>4.9000000000000004</v>
+        <v>8</v>
       </c>
       <c r="I24" s="86">
-        <v>4.68</v>
+        <v>7.82</v>
       </c>
       <c r="J24" s="84">
-        <f>'заказ-order'!E160</f>
+        <f>'заказ-order'!E162</f>
         <v>0</v>
       </c>
       <c r="K24" s="130">
@@ -13758,189 +13728,189 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="82">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="87"/>
       <c r="C25" s="80" t="s">
-        <v>192</v>
-      </c>
-      <c r="D25" s="88">
-        <v>0.33</v>
-      </c>
-      <c r="E25" s="88">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="F25" s="85">
-        <v>0.255</v>
+        <v>335</v>
+      </c>
+      <c r="D25" s="79">
+        <v>0.3</v>
+      </c>
+      <c r="E25" s="79">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="F25" s="86">
+        <v>0.191</v>
       </c>
       <c r="G25" s="89">
-        <f>ROUND(D25*E25*F25,4)</f>
-        <v>1.3899999999999999E-2</v>
+        <f t="shared" ref="G25" si="29">ROUND(D25*E25*F25,4)</f>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="H25" s="86">
-        <v>8</v>
+        <v>5.58</v>
       </c>
       <c r="I25" s="86">
-        <v>7.82</v>
+        <v>5.6</v>
       </c>
       <c r="J25" s="84">
-        <f>'заказ-order'!E162</f>
+        <f>'заказ-order'!E170</f>
         <v>0</v>
       </c>
       <c r="K25" s="130">
-        <f>H25*J25</f>
+        <f t="shared" ref="K25" si="30">H25*J25</f>
         <v>0</v>
       </c>
       <c r="L25" s="130">
-        <f>I25*J25</f>
+        <f t="shared" ref="L25" si="31">I25*J25</f>
         <v>0</v>
       </c>
       <c r="M25" s="83">
-        <f>J25*D25*E25*F25</f>
+        <f t="shared" ref="M25" si="32">J25*D25*E25*F25</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" s="82">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="87"/>
       <c r="C26" s="80" t="s">
-        <v>335</v>
+        <v>184</v>
       </c>
       <c r="D26" s="79">
-        <v>0.3</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="E26" s="79">
-        <v>0.17799999999999999</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="F26" s="86">
-        <v>0.191</v>
+        <v>0.22</v>
       </c>
       <c r="G26" s="89">
-        <f t="shared" ref="G26" si="33">ROUND(D26*E26*F26,4)</f>
-        <v>1.0200000000000001E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.54E-2</v>
       </c>
       <c r="H26" s="86">
-        <v>5.58</v>
+        <v>10.02</v>
       </c>
       <c r="I26" s="86">
-        <v>5.6</v>
+        <v>9.82</v>
       </c>
       <c r="J26" s="84">
-        <f>'заказ-order'!E170</f>
+        <f>'заказ-order'!E171</f>
         <v>0</v>
       </c>
       <c r="K26" s="130">
-        <f t="shared" ref="K26" si="34">H26*J26</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L26" s="130">
-        <f t="shared" ref="L26" si="35">I26*J26</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M26" s="83">
-        <f t="shared" ref="M26" si="36">J26*D26*E26*F26</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" s="82">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" s="87"/>
       <c r="C27" s="80" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="D27" s="79">
-        <v>0.26500000000000001</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="E27" s="79">
         <v>0.26500000000000001</v>
       </c>
       <c r="F27" s="86">
-        <v>0.22</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="G27" s="89">
-        <f t="shared" si="9"/>
-        <v>1.54E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="H27" s="86">
-        <v>10.02</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="I27" s="86">
-        <v>9.82</v>
+        <v>9.76</v>
       </c>
       <c r="J27" s="84">
-        <f>'заказ-order'!E171</f>
+        <f>'заказ-order'!E179</f>
         <v>0</v>
       </c>
       <c r="K27" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L27" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M27" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="82">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" s="87"/>
       <c r="C28" s="80" t="s">
-        <v>164</v>
+        <v>395</v>
       </c>
       <c r="D28" s="79">
-        <v>0.27500000000000002</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="E28" s="79">
-        <v>0.26500000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="F28" s="86">
-        <v>0.22500000000000001</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="G28" s="89">
-        <f t="shared" si="9"/>
-        <v>1.6400000000000001E-2</v>
-      </c>
-      <c r="H28" s="86">
-        <v>9.9600000000000009</v>
-      </c>
-      <c r="I28" s="86">
-        <v>9.76</v>
+        <f t="shared" ref="G28" si="33">ROUND(D28*E28*F28,4)</f>
+        <v>1.55E-2</v>
+      </c>
+      <c r="H28" s="85">
+        <v>8.08</v>
+      </c>
+      <c r="I28" s="85">
+        <v>7.88</v>
       </c>
       <c r="J28" s="84">
-        <f>'заказ-order'!E179</f>
+        <f>'заказ-order'!E185</f>
         <v>0</v>
       </c>
       <c r="K28" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K28" si="34">H28*J28</f>
         <v>0</v>
       </c>
       <c r="L28" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="L28" si="35">I28*J28</f>
         <v>0</v>
       </c>
       <c r="M28" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M28" si="36">J28*D28*E28*F28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A29" s="82">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" s="87"/>
       <c r="C29" s="80" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D29" s="79">
         <v>0.28699999999999998</v>
@@ -13952,39 +13922,39 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="G29" s="89">
-        <f t="shared" ref="G29" si="37">ROUND(D29*E29*F29,4)</f>
+        <f t="shared" si="5"/>
         <v>1.55E-2</v>
       </c>
       <c r="H29" s="85">
-        <v>8.08</v>
+        <v>8.26</v>
       </c>
       <c r="I29" s="85">
-        <v>7.88</v>
+        <v>8.06</v>
       </c>
       <c r="J29" s="84">
-        <f>'заказ-order'!E185</f>
+        <f>'заказ-order'!E191</f>
         <v>0</v>
       </c>
       <c r="K29" s="130">
-        <f t="shared" ref="K29" si="38">H29*J29</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L29" s="130">
-        <f t="shared" ref="L29" si="39">I29*J29</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M29" s="83">
-        <f t="shared" ref="M29" si="40">J29*D29*E29*F29</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="82">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" s="87"/>
       <c r="C30" s="80" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D30" s="79">
         <v>0.28699999999999998</v>
@@ -13996,171 +13966,171 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="G30" s="89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>1.55E-2</v>
       </c>
       <c r="H30" s="85">
-        <v>8.26</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="I30" s="85">
-        <v>8.06</v>
+        <v>8.08</v>
       </c>
       <c r="J30" s="84">
-        <f>'заказ-order'!E191</f>
+        <f>'заказ-order'!E196</f>
         <v>0</v>
       </c>
       <c r="K30" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L30" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M30" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A31" s="82">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" s="87"/>
       <c r="C31" s="80" t="s">
-        <v>394</v>
+        <v>193</v>
       </c>
       <c r="D31" s="79">
-        <v>0.28699999999999998</v>
+        <v>0.34</v>
       </c>
       <c r="E31" s="79">
-        <v>0.19</v>
+        <v>0.216</v>
       </c>
       <c r="F31" s="86">
-        <v>0.28499999999999998</v>
+        <v>0.21</v>
       </c>
       <c r="G31" s="89">
-        <f t="shared" si="9"/>
-        <v>1.55E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.54E-2</v>
       </c>
       <c r="H31" s="85">
-        <v>8.2799999999999994</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I31" s="85">
-        <v>8.08</v>
+        <v>8.6</v>
       </c>
       <c r="J31" s="84">
-        <f>'заказ-order'!E196</f>
+        <f>'заказ-order'!E202</f>
         <v>0</v>
       </c>
       <c r="K31" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L31" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M31" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A32" s="82">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" s="87"/>
       <c r="C32" s="80" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D32" s="79">
-        <v>0.34</v>
+        <v>0.315</v>
       </c>
       <c r="E32" s="79">
-        <v>0.216</v>
+        <v>0.31</v>
       </c>
       <c r="F32" s="86">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="G32" s="89">
-        <f t="shared" si="9"/>
-        <v>1.54E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="H32" s="85">
-        <v>8.8000000000000007</v>
+        <v>10.1</v>
       </c>
       <c r="I32" s="85">
-        <v>8.6</v>
+        <v>9.84</v>
       </c>
       <c r="J32" s="84">
-        <f>'заказ-order'!E202</f>
+        <f>'заказ-order'!E204</f>
         <v>0</v>
       </c>
       <c r="K32" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L32" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M32" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A33" s="82">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" s="87"/>
       <c r="C33" s="80" t="s">
-        <v>194</v>
+        <v>380</v>
       </c>
       <c r="D33" s="79">
-        <v>0.315</v>
+        <v>0.3</v>
       </c>
       <c r="E33" s="79">
-        <v>0.31</v>
+        <v>0.158</v>
       </c>
       <c r="F33" s="86">
-        <v>0.18</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="G33" s="89">
-        <f t="shared" si="9"/>
-        <v>1.7600000000000001E-2</v>
+        <f t="shared" ref="G33" si="37">ROUND(D33*E33*F33,4)</f>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H33" s="85">
-        <v>10.1</v>
+        <v>3.7</v>
       </c>
       <c r="I33" s="85">
-        <v>9.84</v>
+        <v>3.58</v>
       </c>
       <c r="J33" s="84">
-        <f>'заказ-order'!E204</f>
+        <f>'заказ-order'!E205</f>
         <v>0</v>
       </c>
       <c r="K33" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K33" si="38">H33*J33</f>
         <v>0</v>
       </c>
       <c r="L33" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="L33" si="39">I33*J33</f>
         <v>0</v>
       </c>
       <c r="M33" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="M33" si="40">J33*D33*E33*F33</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A34" s="82">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" s="87"/>
       <c r="C34" s="80" t="s">
-        <v>380</v>
+        <v>195</v>
       </c>
       <c r="D34" s="79">
         <v>0.3</v>
@@ -14172,127 +14142,127 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G34" s="89">
-        <f t="shared" ref="G34" si="41">ROUND(D34*E34*F34,4)</f>
+        <f t="shared" si="5"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="H34" s="85">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="I34" s="85">
-        <v>3.58</v>
+        <v>3.04</v>
       </c>
       <c r="J34" s="84">
-        <f>'заказ-order'!E205</f>
+        <f>'заказ-order'!E206</f>
         <v>0</v>
       </c>
       <c r="K34" s="130">
-        <f t="shared" ref="K34" si="42">H34*J34</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L34" s="130">
-        <f t="shared" ref="L34" si="43">I34*J34</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M34" s="83">
-        <f t="shared" ref="M34" si="44">J34*D34*E34*F34</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A35" s="82">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" s="87"/>
       <c r="C35" s="80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D35" s="79">
-        <v>0.3</v>
+        <v>0.316</v>
       </c>
       <c r="E35" s="79">
-        <v>0.158</v>
+        <v>0.19</v>
       </c>
       <c r="F35" s="86">
-        <v>0.16800000000000001</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="G35" s="89">
-        <f t="shared" si="9"/>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="5"/>
+        <v>1.06E-2</v>
       </c>
       <c r="H35" s="85">
-        <v>3.18</v>
+        <v>2.72</v>
       </c>
       <c r="I35" s="85">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
       <c r="J35" s="84">
-        <f>'заказ-order'!E206</f>
+        <f>'заказ-order'!E207</f>
         <v>0</v>
       </c>
       <c r="K35" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L35" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M35" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A36" s="82">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" s="87"/>
       <c r="C36" s="80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D36" s="79">
-        <v>0.316</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="E36" s="79">
-        <v>0.19</v>
+        <v>0.215</v>
       </c>
       <c r="F36" s="86">
-        <v>0.17699999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="G36" s="89">
-        <f t="shared" si="9"/>
-        <v>1.06E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H36" s="85">
-        <v>2.72</v>
+        <v>6.62</v>
       </c>
       <c r="I36" s="85">
-        <v>2.56</v>
+        <v>6.4</v>
       </c>
       <c r="J36" s="84">
-        <f>'заказ-order'!E207</f>
+        <f>'заказ-order'!E208</f>
         <v>0</v>
       </c>
       <c r="K36" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L36" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M36" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A37" s="82">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" s="87"/>
       <c r="C37" s="80" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D37" s="79">
         <v>0.28499999999999998</v>
@@ -14304,7 +14274,7 @@
         <v>0.18</v>
       </c>
       <c r="G37" s="89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="H37" s="85">
@@ -14314,1375 +14284,1375 @@
         <v>6.4</v>
       </c>
       <c r="J37" s="84">
-        <f>'заказ-order'!E208</f>
+        <f>'заказ-order'!E209</f>
         <v>0</v>
       </c>
       <c r="K37" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L37" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M37" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A38" s="82">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" s="87"/>
       <c r="C38" s="80" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D38" s="79">
-        <v>0.28499999999999998</v>
+        <v>0.215</v>
       </c>
       <c r="E38" s="79">
         <v>0.215</v>
       </c>
       <c r="F38" s="86">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G38" s="89">
-        <f t="shared" si="9"/>
-        <v>1.0999999999999999E-2</v>
+        <f t="shared" si="5"/>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="H38" s="85">
-        <v>6.62</v>
+        <v>3.7</v>
       </c>
       <c r="I38" s="85">
-        <v>6.4</v>
+        <v>3.52</v>
       </c>
       <c r="J38" s="84">
-        <f>'заказ-order'!E209</f>
+        <f>'заказ-order'!E210</f>
         <v>0</v>
       </c>
       <c r="K38" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L38" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M38" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A39" s="82">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" s="87"/>
       <c r="C39" s="80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D39" s="79">
-        <v>0.215</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="E39" s="79">
-        <v>0.215</v>
+        <v>0.16</v>
       </c>
       <c r="F39" s="86">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="G39" s="89">
-        <f t="shared" si="9"/>
-        <v>6.8999999999999999E-3</v>
+        <f t="shared" si="5"/>
+        <v>1.18E-2</v>
       </c>
       <c r="H39" s="85">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="I39" s="85">
-        <v>3.52</v>
+        <v>7.04</v>
       </c>
       <c r="J39" s="84">
-        <f>'заказ-order'!E210</f>
+        <f>'заказ-order'!E213</f>
         <v>0</v>
       </c>
       <c r="K39" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L39" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M39" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A40" s="82">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="87"/>
       <c r="C40" s="80" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D40" s="79">
-        <v>0.29499999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="E40" s="79">
-        <v>0.16</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="F40" s="86">
-        <v>0.25</v>
+        <v>0.191</v>
       </c>
       <c r="G40" s="89">
-        <f t="shared" si="9"/>
-        <v>1.18E-2</v>
+        <f>ROUND(D40*E40*F40,4)</f>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="H40" s="85">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="I40" s="85">
-        <v>7.04</v>
+        <v>5.46</v>
       </c>
       <c r="J40" s="84">
-        <f>'заказ-order'!E213</f>
+        <f>'заказ-order'!E214</f>
         <v>0</v>
       </c>
       <c r="K40" s="130">
-        <f t="shared" si="10"/>
+        <f>H40*J40</f>
         <v>0</v>
       </c>
       <c r="L40" s="130">
-        <f t="shared" si="11"/>
+        <f>I40*J40</f>
         <v>0</v>
       </c>
       <c r="M40" s="83">
-        <f t="shared" si="12"/>
+        <f>J40*D40*E40*F40</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A41" s="82">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="87"/>
       <c r="C41" s="80" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D41" s="79">
-        <v>0.3</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="E41" s="79">
-        <v>0.17799999999999999</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="F41" s="86">
-        <v>0.191</v>
+        <v>0.2</v>
       </c>
       <c r="G41" s="89">
-        <f>ROUND(D41*E41*F41,4)</f>
-        <v>1.0200000000000001E-2</v>
+        <f t="shared" si="5"/>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="H41" s="85">
-        <v>5.6</v>
+        <v>4.62</v>
       </c>
       <c r="I41" s="85">
-        <v>5.46</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="J41" s="84">
-        <f>'заказ-order'!E214</f>
+        <f>'заказ-order'!E215</f>
         <v>0</v>
       </c>
       <c r="K41" s="130">
-        <f>H41*J41</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L41" s="130">
-        <f>I41*J41</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M41" s="83">
-        <f>J41*D41*E41*F41</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A42" s="82">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" s="87"/>
       <c r="C42" s="80" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D42" s="79">
         <v>0.29499999999999998</v>
       </c>
       <c r="E42" s="79">
-        <v>0.14000000000000001</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="F42" s="86">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G42" s="89">
-        <f t="shared" si="9"/>
-        <v>8.3000000000000001E-3</v>
+        <f>ROUND(D42*E42*F42,4)</f>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="H42" s="85">
-        <v>4.62</v>
+        <v>3.44</v>
       </c>
       <c r="I42" s="85">
-        <v>4.4800000000000004</v>
+        <v>3.3200000000000003</v>
       </c>
       <c r="J42" s="84">
-        <f>'заказ-order'!E215</f>
+        <f>'заказ-order'!E216</f>
         <v>0</v>
       </c>
       <c r="K42" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L42" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M42" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A43" s="82">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" s="87"/>
       <c r="C43" s="80" t="s">
-        <v>203</v>
-      </c>
-      <c r="D43" s="79">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="E43" s="79">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="F43" s="86">
-        <v>0.15</v>
+        <v>232</v>
+      </c>
+      <c r="D43" s="88">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="E43" s="88">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="F43" s="85">
+        <v>0.157</v>
       </c>
       <c r="G43" s="89">
         <f>ROUND(D43*E43*F43,4)</f>
-        <v>7.7000000000000002E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="H43" s="85">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="I43" s="85">
-        <v>3.3200000000000003</v>
+        <v>3.1440000000000001</v>
       </c>
       <c r="J43" s="84">
-        <f>'заказ-order'!E216</f>
+        <f>'заказ-order'!E218</f>
         <v>0</v>
       </c>
       <c r="K43" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L43" s="130">
-        <f t="shared" si="11"/>
+        <f>I43*J43</f>
         <v>0</v>
       </c>
       <c r="M43" s="83">
-        <f t="shared" si="12"/>
+        <f>J43*D43*E43*F43</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A44" s="82">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" s="87"/>
       <c r="C44" s="80" t="s">
-        <v>232</v>
-      </c>
-      <c r="D44" s="88">
-        <v>0.26300000000000001</v>
-      </c>
-      <c r="E44" s="88">
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="F44" s="85">
-        <v>0.157</v>
+        <v>324</v>
+      </c>
+      <c r="D44" s="79">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="E44" s="79">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="F44" s="86">
+        <v>0.19</v>
       </c>
       <c r="G44" s="89">
-        <f>ROUND(D44*E44*F44,4)</f>
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="H44" s="85">
-        <v>3.27</v>
-      </c>
-      <c r="I44" s="85">
-        <v>3.1440000000000001</v>
+        <f t="shared" ref="G44:G74" si="41">ROUND(D44*E44*F44,4)</f>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="H44" s="86">
+        <v>5.3</v>
+      </c>
+      <c r="I44" s="86">
+        <v>5.16</v>
       </c>
       <c r="J44" s="84">
-        <f>'заказ-order'!E218</f>
+        <f>'заказ-order'!E220</f>
         <v>0</v>
       </c>
       <c r="K44" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K44" si="42">H44*J44</f>
         <v>0</v>
       </c>
       <c r="L44" s="130">
-        <f>I44*J44</f>
+        <f t="shared" ref="L44" si="43">I44*J44</f>
         <v>0</v>
       </c>
       <c r="M44" s="83">
-        <f>J44*D44*E44*F44</f>
+        <f t="shared" ref="M44" si="44">J44*D44*E44*F44</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A45" s="82">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="87"/>
       <c r="C45" s="80" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="D45" s="79">
-        <v>0.22500000000000001</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="E45" s="79">
-        <v>0.21299999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="F45" s="86">
-        <v>0.19</v>
+        <v>0.155</v>
       </c>
       <c r="G45" s="89">
-        <f t="shared" ref="G45:G75" si="45">ROUND(D45*E45*F45,4)</f>
-        <v>9.1000000000000004E-3</v>
+        <f t="shared" si="5"/>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="H45" s="86">
-        <v>5.3</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="I45" s="86">
-        <v>5.16</v>
+        <v>3.94</v>
       </c>
       <c r="J45" s="84">
-        <f>'заказ-order'!E220</f>
+        <f>'заказ-order'!E226</f>
         <v>0</v>
       </c>
       <c r="K45" s="130">
-        <f t="shared" ref="K45" si="46">H45*J45</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L45" s="130">
-        <f t="shared" ref="L45" si="47">I45*J45</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M45" s="83">
-        <f t="shared" ref="M45" si="48">J45*D45*E45*F45</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A46" s="82">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" s="87"/>
       <c r="C46" s="80" t="s">
-        <v>204</v>
+        <v>291</v>
       </c>
       <c r="D46" s="79">
-        <v>0.27500000000000002</v>
+        <v>0.24</v>
       </c>
       <c r="E46" s="79">
-        <v>0.17</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="F46" s="86">
-        <v>0.155</v>
+        <v>0.193</v>
       </c>
       <c r="G46" s="89">
-        <f t="shared" si="9"/>
-        <v>7.1999999999999998E-3</v>
+        <f t="shared" si="41"/>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="H46" s="86">
-        <v>4.0599999999999996</v>
+        <v>3.67</v>
       </c>
       <c r="I46" s="86">
-        <v>3.94</v>
+        <v>3.57</v>
       </c>
       <c r="J46" s="84">
-        <f>'заказ-order'!E226</f>
+        <f>'заказ-order'!E221</f>
         <v>0</v>
       </c>
       <c r="K46" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K46:K54" si="45">H46*J46</f>
         <v>0</v>
       </c>
       <c r="L46" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M46" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A47" s="82">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" s="87"/>
       <c r="C47" s="80" t="s">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="D47" s="79">
-        <v>0.24</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="E47" s="79">
-        <v>0.14499999999999999</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="F47" s="86">
-        <v>0.193</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="G47" s="89">
+        <f t="shared" si="5"/>
+        <v>7.6E-3</v>
+      </c>
+      <c r="H47" s="86">
+        <v>3.42</v>
+      </c>
+      <c r="I47" s="86">
+        <v>3.27</v>
+      </c>
+      <c r="J47" s="84">
+        <f>'заказ-order'!E223</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="130">
         <f t="shared" si="45"/>
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="H47" s="86">
-        <v>3.67</v>
-      </c>
-      <c r="I47" s="86">
-        <v>3.57</v>
-      </c>
-      <c r="J47" s="84">
-        <f>'заказ-order'!E221</f>
-        <v>0</v>
-      </c>
-      <c r="K47" s="130">
-        <f t="shared" ref="K47:K55" si="49">H47*J47</f>
         <v>0</v>
       </c>
       <c r="L47" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M47" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A48" s="82">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" s="87"/>
       <c r="C48" s="80" t="s">
-        <v>246</v>
+        <v>424</v>
       </c>
       <c r="D48" s="79">
-        <v>0.23499999999999999</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="E48" s="79">
-        <v>0.19700000000000001</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="F48" s="86">
-        <v>0.16500000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G48" s="89">
-        <f t="shared" si="9"/>
-        <v>7.6E-3</v>
+        <f t="shared" si="41"/>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="H48" s="86">
-        <v>3.42</v>
+        <v>5.1230000000000002</v>
       </c>
       <c r="I48" s="86">
-        <v>3.27</v>
+        <v>4.9320000000000004</v>
       </c>
       <c r="J48" s="84">
-        <f>'заказ-order'!E223</f>
+        <f>'заказ-order'!E229</f>
         <v>0</v>
       </c>
       <c r="K48" s="130">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L48" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="L48:L54" si="46">I48*J48</f>
         <v>0</v>
       </c>
       <c r="M48" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M48:M54" si="47">J48*D48*E48*F48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A49" s="82">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" s="87"/>
       <c r="C49" s="80" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D49" s="79">
-        <v>0.26500000000000001</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E49" s="79">
-        <v>0.22500000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="F49" s="86">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G49" s="89">
+        <f t="shared" si="5"/>
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="H49" s="86">
+        <v>3.78</v>
+      </c>
+      <c r="I49" s="86">
+        <v>3.64</v>
+      </c>
+      <c r="J49" s="84">
+        <f>'заказ-order'!E224</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="130">
         <f t="shared" si="45"/>
-        <v>1.0699999999999999E-2</v>
-      </c>
-      <c r="H49" s="86">
-        <v>5.1230000000000002</v>
-      </c>
-      <c r="I49" s="86">
-        <v>4.9320000000000004</v>
-      </c>
-      <c r="J49" s="84">
-        <f>'заказ-order'!E229</f>
-        <v>0</v>
-      </c>
-      <c r="K49" s="130">
-        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L49" s="130">
-        <f t="shared" ref="L49:L55" si="50">I49*J49</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M49" s="83">
-        <f t="shared" ref="M49:M55" si="51">J49*D49*E49*F49</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A50" s="82">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" s="87"/>
       <c r="C50" s="80" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D50" s="79">
-        <v>0.28999999999999998</v>
+        <v>0.255</v>
       </c>
       <c r="E50" s="79">
-        <v>0.18</v>
+        <v>0.185</v>
       </c>
       <c r="F50" s="86">
-        <v>0.17</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G50" s="89">
-        <f t="shared" si="9"/>
-        <v>8.8999999999999999E-3</v>
+        <f t="shared" si="41"/>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="H50" s="86">
-        <v>3.78</v>
+        <v>2.48</v>
       </c>
       <c r="I50" s="86">
-        <v>3.64</v>
+        <v>2.359</v>
       </c>
       <c r="J50" s="84">
-        <f>'заказ-order'!E224</f>
+        <f>'заказ-order'!E226</f>
         <v>0</v>
       </c>
       <c r="K50" s="130">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L50" s="130">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M50" s="83">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A51" s="82">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" s="87"/>
       <c r="C51" s="80" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D51" s="79">
-        <v>0.255</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="E51" s="79">
-        <v>0.185</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="F51" s="86">
         <v>0.13500000000000001</v>
       </c>
       <c r="G51" s="89">
+        <f t="shared" si="5"/>
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="H51" s="86">
+        <v>3.04</v>
+      </c>
+      <c r="I51" s="86">
+        <v>2.9039999999999999</v>
+      </c>
+      <c r="J51" s="84">
+        <f>'заказ-order'!E232</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="130">
         <f t="shared" si="45"/>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="H51" s="86">
-        <v>2.48</v>
-      </c>
-      <c r="I51" s="86">
-        <v>2.359</v>
-      </c>
-      <c r="J51" s="84">
-        <f>'заказ-order'!E226</f>
-        <v>0</v>
-      </c>
-      <c r="K51" s="130">
-        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L51" s="130">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M51" s="83">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A52" s="82">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" s="87"/>
       <c r="C52" s="80" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D52" s="79">
-        <v>0.26500000000000001</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="E52" s="79">
-        <v>0.20699999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="F52" s="86">
-        <v>0.13500000000000001</v>
+        <v>0.188</v>
       </c>
       <c r="G52" s="89">
-        <f t="shared" si="9"/>
-        <v>7.4000000000000003E-3</v>
+        <f t="shared" si="41"/>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="H52" s="86">
-        <v>3.04</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="I52" s="86">
-        <v>2.9039999999999999</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="J52" s="84">
-        <f>'заказ-order'!E232</f>
+        <f>'заказ-order'!E227</f>
         <v>0</v>
       </c>
       <c r="K52" s="130">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L52" s="130">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M52" s="83">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A53" s="82">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53" s="87"/>
       <c r="C53" s="80" t="s">
-        <v>420</v>
+        <v>311</v>
       </c>
       <c r="D53" s="79">
-        <v>0.25800000000000001</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E53" s="79">
-        <v>0.17</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="F53" s="86">
-        <v>0.188</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G53" s="89">
+        <f t="shared" si="5"/>
+        <v>1.34E-2</v>
+      </c>
+      <c r="H53" s="85">
+        <v>6.82</v>
+      </c>
+      <c r="I53" s="85">
+        <v>6.66</v>
+      </c>
+      <c r="J53" s="84">
+        <f>'заказ-order'!E249</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="130">
         <f t="shared" si="45"/>
-        <v>8.2000000000000007E-3</v>
-      </c>
-      <c r="H53" s="86">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="I53" s="86">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="J53" s="84">
-        <f>'заказ-order'!E227</f>
-        <v>0</v>
-      </c>
-      <c r="K53" s="130">
-        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L53" s="130">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M53" s="83">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A54" s="82">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" s="87"/>
       <c r="C54" s="80" t="s">
-        <v>311</v>
+        <v>425</v>
       </c>
       <c r="D54" s="79">
-        <v>0.28999999999999998</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="E54" s="79">
-        <v>0.17499999999999999</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="F54" s="86">
-        <v>0.26400000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="G54" s="89">
-        <f t="shared" si="9"/>
-        <v>1.34E-2</v>
+        <f t="shared" si="41"/>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="H54" s="85">
-        <v>6.82</v>
+        <v>2.3340000000000001</v>
       </c>
       <c r="I54" s="85">
-        <v>6.66</v>
+        <v>2.2080000000000002</v>
       </c>
       <c r="J54" s="84">
-        <f>'заказ-order'!E249</f>
+        <f>'заказ-order'!E235</f>
         <v>0</v>
       </c>
       <c r="K54" s="130">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L54" s="130">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M54" s="83">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A55" s="82">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" s="87"/>
       <c r="C55" s="80" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D55" s="79">
-        <v>0.24199999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="E55" s="79">
-        <v>0.17199999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="F55" s="86">
-        <v>0.17</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G55" s="89">
-        <f t="shared" si="45"/>
-        <v>7.1000000000000004E-3</v>
+        <f t="shared" si="5"/>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="H55" s="85">
-        <v>2.3340000000000001</v>
+        <v>1.6759999999999999</v>
       </c>
       <c r="I55" s="85">
-        <v>2.2080000000000002</v>
+        <v>1.536</v>
       </c>
       <c r="J55" s="84">
-        <f>'заказ-order'!E235</f>
+        <f>'заказ-order'!E268</f>
         <v>0</v>
       </c>
       <c r="K55" s="130">
-        <f t="shared" si="49"/>
+        <f>H55*J55</f>
         <v>0</v>
       </c>
       <c r="L55" s="130">
-        <f t="shared" si="50"/>
+        <f>I55*J55</f>
         <v>0</v>
       </c>
       <c r="M55" s="83">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f>J55*D55*E55*F55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A56" s="82">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" s="87"/>
       <c r="C56" s="80" t="s">
-        <v>426</v>
+        <v>95</v>
       </c>
       <c r="D56" s="79">
-        <v>0.25</v>
+        <v>0.255</v>
       </c>
       <c r="E56" s="79">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="F56" s="86">
-        <v>0.13500000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="G56" s="89">
-        <f t="shared" si="9"/>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="H56" s="85">
-        <v>1.6759999999999999</v>
-      </c>
-      <c r="I56" s="85">
-        <v>1.536</v>
+        <f t="shared" si="41"/>
+        <v>5.3E-3</v>
+      </c>
+      <c r="H56" s="86">
+        <v>2.58</v>
+      </c>
+      <c r="I56" s="86">
+        <v>2.5</v>
       </c>
       <c r="J56" s="84">
-        <f>'заказ-order'!E268</f>
+        <f>'заказ-order'!E273</f>
         <v>0</v>
       </c>
       <c r="K56" s="130">
-        <f>H56*J56</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L56" s="130">
-        <f>I56*J56</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M56" s="83">
-        <f>J56*D56*E56*F56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A57" s="82">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" s="87"/>
       <c r="C57" s="80" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="D57" s="79">
-        <v>0.255</v>
+        <v>0.315</v>
       </c>
       <c r="E57" s="79">
-        <v>0.13</v>
+        <v>0.187</v>
       </c>
       <c r="F57" s="86">
-        <v>0.16</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="G57" s="89">
-        <f t="shared" si="45"/>
-        <v>5.3E-3</v>
+        <f t="shared" si="5"/>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="H57" s="86">
-        <v>2.58</v>
+        <v>3.54</v>
       </c>
       <c r="I57" s="86">
-        <v>2.5</v>
+        <v>3.38</v>
       </c>
       <c r="J57" s="84">
-        <f>'заказ-order'!E273</f>
+        <f>'заказ-order'!E285</f>
         <v>0</v>
       </c>
       <c r="K57" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L57" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M57" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A58" s="82">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B58" s="87"/>
       <c r="C58" s="80" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D58" s="79">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="E58" s="79">
-        <v>0.187</v>
+        <v>0.21</v>
       </c>
       <c r="F58" s="86">
-        <v>0.21199999999999999</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="G58" s="89">
-        <f t="shared" si="9"/>
-        <v>1.2500000000000001E-2</v>
+        <f t="shared" si="41"/>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H58" s="86">
-        <v>3.54</v>
+        <v>3.08</v>
       </c>
       <c r="I58" s="86">
-        <v>3.38</v>
+        <v>2.92</v>
       </c>
       <c r="J58" s="84">
-        <f>'заказ-order'!E285</f>
+        <f>'заказ-order'!E289</f>
         <v>0</v>
       </c>
       <c r="K58" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L58" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M58" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A59" s="82">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59" s="87"/>
       <c r="C59" s="80" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D59" s="79">
-        <v>0.31</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="E59" s="79">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="F59" s="86">
-        <v>0.16900000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G59" s="89">
-        <f t="shared" si="45"/>
-        <v>1.0999999999999999E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="H59" s="86">
-        <v>3.08</v>
+        <v>8.26</v>
       </c>
       <c r="I59" s="86">
-        <v>2.92</v>
+        <v>7.9</v>
       </c>
       <c r="J59" s="84">
-        <f>'заказ-order'!E289</f>
+        <f>'заказ-order'!E294</f>
         <v>0</v>
       </c>
       <c r="K59" s="130">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K59" si="48">H59*J59</f>
         <v>0</v>
       </c>
       <c r="L59" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M59" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A60" s="82">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60" s="87"/>
       <c r="C60" s="80" t="s">
-        <v>183</v>
+        <v>429</v>
       </c>
       <c r="D60" s="79">
-        <v>0.39400000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="E60" s="79">
-        <v>0.23</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="F60" s="86">
-        <v>0.18</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="G60" s="89">
-        <f t="shared" si="9"/>
-        <v>1.6299999999999999E-2</v>
+        <f t="shared" si="41"/>
+        <v>1.3599999999999999E-2</v>
       </c>
       <c r="H60" s="86">
-        <v>8.26</v>
+        <v>7.4279999999999999</v>
       </c>
       <c r="I60" s="86">
-        <v>7.9</v>
+        <v>7.2560000000000002</v>
       </c>
       <c r="J60" s="84">
-        <f>'заказ-order'!E294</f>
+        <f>'заказ-order'!E301</f>
         <v>0</v>
       </c>
       <c r="K60" s="130">
-        <f t="shared" ref="K60" si="52">H60*J60</f>
+        <f t="shared" ref="K60" si="49">H60*J60</f>
         <v>0</v>
       </c>
       <c r="L60" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="L60" si="50">I60*J60</f>
         <v>0</v>
       </c>
       <c r="M60" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M60" si="51">J60*D60*E60*F60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A61" s="82">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61" s="87"/>
       <c r="C61" s="80" t="s">
-        <v>429</v>
+        <v>67</v>
       </c>
       <c r="D61" s="79">
-        <v>0.27</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="E61" s="79">
-        <v>0.19500000000000001</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="F61" s="86">
-        <v>0.25800000000000001</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G61" s="89">
-        <f t="shared" si="45"/>
-        <v>1.3599999999999999E-2</v>
+        <f t="shared" si="5"/>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="H61" s="86">
-        <v>7.4279999999999999</v>
+        <v>6.92</v>
       </c>
       <c r="I61" s="86">
-        <v>7.2560000000000002</v>
+        <v>6.76</v>
       </c>
       <c r="J61" s="84">
-        <f>'заказ-order'!E301</f>
+        <f>'заказ-order'!E313</f>
         <v>0</v>
       </c>
       <c r="K61" s="130">
-        <f t="shared" ref="K61" si="53">H61*J61</f>
+        <f t="shared" ref="K61:K68" si="52">H61*J61</f>
         <v>0</v>
       </c>
       <c r="L61" s="130">
-        <f t="shared" ref="L61" si="54">I61*J61</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M61" s="83">
-        <f t="shared" ref="M61" si="55">J61*D61*E61*F61</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A62" s="82">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62" s="87"/>
       <c r="C62" s="80" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D62" s="79">
-        <v>0.39200000000000002</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="E62" s="79">
-        <v>0.17699999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="F62" s="86">
-        <v>0.13500000000000001</v>
+        <v>0.185</v>
       </c>
       <c r="G62" s="89">
-        <f t="shared" si="9"/>
-        <v>9.4000000000000004E-3</v>
+        <f t="shared" si="41"/>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="H62" s="86">
-        <v>6.92</v>
+        <v>6.9</v>
       </c>
       <c r="I62" s="86">
-        <v>6.76</v>
+        <v>6.74</v>
       </c>
       <c r="J62" s="84">
-        <f>'заказ-order'!E313</f>
+        <f>'заказ-order'!E315</f>
         <v>0</v>
       </c>
       <c r="K62" s="130">
-        <f t="shared" ref="K62:K69" si="56">H62*J62</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="L62" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M62" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A63" s="82">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63" s="87"/>
       <c r="C63" s="80" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D63" s="79">
-        <v>0.32500000000000001</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="E63" s="79">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="F63" s="86">
-        <v>0.185</v>
+        <v>0.15</v>
       </c>
       <c r="G63" s="89">
-        <f t="shared" si="45"/>
-        <v>1.0800000000000001E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.01E-2</v>
       </c>
       <c r="H63" s="86">
-        <v>6.9</v>
+        <v>6.89</v>
       </c>
       <c r="I63" s="86">
-        <v>6.74</v>
+        <v>6.72</v>
       </c>
       <c r="J63" s="84">
-        <f>'заказ-order'!E315</f>
+        <f>'заказ-order'!E324</f>
         <v>0</v>
       </c>
       <c r="K63" s="130">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="L63" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M63" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A64" s="82">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64" s="87"/>
       <c r="C64" s="80" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D64" s="79">
-        <v>0.33500000000000002</v>
+        <v>0.35</v>
       </c>
       <c r="E64" s="79">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="F64" s="86">
-        <v>0.15</v>
+        <v>0.153</v>
       </c>
       <c r="G64" s="89">
-        <f t="shared" si="9"/>
-        <v>1.01E-2</v>
+        <f t="shared" si="41"/>
+        <v>1.12E-2</v>
       </c>
       <c r="H64" s="86">
-        <v>6.89</v>
+        <v>8.34</v>
       </c>
       <c r="I64" s="86">
-        <v>6.72</v>
+        <v>8.16</v>
       </c>
       <c r="J64" s="84">
-        <f>'заказ-order'!E324</f>
+        <f>'заказ-order'!E333</f>
         <v>0</v>
       </c>
       <c r="K64" s="130">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="L64" s="130">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="L64:L65" si="53">I64*J64</f>
         <v>0</v>
       </c>
       <c r="M64" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A65" s="82">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B65" s="87"/>
       <c r="C65" s="80" t="s">
-        <v>77</v>
+        <v>307</v>
       </c>
       <c r="D65" s="79">
-        <v>0.35</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="E65" s="79">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F65" s="86">
-        <v>0.153</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="G65" s="89">
-        <f t="shared" si="45"/>
-        <v>1.12E-2</v>
+        <f>ROUND(D65*E65*F65,4)</f>
+        <v>0.01</v>
       </c>
       <c r="H65" s="86">
-        <v>8.34</v>
+        <v>6.54</v>
       </c>
       <c r="I65" s="86">
-        <v>8.16</v>
+        <v>6.38</v>
       </c>
       <c r="J65" s="84">
-        <f>'заказ-order'!E333</f>
+        <f>'заказ-order'!E342</f>
         <v>0</v>
       </c>
       <c r="K65" s="130">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="L65" s="130">
-        <f t="shared" ref="L65:L66" si="57">I65*J65</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="M65" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A66" s="82">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66" s="87"/>
       <c r="C66" s="80" t="s">
-        <v>307</v>
+        <v>418</v>
       </c>
       <c r="D66" s="79">
-        <v>0.34499999999999997</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="E66" s="79">
-        <v>0.2</v>
+        <v>0.192</v>
       </c>
       <c r="F66" s="86">
-        <v>0.14499999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="G66" s="89">
-        <f>ROUND(D66*E66*F66,4)</f>
-        <v>0.01</v>
+        <f t="shared" si="41"/>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="H66" s="86">
-        <v>6.54</v>
+        <v>8.44</v>
       </c>
       <c r="I66" s="86">
-        <v>6.38</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="J66" s="84">
-        <f>'заказ-order'!E342</f>
+        <f>'заказ-order'!E349</f>
         <v>0</v>
       </c>
       <c r="K66" s="130">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="K66" si="54">H66*J66</f>
         <v>0</v>
       </c>
       <c r="L66" s="130">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="L66" si="55">I66*J66</f>
         <v>0</v>
       </c>
       <c r="M66" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M66" si="56">J66*D66*E66*F66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A67" s="82">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B67" s="87"/>
       <c r="C67" s="80" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="D67" s="79">
-        <v>0.33400000000000002</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="E67" s="79">
-        <v>0.192</v>
-      </c>
-      <c r="F67" s="86">
-        <v>0.155</v>
+        <v>0.25</v>
+      </c>
+      <c r="F67" s="79">
+        <v>0.17499999999999999</v>
       </c>
       <c r="G67" s="89">
-        <f t="shared" si="45"/>
-        <v>9.9000000000000008E-3</v>
+        <f t="shared" si="5"/>
+        <v>1.67E-2</v>
       </c>
       <c r="H67" s="86">
-        <v>8.44</v>
+        <v>5.46</v>
       </c>
       <c r="I67" s="86">
-        <v>8.2799999999999994</v>
+        <v>5.53</v>
       </c>
       <c r="J67" s="84">
-        <f>'заказ-order'!E349</f>
+        <f>'заказ-order'!E353</f>
         <v>0</v>
       </c>
       <c r="K67" s="130">
-        <f t="shared" ref="K67" si="58">H67*J67</f>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="L67" s="130">
-        <f t="shared" ref="L67" si="59">I67*J67</f>
+        <f>I67*J67</f>
         <v>0</v>
       </c>
       <c r="M67" s="83">
-        <f t="shared" ref="M67" si="60">J67*D67*E67*F67</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A68" s="82">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B68" s="87"/>
       <c r="C68" s="80" t="s">
-        <v>427</v>
+        <v>185</v>
       </c>
       <c r="D68" s="79">
-        <v>0.38200000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="E68" s="79">
-        <v>0.25</v>
-      </c>
-      <c r="F68" s="79">
-        <v>0.17499999999999999</v>
+        <v>0.21</v>
+      </c>
+      <c r="F68" s="86">
+        <v>0.19</v>
       </c>
       <c r="G68" s="89">
-        <f t="shared" si="9"/>
-        <v>1.67E-2</v>
+        <f t="shared" si="41"/>
+        <v>1.04E-2</v>
       </c>
       <c r="H68" s="86">
-        <v>5.46</v>
+        <v>5.6</v>
       </c>
       <c r="I68" s="86">
-        <v>5.53</v>
+        <v>5.38</v>
       </c>
       <c r="J68" s="84">
-        <f>'заказ-order'!E353</f>
+        <f>'заказ-order'!E354</f>
         <v>0</v>
       </c>
       <c r="K68" s="130">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="L68" s="130">
@@ -15690,61 +15660,61 @@
         <v>0</v>
       </c>
       <c r="M68" s="83">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M68" si="57">J68*D68*E68*F68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A69" s="82">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B69" s="87"/>
       <c r="C69" s="80" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="D69" s="79">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="E69" s="79">
-        <v>0.21</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="F69" s="86">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="G69" s="89">
-        <f t="shared" si="45"/>
-        <v>1.04E-2</v>
-      </c>
-      <c r="H69" s="86">
-        <v>5.6</v>
-      </c>
-      <c r="I69" s="86">
-        <v>5.38</v>
+        <f t="shared" si="5"/>
+        <v>1.44E-2</v>
+      </c>
+      <c r="H69" s="85">
+        <v>6.64</v>
+      </c>
+      <c r="I69" s="85">
+        <v>6.44</v>
       </c>
       <c r="J69" s="84">
-        <f>'заказ-order'!E354</f>
+        <f>'заказ-order'!E357</f>
         <v>0</v>
       </c>
       <c r="K69" s="130">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="K69:K74" si="58">H69*J69</f>
         <v>0</v>
       </c>
       <c r="L69" s="130">
-        <f>I69*J69</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M69" s="83">
-        <f t="shared" ref="M69" si="61">J69*D69*E69*F69</f>
+        <f t="shared" ref="M69:M74" si="59">J69*D69*E69*F69</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A70" s="82">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B70" s="87"/>
       <c r="C70" s="80" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D70" s="79">
         <v>0.27</v>
@@ -15756,7 +15726,7 @@
         <v>0.27</v>
       </c>
       <c r="G70" s="89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="41"/>
         <v>1.44E-2</v>
       </c>
       <c r="H70" s="85">
@@ -15766,73 +15736,73 @@
         <v>6.44</v>
       </c>
       <c r="J70" s="84">
-        <f>'заказ-order'!E357</f>
+        <f>'заказ-order'!E358</f>
         <v>0</v>
       </c>
       <c r="K70" s="130">
-        <f t="shared" ref="K70:K75" si="62">H70*J70</f>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="L70" s="130">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M70" s="83">
-        <f t="shared" ref="M70:M75" si="63">J70*D70*E70*F70</f>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A71" s="82">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B71" s="87"/>
       <c r="C71" s="80" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D71" s="79">
-        <v>0.27</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="E71" s="79">
-        <v>0.19700000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="F71" s="86">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="G71" s="89">
-        <f t="shared" si="45"/>
-        <v>1.44E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.17E-2</v>
       </c>
       <c r="H71" s="85">
-        <v>6.64</v>
+        <v>7.04</v>
       </c>
       <c r="I71" s="85">
-        <v>6.44</v>
+        <v>6.84</v>
       </c>
       <c r="J71" s="84">
-        <f>'заказ-order'!E358</f>
+        <f>'заказ-order'!E359</f>
         <v>0</v>
       </c>
       <c r="K71" s="130">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="L71" s="130">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M71" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A72" s="82">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72" s="87"/>
       <c r="C72" s="80" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D72" s="79">
         <v>0.26500000000000001</v>
@@ -15844,7 +15814,7 @@
         <v>0.22</v>
       </c>
       <c r="G72" s="89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="41"/>
         <v>1.17E-2</v>
       </c>
       <c r="H72" s="85">
@@ -15854,29 +15824,29 @@
         <v>6.84</v>
       </c>
       <c r="J72" s="84">
-        <f>'заказ-order'!E359</f>
+        <f>'заказ-order'!E360</f>
         <v>0</v>
       </c>
       <c r="K72" s="130">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="L72" s="130">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M72" s="83">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A73" s="82">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B73" s="87"/>
       <c r="C73" s="80" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D73" s="79">
         <v>0.26500000000000001</v>
@@ -15888,7 +15858,7 @@
         <v>0.22</v>
       </c>
       <c r="G73" s="89">
-        <f t="shared" si="45"/>
+        <f t="shared" si="41"/>
         <v>1.17E-2</v>
       </c>
       <c r="H73" s="85">
@@ -15902,25 +15872,25 @@
         <v>0</v>
       </c>
       <c r="K73" s="130">
-        <f t="shared" si="62"/>
+        <f t="shared" ref="K73" si="60">H73*J73</f>
         <v>0</v>
       </c>
       <c r="L73" s="130">
-        <f t="shared" si="6"/>
+        <f>I73*J73</f>
         <v>0</v>
       </c>
       <c r="M73" s="83">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M73" si="61">J73*D73*E73*F73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A74" s="82">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B74" s="87"/>
       <c r="C74" s="80" t="s">
-        <v>66</v>
+        <v>336</v>
       </c>
       <c r="D74" s="79">
         <v>0.26500000000000001</v>
@@ -15932,21 +15902,21 @@
         <v>0.22</v>
       </c>
       <c r="G74" s="89">
-        <f t="shared" si="45"/>
+        <f t="shared" si="41"/>
         <v>1.17E-2</v>
       </c>
       <c r="H74" s="85">
-        <v>7.04</v>
+        <v>6.58</v>
       </c>
       <c r="I74" s="85">
-        <v>6.84</v>
+        <v>6.42</v>
       </c>
       <c r="J74" s="84">
-        <f>'заказ-order'!E360</f>
+        <f>'заказ-order'!E361</f>
         <v>0</v>
       </c>
       <c r="K74" s="130">
-        <f t="shared" ref="K74" si="64">H74*J74</f>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="L74" s="130">
@@ -15954,82 +15924,45 @@
         <v>0</v>
       </c>
       <c r="M74" s="83">
-        <f t="shared" ref="M74" si="65">J74*D74*E74*F74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="82">
-        <v>72</v>
-      </c>
-      <c r="B75" s="87"/>
-      <c r="C75" s="80" t="s">
-        <v>336</v>
-      </c>
-      <c r="D75" s="79">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="E75" s="79">
-        <v>0.2</v>
-      </c>
-      <c r="F75" s="86">
-        <v>0.22</v>
-      </c>
-      <c r="G75" s="89">
-        <f t="shared" si="45"/>
-        <v>1.17E-2</v>
-      </c>
-      <c r="H75" s="85">
-        <v>6.58</v>
-      </c>
-      <c r="I75" s="85">
-        <v>6.42</v>
-      </c>
-      <c r="J75" s="84">
-        <f>'заказ-order'!E361</f>
-        <v>0</v>
-      </c>
-      <c r="K75" s="130">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="L75" s="130">
-        <f>I75*J75</f>
-        <v>0</v>
-      </c>
-      <c r="M75" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" s="82"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="80"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="79"/>
+      <c r="F75" s="79"/>
+      <c r="G75" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="H75" s="77"/>
+      <c r="I75" s="77"/>
+      <c r="J75" s="76">
+        <f>SUM(J3:J74)</f>
+        <v>0</v>
+      </c>
+      <c r="K75" s="131">
+        <f>SUM(K3:K74)</f>
+        <v>0</v>
+      </c>
+      <c r="L75" s="131">
+        <f>SUM(L3:L74)</f>
+        <v>0</v>
+      </c>
+      <c r="M75" s="76">
+        <f>SUM(M3:M74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" s="82"/>
-      <c r="B76" s="81"/>
-      <c r="C76" s="80"/>
-      <c r="D76" s="79"/>
-      <c r="E76" s="79"/>
-      <c r="F76" s="79"/>
-      <c r="G76" s="78" t="s">
-        <v>8</v>
-      </c>
-      <c r="H76" s="77"/>
-      <c r="I76" s="77"/>
-      <c r="J76" s="76" t="e">
-        <f>SUM(J3:J75)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K76" s="131" t="e">
-        <f>SUM(K3:K75)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L76" s="131" t="e">
-        <f>SUM(L3:L75)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M76" s="76" t="e">
-        <f>SUM(M3:M75)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="F76" s="74"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="71"/>
+      <c r="I76" s="71"/>
+      <c r="M76" s="70"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F77" s="74"/>
@@ -16038,29 +15971,22 @@
       <c r="I77" s="71"/>
       <c r="M77" s="70"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F78" s="74"/>
-      <c r="G78" s="73"/>
-      <c r="H78" s="71"/>
-      <c r="I78" s="71"/>
+    <row r="78" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F78" s="70"/>
+      <c r="G78" s="70"/>
+      <c r="H78" s="70"/>
+      <c r="I78" s="70"/>
+      <c r="J78" s="70"/>
+      <c r="K78" s="70"/>
+      <c r="L78" s="70"/>
       <c r="M78" s="70"/>
     </row>
-    <row r="79" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="F79" s="70"/>
-      <c r="G79" s="70"/>
-      <c r="H79" s="70"/>
-      <c r="I79" s="70"/>
-      <c r="J79" s="70"/>
-      <c r="K79" s="70"/>
-      <c r="L79" s="70"/>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F79" s="74"/>
+      <c r="G79" s="73"/>
+      <c r="H79" s="71"/>
+      <c r="I79" s="71"/>
       <c r="M79" s="70"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F80" s="74"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="71"/>
-      <c r="I80" s="71"/>
-      <c r="M80" s="70"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3997615-5A2B-4F31-9995-7ABA7253EF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9467FF5E-36E7-4A4C-B11C-0842AFFEB0B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="433">
   <si>
     <t>№ з/п</t>
   </si>
@@ -1333,6 +1333,9 @@
   </si>
   <si>
     <t xml:space="preserve">Шампун для волос 830 мл / Shampoo for hair 830 ml </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шампун для волос "Amfiora"  «Éclair» 830 мл / Shampoo for hair 830 ml </t>
   </si>
 </sst>
 </file>
@@ -8481,7 +8484,7 @@
         <v>431</v>
       </c>
       <c r="C203" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D203" s="8">
         <f>E203*C203</f>
@@ -12606,7 +12609,7 @@
       <c r="D370" s="12"/>
       <c r="E370" s="12"/>
       <c r="F370" s="132">
-        <f>'логист.данные  logistic dim'!K75</f>
+        <f>'логист.данные  logistic dim'!K76</f>
         <v>0</v>
       </c>
       <c r="G370" s="142"/>
@@ -12619,7 +12622,7 @@
       <c r="D371" s="12"/>
       <c r="E371" s="12"/>
       <c r="F371" s="132">
-        <f>'логист.данные  logistic dim'!L75</f>
+        <f>'логист.данные  logistic dim'!L76</f>
         <v>0</v>
       </c>
       <c r="G371" s="142"/>
@@ -12632,7 +12635,7 @@
       <c r="D372" s="12"/>
       <c r="E372" s="12"/>
       <c r="F372" s="63">
-        <f>'логист.данные  logistic dim'!M75</f>
+        <f>'логист.данные  logistic dim'!M76</f>
         <v>0</v>
       </c>
       <c r="G372" s="142"/>
@@ -12684,7 +12687,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.5546875" style="70" customWidth="1"/>
@@ -12840,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="130">
-        <f t="shared" ref="L4:L72" si="2">I4*J4</f>
+        <f t="shared" ref="L4:L73" si="2">I4*J4</f>
         <v>0</v>
       </c>
       <c r="M4" s="83">
@@ -12998,7 +13001,7 @@
         <v>0.255</v>
       </c>
       <c r="G8" s="89">
-        <f t="shared" ref="G8:G71" si="5">ROUND(D8*E8*F8,4)</f>
+        <f t="shared" ref="G8:G72" si="5">ROUND(D8*E8*F8,4)</f>
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="H8" s="85">
@@ -13012,15 +13015,15 @@
         <v>0</v>
       </c>
       <c r="K8" s="130">
-        <f t="shared" ref="K8:K58" si="6">H8*J8</f>
+        <f t="shared" ref="K8:K59" si="6">H8*J8</f>
         <v>0</v>
       </c>
       <c r="L8" s="130">
-        <f t="shared" ref="L8:L63" si="7">I8*J8</f>
+        <f t="shared" ref="L8:L64" si="7">I8*J8</f>
         <v>0</v>
       </c>
       <c r="M8" s="83">
-        <f t="shared" ref="M8:M67" si="8">J8*D8*E8*F8</f>
+        <f t="shared" ref="M8:M68" si="8">J8*D8*E8*F8</f>
         <v>0</v>
       </c>
     </row>
@@ -14037,100 +14040,98 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="82">
-        <v>30</v>
-      </c>
+      <c r="A32" s="82"/>
       <c r="B32" s="87"/>
       <c r="C32" s="80" t="s">
+        <v>432</v>
+      </c>
+      <c r="D32" s="79">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="E32" s="79">
+        <v>0.19</v>
+      </c>
+      <c r="F32" s="86">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="G32" s="89">
+        <f t="shared" ref="G32" si="37">ROUND(D32*E32*F32,4)</f>
+        <v>1.55E-2</v>
+      </c>
+      <c r="H32" s="85">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="I32" s="85">
+        <v>8.08</v>
+      </c>
+      <c r="J32" s="84">
+        <f>'заказ-order'!E203</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="130">
+        <f t="shared" ref="K32" si="38">H32*J32</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="130">
+        <f t="shared" ref="L32" si="39">I32*J32</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="83">
+        <f t="shared" ref="M32" si="40">J32*D32*E32*F32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="82">
+        <v>30</v>
+      </c>
+      <c r="B33" s="87"/>
+      <c r="C33" s="80" t="s">
         <v>194</v>
       </c>
-      <c r="D32" s="79">
+      <c r="D33" s="79">
         <v>0.315</v>
       </c>
-      <c r="E32" s="79">
+      <c r="E33" s="79">
         <v>0.31</v>
       </c>
-      <c r="F32" s="86">
+      <c r="F33" s="86">
         <v>0.18</v>
       </c>
-      <c r="G32" s="89">
+      <c r="G33" s="89">
         <f t="shared" si="5"/>
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="H32" s="85">
+      <c r="H33" s="85">
         <v>10.1</v>
       </c>
-      <c r="I32" s="85">
+      <c r="I33" s="85">
         <v>9.84</v>
       </c>
-      <c r="J32" s="84">
+      <c r="J33" s="84">
         <f>'заказ-order'!E204</f>
         <v>0</v>
       </c>
-      <c r="K32" s="130">
+      <c r="K33" s="130">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L32" s="130">
+      <c r="L33" s="130">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M32" s="83">
+      <c r="M33" s="83">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="82">
-        <v>31</v>
-      </c>
-      <c r="B33" s="87"/>
-      <c r="C33" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="D33" s="79">
-        <v>0.3</v>
-      </c>
-      <c r="E33" s="79">
-        <v>0.158</v>
-      </c>
-      <c r="F33" s="86">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="G33" s="89">
-        <f t="shared" ref="G33" si="37">ROUND(D33*E33*F33,4)</f>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="H33" s="85">
-        <v>3.7</v>
-      </c>
-      <c r="I33" s="85">
-        <v>3.58</v>
-      </c>
-      <c r="J33" s="84">
-        <f>'заказ-order'!E205</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="130">
-        <f t="shared" ref="K33" si="38">H33*J33</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="130">
-        <f t="shared" ref="L33" si="39">I33*J33</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="83">
-        <f t="shared" ref="M33" si="40">J33*D33*E33*F33</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A34" s="82">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="87"/>
       <c r="C34" s="80" t="s">
-        <v>195</v>
+        <v>380</v>
       </c>
       <c r="D34" s="79">
         <v>0.3</v>
@@ -14142,105 +14143,105 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G34" s="89">
+        <f t="shared" ref="G34" si="41">ROUND(D34*E34*F34,4)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H34" s="85">
+        <v>3.7</v>
+      </c>
+      <c r="I34" s="85">
+        <v>3.58</v>
+      </c>
+      <c r="J34" s="84">
+        <f>'заказ-order'!E205</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="130">
+        <f t="shared" ref="K34" si="42">H34*J34</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="130">
+        <f t="shared" ref="L34" si="43">I34*J34</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="83">
+        <f t="shared" ref="M34" si="44">J34*D34*E34*F34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="82">
+        <v>32</v>
+      </c>
+      <c r="B35" s="87"/>
+      <c r="C35" s="80" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="79">
+        <v>0.3</v>
+      </c>
+      <c r="E35" s="79">
+        <v>0.158</v>
+      </c>
+      <c r="F35" s="86">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="G35" s="89">
         <f t="shared" si="5"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H34" s="85">
+      <c r="H35" s="85">
         <v>3.18</v>
       </c>
-      <c r="I34" s="85">
+      <c r="I35" s="85">
         <v>3.04</v>
       </c>
-      <c r="J34" s="84">
+      <c r="J35" s="84">
         <f>'заказ-order'!E206</f>
         <v>0</v>
       </c>
-      <c r="K34" s="130">
+      <c r="K35" s="130">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L34" s="130">
+      <c r="L35" s="130">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M34" s="83">
+      <c r="M35" s="83">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="82">
+    <row r="36" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="82">
         <v>33</v>
       </c>
-      <c r="B35" s="87"/>
-      <c r="C35" s="80" t="s">
+      <c r="B36" s="87"/>
+      <c r="C36" s="80" t="s">
         <v>196</v>
       </c>
-      <c r="D35" s="79">
+      <c r="D36" s="79">
         <v>0.316</v>
       </c>
-      <c r="E35" s="79">
+      <c r="E36" s="79">
         <v>0.19</v>
       </c>
-      <c r="F35" s="86">
+      <c r="F36" s="86">
         <v>0.17699999999999999</v>
       </c>
-      <c r="G35" s="89">
+      <c r="G36" s="89">
         <f t="shared" si="5"/>
         <v>1.06E-2</v>
       </c>
-      <c r="H35" s="85">
+      <c r="H36" s="85">
         <v>2.72</v>
       </c>
-      <c r="I35" s="85">
+      <c r="I36" s="85">
         <v>2.56</v>
       </c>
-      <c r="J35" s="84">
+      <c r="J36" s="84">
         <f>'заказ-order'!E207</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="130">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="83">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="82">
-        <v>34</v>
-      </c>
-      <c r="B36" s="87"/>
-      <c r="C36" s="80" t="s">
-        <v>197</v>
-      </c>
-      <c r="D36" s="79">
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="E36" s="79">
-        <v>0.215</v>
-      </c>
-      <c r="F36" s="86">
-        <v>0.18</v>
-      </c>
-      <c r="G36" s="89">
-        <f t="shared" si="5"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="H36" s="85">
-        <v>6.62</v>
-      </c>
-      <c r="I36" s="85">
-        <v>6.4</v>
-      </c>
-      <c r="J36" s="84">
-        <f>'заказ-order'!E208</f>
         <v>0</v>
       </c>
       <c r="K36" s="130">
@@ -14258,11 +14259,11 @@
     </row>
     <row r="37" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A37" s="82">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="87"/>
       <c r="C37" s="80" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D37" s="79">
         <v>0.28499999999999998</v>
@@ -14284,7 +14285,7 @@
         <v>6.4</v>
       </c>
       <c r="J37" s="84">
-        <f>'заказ-order'!E209</f>
+        <f>'заказ-order'!E208</f>
         <v>0</v>
       </c>
       <c r="K37" s="130">
@@ -14300,35 +14301,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A38" s="82">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="87"/>
       <c r="C38" s="80" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D38" s="79">
-        <v>0.215</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="E38" s="79">
         <v>0.215</v>
       </c>
       <c r="F38" s="86">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="G38" s="89">
         <f t="shared" si="5"/>
-        <v>6.8999999999999999E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H38" s="85">
-        <v>3.7</v>
+        <v>6.62</v>
       </c>
       <c r="I38" s="85">
-        <v>3.52</v>
+        <v>6.4</v>
       </c>
       <c r="J38" s="84">
-        <f>'заказ-order'!E210</f>
+        <f>'заказ-order'!E209</f>
         <v>0</v>
       </c>
       <c r="K38" s="130">
@@ -14344,35 +14345,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A39" s="82">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="87"/>
       <c r="C39" s="80" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D39" s="79">
-        <v>0.29499999999999998</v>
+        <v>0.215</v>
       </c>
       <c r="E39" s="79">
-        <v>0.16</v>
+        <v>0.215</v>
       </c>
       <c r="F39" s="86">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="G39" s="89">
         <f t="shared" si="5"/>
-        <v>1.18E-2</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="H39" s="85">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="I39" s="85">
-        <v>7.04</v>
+        <v>3.52</v>
       </c>
       <c r="J39" s="84">
-        <f>'заказ-order'!E213</f>
+        <f>'заказ-order'!E210</f>
         <v>0</v>
       </c>
       <c r="K39" s="130">
@@ -14390,121 +14391,121 @@
     </row>
     <row r="40" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A40" s="82">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="87"/>
       <c r="C40" s="80" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D40" s="79">
-        <v>0.3</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="E40" s="79">
-        <v>0.17799999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="F40" s="86">
-        <v>0.191</v>
+        <v>0.25</v>
       </c>
       <c r="G40" s="89">
-        <f>ROUND(D40*E40*F40,4)</f>
-        <v>1.0200000000000001E-2</v>
+        <f t="shared" si="5"/>
+        <v>1.18E-2</v>
       </c>
       <c r="H40" s="85">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="I40" s="85">
-        <v>5.46</v>
+        <v>7.04</v>
       </c>
       <c r="J40" s="84">
-        <f>'заказ-order'!E214</f>
+        <f>'заказ-order'!E213</f>
         <v>0</v>
       </c>
       <c r="K40" s="130">
-        <f>H40*J40</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L40" s="130">
-        <f>I40*J40</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M40" s="83">
-        <f>J40*D40*E40*F40</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A41" s="82">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="87"/>
       <c r="C41" s="80" t="s">
+        <v>202</v>
+      </c>
+      <c r="D41" s="79">
+        <v>0.3</v>
+      </c>
+      <c r="E41" s="79">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="F41" s="86">
+        <v>0.191</v>
+      </c>
+      <c r="G41" s="89">
+        <f>ROUND(D41*E41*F41,4)</f>
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="H41" s="85">
+        <v>5.6</v>
+      </c>
+      <c r="I41" s="85">
+        <v>5.46</v>
+      </c>
+      <c r="J41" s="84">
+        <f>'заказ-order'!E214</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="130">
+        <f>H41*J41</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="130">
+        <f>I41*J41</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="83">
+        <f>J41*D41*E41*F41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="82">
+        <v>39</v>
+      </c>
+      <c r="B42" s="87"/>
+      <c r="C42" s="80" t="s">
         <v>201</v>
       </c>
-      <c r="D41" s="79">
+      <c r="D42" s="79">
         <v>0.29499999999999998</v>
       </c>
-      <c r="E41" s="79">
+      <c r="E42" s="79">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F41" s="86">
+      <c r="F42" s="86">
         <v>0.2</v>
       </c>
-      <c r="G41" s="89">
+      <c r="G42" s="89">
         <f t="shared" si="5"/>
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="H41" s="85">
+      <c r="H42" s="85">
         <v>4.62</v>
       </c>
-      <c r="I41" s="85">
+      <c r="I42" s="85">
         <v>4.4800000000000004</v>
       </c>
-      <c r="J41" s="84">
+      <c r="J42" s="84">
         <f>'заказ-order'!E215</f>
-        <v>0</v>
-      </c>
-      <c r="K41" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L41" s="130">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="83">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="82">
-        <v>40</v>
-      </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="80" t="s">
-        <v>203</v>
-      </c>
-      <c r="D42" s="79">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="E42" s="79">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="F42" s="86">
-        <v>0.15</v>
-      </c>
-      <c r="G42" s="89">
-        <f>ROUND(D42*E42*F42,4)</f>
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="H42" s="85">
-        <v>3.44</v>
-      </c>
-      <c r="I42" s="85">
-        <v>3.3200000000000003</v>
-      </c>
-      <c r="J42" s="84">
-        <f>'заказ-order'!E216</f>
         <v>0</v>
       </c>
       <c r="K42" s="130">
@@ -14520,35 +14521,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A43" s="82">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="87"/>
       <c r="C43" s="80" t="s">
-        <v>232</v>
-      </c>
-      <c r="D43" s="88">
-        <v>0.26300000000000001</v>
-      </c>
-      <c r="E43" s="88">
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="F43" s="85">
-        <v>0.157</v>
+        <v>203</v>
+      </c>
+      <c r="D43" s="79">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E43" s="79">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="F43" s="86">
+        <v>0.15</v>
       </c>
       <c r="G43" s="89">
         <f>ROUND(D43*E43*F43,4)</f>
-        <v>7.1999999999999998E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="H43" s="85">
-        <v>3.27</v>
+        <v>3.44</v>
       </c>
       <c r="I43" s="85">
-        <v>3.1440000000000001</v>
+        <v>3.3200000000000003</v>
       </c>
       <c r="J43" s="84">
-        <f>'заказ-order'!E218</f>
+        <f>'заказ-order'!E216</f>
         <v>0</v>
       </c>
       <c r="K43" s="130">
@@ -14556,135 +14557,135 @@
         <v>0</v>
       </c>
       <c r="L43" s="130">
-        <f>I43*J43</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M43" s="83">
-        <f>J43*D43*E43*F43</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A44" s="82">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="87"/>
       <c r="C44" s="80" t="s">
-        <v>324</v>
-      </c>
-      <c r="D44" s="79">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="E44" s="79">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="F44" s="86">
-        <v>0.19</v>
+        <v>232</v>
+      </c>
+      <c r="D44" s="88">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="E44" s="88">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="F44" s="85">
+        <v>0.157</v>
       </c>
       <c r="G44" s="89">
-        <f t="shared" ref="G44:G74" si="41">ROUND(D44*E44*F44,4)</f>
-        <v>9.1000000000000004E-3</v>
-      </c>
-      <c r="H44" s="86">
-        <v>5.3</v>
-      </c>
-      <c r="I44" s="86">
-        <v>5.16</v>
+        <f>ROUND(D44*E44*F44,4)</f>
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="H44" s="85">
+        <v>3.27</v>
+      </c>
+      <c r="I44" s="85">
+        <v>3.1440000000000001</v>
       </c>
       <c r="J44" s="84">
-        <f>'заказ-order'!E220</f>
+        <f>'заказ-order'!E218</f>
         <v>0</v>
       </c>
       <c r="K44" s="130">
-        <f t="shared" ref="K44" si="42">H44*J44</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L44" s="130">
-        <f t="shared" ref="L44" si="43">I44*J44</f>
+        <f>I44*J44</f>
         <v>0</v>
       </c>
       <c r="M44" s="83">
-        <f t="shared" ref="M44" si="44">J44*D44*E44*F44</f>
+        <f>J44*D44*E44*F44</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A45" s="82">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="87"/>
       <c r="C45" s="80" t="s">
+        <v>324</v>
+      </c>
+      <c r="D45" s="79">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="E45" s="79">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="F45" s="86">
+        <v>0.19</v>
+      </c>
+      <c r="G45" s="89">
+        <f t="shared" ref="G45:G75" si="45">ROUND(D45*E45*F45,4)</f>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="H45" s="86">
+        <v>5.3</v>
+      </c>
+      <c r="I45" s="86">
+        <v>5.16</v>
+      </c>
+      <c r="J45" s="84">
+        <f>'заказ-order'!E220</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="130">
+        <f t="shared" ref="K45" si="46">H45*J45</f>
+        <v>0</v>
+      </c>
+      <c r="L45" s="130">
+        <f t="shared" ref="L45" si="47">I45*J45</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="83">
+        <f t="shared" ref="M45" si="48">J45*D45*E45*F45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="82">
+        <v>43</v>
+      </c>
+      <c r="B46" s="87"/>
+      <c r="C46" s="80" t="s">
         <v>204</v>
       </c>
-      <c r="D45" s="79">
+      <c r="D46" s="79">
         <v>0.27500000000000002</v>
       </c>
-      <c r="E45" s="79">
+      <c r="E46" s="79">
         <v>0.17</v>
       </c>
-      <c r="F45" s="86">
+      <c r="F46" s="86">
         <v>0.155</v>
       </c>
-      <c r="G45" s="89">
+      <c r="G46" s="89">
         <f t="shared" si="5"/>
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="H45" s="86">
+      <c r="H46" s="86">
         <v>4.0599999999999996</v>
       </c>
-      <c r="I45" s="86">
+      <c r="I46" s="86">
         <v>3.94</v>
       </c>
-      <c r="J45" s="84">
+      <c r="J46" s="84">
         <f>'заказ-order'!E226</f>
         <v>0</v>
       </c>
-      <c r="K45" s="130">
+      <c r="K46" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L45" s="130">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="83">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="82">
-        <v>44</v>
-      </c>
-      <c r="B46" s="87"/>
-      <c r="C46" s="80" t="s">
-        <v>291</v>
-      </c>
-      <c r="D46" s="79">
-        <v>0.24</v>
-      </c>
-      <c r="E46" s="79">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="F46" s="86">
-        <v>0.193</v>
-      </c>
-      <c r="G46" s="89">
-        <f t="shared" si="41"/>
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="H46" s="86">
-        <v>3.67</v>
-      </c>
-      <c r="I46" s="86">
-        <v>3.57</v>
-      </c>
-      <c r="J46" s="84">
-        <f>'заказ-order'!E221</f>
-        <v>0</v>
-      </c>
-      <c r="K46" s="130">
-        <f t="shared" ref="K46:K54" si="45">H46*J46</f>
         <v>0</v>
       </c>
       <c r="L46" s="130">
@@ -14696,519 +14697,519 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A47" s="82">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" s="87"/>
       <c r="C47" s="80" t="s">
+        <v>291</v>
+      </c>
+      <c r="D47" s="79">
+        <v>0.24</v>
+      </c>
+      <c r="E47" s="79">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="F47" s="86">
+        <v>0.193</v>
+      </c>
+      <c r="G47" s="89">
+        <f t="shared" si="45"/>
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="H47" s="86">
+        <v>3.67</v>
+      </c>
+      <c r="I47" s="86">
+        <v>3.57</v>
+      </c>
+      <c r="J47" s="84">
+        <f>'заказ-order'!E221</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="130">
+        <f t="shared" ref="K47:K55" si="49">H47*J47</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="130">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="83">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="82">
+        <v>45</v>
+      </c>
+      <c r="B48" s="87"/>
+      <c r="C48" s="80" t="s">
         <v>246</v>
       </c>
-      <c r="D47" s="79">
+      <c r="D48" s="79">
         <v>0.23499999999999999</v>
       </c>
-      <c r="E47" s="79">
+      <c r="E48" s="79">
         <v>0.19700000000000001</v>
       </c>
-      <c r="F47" s="86">
+      <c r="F48" s="86">
         <v>0.16500000000000001</v>
       </c>
-      <c r="G47" s="89">
+      <c r="G48" s="89">
         <f t="shared" si="5"/>
         <v>7.6E-3</v>
       </c>
-      <c r="H47" s="86">
+      <c r="H48" s="86">
         <v>3.42</v>
       </c>
-      <c r="I47" s="86">
+      <c r="I48" s="86">
         <v>3.27</v>
       </c>
-      <c r="J47" s="84">
+      <c r="J48" s="84">
         <f>'заказ-order'!E223</f>
         <v>0</v>
       </c>
-      <c r="K47" s="130">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L47" s="130">
+      <c r="K48" s="130">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="130">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M47" s="83">
+      <c r="M48" s="83">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="82">
+    <row r="49" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="82">
         <v>46</v>
-      </c>
-      <c r="B48" s="87"/>
-      <c r="C48" s="80" t="s">
-        <v>424</v>
-      </c>
-      <c r="D48" s="79">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="E48" s="79">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="F48" s="86">
-        <v>0.18</v>
-      </c>
-      <c r="G48" s="89">
-        <f t="shared" si="41"/>
-        <v>1.0699999999999999E-2</v>
-      </c>
-      <c r="H48" s="86">
-        <v>5.1230000000000002</v>
-      </c>
-      <c r="I48" s="86">
-        <v>4.9320000000000004</v>
-      </c>
-      <c r="J48" s="84">
-        <f>'заказ-order'!E229</f>
-        <v>0</v>
-      </c>
-      <c r="K48" s="130">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="130">
-        <f t="shared" ref="L48:L54" si="46">I48*J48</f>
-        <v>0</v>
-      </c>
-      <c r="M48" s="83">
-        <f t="shared" ref="M48:M54" si="47">J48*D48*E48*F48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="82">
-        <v>47</v>
       </c>
       <c r="B49" s="87"/>
       <c r="C49" s="80" t="s">
+        <v>424</v>
+      </c>
+      <c r="D49" s="79">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="E49" s="79">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="F49" s="86">
+        <v>0.18</v>
+      </c>
+      <c r="G49" s="89">
+        <f t="shared" si="45"/>
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="H49" s="86">
+        <v>5.1230000000000002</v>
+      </c>
+      <c r="I49" s="86">
+        <v>4.9320000000000004</v>
+      </c>
+      <c r="J49" s="84">
+        <f>'заказ-order'!E229</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="130">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="130">
+        <f t="shared" ref="L49:L55" si="50">I49*J49</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="83">
+        <f t="shared" ref="M49:M55" si="51">J49*D49*E49*F49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="82">
+        <v>47</v>
+      </c>
+      <c r="B50" s="87"/>
+      <c r="C50" s="80" t="s">
         <v>423</v>
       </c>
-      <c r="D49" s="79">
+      <c r="D50" s="79">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E49" s="79">
+      <c r="E50" s="79">
         <v>0.18</v>
       </c>
-      <c r="F49" s="86">
+      <c r="F50" s="86">
         <v>0.17</v>
       </c>
-      <c r="G49" s="89">
+      <c r="G50" s="89">
         <f t="shared" si="5"/>
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="H49" s="86">
+      <c r="H50" s="86">
         <v>3.78</v>
       </c>
-      <c r="I49" s="86">
+      <c r="I50" s="86">
         <v>3.64</v>
       </c>
-      <c r="J49" s="84">
+      <c r="J50" s="84">
         <f>'заказ-order'!E224</f>
         <v>0</v>
       </c>
-      <c r="K49" s="130">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L49" s="130">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="83">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="82">
+      <c r="K50" s="130">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="130">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="83">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="82">
         <v>48</v>
-      </c>
-      <c r="B50" s="87"/>
-      <c r="C50" s="80" t="s">
-        <v>422</v>
-      </c>
-      <c r="D50" s="79">
-        <v>0.255</v>
-      </c>
-      <c r="E50" s="79">
-        <v>0.185</v>
-      </c>
-      <c r="F50" s="86">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="G50" s="89">
-        <f t="shared" si="41"/>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="H50" s="86">
-        <v>2.48</v>
-      </c>
-      <c r="I50" s="86">
-        <v>2.359</v>
-      </c>
-      <c r="J50" s="84">
-        <f>'заказ-order'!E226</f>
-        <v>0</v>
-      </c>
-      <c r="K50" s="130">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="130">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="83">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="82">
-        <v>49</v>
       </c>
       <c r="B51" s="87"/>
       <c r="C51" s="80" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D51" s="79">
-        <v>0.26500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="E51" s="79">
-        <v>0.20699999999999999</v>
+        <v>0.185</v>
       </c>
       <c r="F51" s="86">
         <v>0.13500000000000001</v>
       </c>
       <c r="G51" s="89">
+        <f t="shared" si="45"/>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="H51" s="86">
+        <v>2.48</v>
+      </c>
+      <c r="I51" s="86">
+        <v>2.359</v>
+      </c>
+      <c r="J51" s="84">
+        <f>'заказ-order'!E226</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="130">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="130">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M51" s="83">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="82">
+        <v>49</v>
+      </c>
+      <c r="B52" s="87"/>
+      <c r="C52" s="80" t="s">
+        <v>421</v>
+      </c>
+      <c r="D52" s="79">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="E52" s="79">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="F52" s="86">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="G52" s="89">
         <f t="shared" si="5"/>
         <v>7.4000000000000003E-3</v>
       </c>
-      <c r="H51" s="86">
+      <c r="H52" s="86">
         <v>3.04</v>
       </c>
-      <c r="I51" s="86">
+      <c r="I52" s="86">
         <v>2.9039999999999999</v>
       </c>
-      <c r="J51" s="84">
+      <c r="J52" s="84">
         <f>'заказ-order'!E232</f>
         <v>0</v>
       </c>
-      <c r="K51" s="130">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="130">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="83">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="82">
-        <v>50</v>
-      </c>
-      <c r="B52" s="87"/>
-      <c r="C52" s="80" t="s">
-        <v>420</v>
-      </c>
-      <c r="D52" s="79">
-        <v>0.25800000000000001</v>
-      </c>
-      <c r="E52" s="79">
-        <v>0.17</v>
-      </c>
-      <c r="F52" s="86">
-        <v>0.188</v>
-      </c>
-      <c r="G52" s="89">
-        <f t="shared" si="41"/>
-        <v>8.2000000000000007E-3</v>
-      </c>
-      <c r="H52" s="86">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="I52" s="86">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="J52" s="84">
-        <f>'заказ-order'!E227</f>
-        <v>0</v>
-      </c>
       <c r="K52" s="130">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L52" s="130">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M52" s="83">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A53" s="82">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B53" s="87"/>
       <c r="C53" s="80" t="s">
+        <v>420</v>
+      </c>
+      <c r="D53" s="79">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="E53" s="79">
+        <v>0.17</v>
+      </c>
+      <c r="F53" s="86">
+        <v>0.188</v>
+      </c>
+      <c r="G53" s="89">
+        <f t="shared" si="45"/>
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="H53" s="86">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="I53" s="86">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="J53" s="84">
+        <f>'заказ-order'!E227</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="130">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="130">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M53" s="83">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="82">
+        <v>51</v>
+      </c>
+      <c r="B54" s="87"/>
+      <c r="C54" s="80" t="s">
         <v>311</v>
       </c>
-      <c r="D53" s="79">
+      <c r="D54" s="79">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E53" s="79">
+      <c r="E54" s="79">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F53" s="86">
+      <c r="F54" s="86">
         <v>0.26400000000000001</v>
       </c>
-      <c r="G53" s="89">
+      <c r="G54" s="89">
         <f t="shared" si="5"/>
         <v>1.34E-2</v>
       </c>
-      <c r="H53" s="85">
+      <c r="H54" s="85">
         <v>6.82</v>
       </c>
-      <c r="I53" s="85">
+      <c r="I54" s="85">
         <v>6.66</v>
       </c>
-      <c r="J53" s="84">
+      <c r="J54" s="84">
         <f>'заказ-order'!E249</f>
         <v>0</v>
       </c>
-      <c r="K53" s="130">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="130">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="M53" s="83">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="82">
-        <v>52</v>
-      </c>
-      <c r="B54" s="87"/>
-      <c r="C54" s="80" t="s">
-        <v>425</v>
-      </c>
-      <c r="D54" s="79">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="E54" s="79">
-        <v>0.17199999999999999</v>
-      </c>
-      <c r="F54" s="86">
-        <v>0.17</v>
-      </c>
-      <c r="G54" s="89">
-        <f t="shared" si="41"/>
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="H54" s="85">
-        <v>2.3340000000000001</v>
-      </c>
-      <c r="I54" s="85">
-        <v>2.2080000000000002</v>
-      </c>
-      <c r="J54" s="84">
-        <f>'заказ-order'!E235</f>
-        <v>0</v>
-      </c>
       <c r="K54" s="130">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L54" s="130">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M54" s="83">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A55" s="82">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55" s="87"/>
       <c r="C55" s="80" t="s">
+        <v>425</v>
+      </c>
+      <c r="D55" s="79">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="E55" s="79">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="F55" s="86">
+        <v>0.17</v>
+      </c>
+      <c r="G55" s="89">
+        <f t="shared" si="45"/>
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="H55" s="85">
+        <v>2.3340000000000001</v>
+      </c>
+      <c r="I55" s="85">
+        <v>2.2080000000000002</v>
+      </c>
+      <c r="J55" s="84">
+        <f>'заказ-order'!E235</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="130">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="130">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="M55" s="83">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="82">
+        <v>53</v>
+      </c>
+      <c r="B56" s="87"/>
+      <c r="C56" s="80" t="s">
         <v>426</v>
       </c>
-      <c r="D55" s="79">
+      <c r="D56" s="79">
         <v>0.25</v>
       </c>
-      <c r="E55" s="79">
+      <c r="E56" s="79">
         <v>0.19</v>
       </c>
-      <c r="F55" s="86">
+      <c r="F56" s="86">
         <v>0.13500000000000001</v>
       </c>
-      <c r="G55" s="89">
+      <c r="G56" s="89">
         <f t="shared" si="5"/>
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="H55" s="85">
+      <c r="H56" s="85">
         <v>1.6759999999999999</v>
       </c>
-      <c r="I55" s="85">
+      <c r="I56" s="85">
         <v>1.536</v>
       </c>
-      <c r="J55" s="84">
+      <c r="J56" s="84">
         <f>'заказ-order'!E268</f>
         <v>0</v>
       </c>
-      <c r="K55" s="130">
-        <f>H55*J55</f>
-        <v>0</v>
-      </c>
-      <c r="L55" s="130">
-        <f>I55*J55</f>
-        <v>0</v>
-      </c>
-      <c r="M55" s="83">
-        <f>J55*D55*E55*F55</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="82">
+      <c r="K56" s="130">
+        <f>H56*J56</f>
+        <v>0</v>
+      </c>
+      <c r="L56" s="130">
+        <f>I56*J56</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="83">
+        <f>J56*D56*E56*F56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="82">
         <v>54</v>
-      </c>
-      <c r="B56" s="87"/>
-      <c r="C56" s="80" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="79">
-        <v>0.255</v>
-      </c>
-      <c r="E56" s="79">
-        <v>0.13</v>
-      </c>
-      <c r="F56" s="86">
-        <v>0.16</v>
-      </c>
-      <c r="G56" s="89">
-        <f t="shared" si="41"/>
-        <v>5.3E-3</v>
-      </c>
-      <c r="H56" s="86">
-        <v>2.58</v>
-      </c>
-      <c r="I56" s="86">
-        <v>2.5</v>
-      </c>
-      <c r="J56" s="84">
-        <f>'заказ-order'!E273</f>
-        <v>0</v>
-      </c>
-      <c r="K56" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L56" s="130">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M56" s="83">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="82">
-        <v>55</v>
       </c>
       <c r="B57" s="87"/>
       <c r="C57" s="80" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57" s="79">
+        <v>0.255</v>
+      </c>
+      <c r="E57" s="79">
+        <v>0.13</v>
+      </c>
+      <c r="F57" s="86">
+        <v>0.16</v>
+      </c>
+      <c r="G57" s="89">
+        <f t="shared" si="45"/>
+        <v>5.3E-3</v>
+      </c>
+      <c r="H57" s="86">
+        <v>2.58</v>
+      </c>
+      <c r="I57" s="86">
+        <v>2.5</v>
+      </c>
+      <c r="J57" s="84">
+        <f>'заказ-order'!E273</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="130">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="83">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A58" s="82">
+        <v>55</v>
+      </c>
+      <c r="B58" s="87"/>
+      <c r="C58" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="D57" s="79">
+      <c r="D58" s="79">
         <v>0.315</v>
       </c>
-      <c r="E57" s="79">
+      <c r="E58" s="79">
         <v>0.187</v>
       </c>
-      <c r="F57" s="86">
+      <c r="F58" s="86">
         <v>0.21199999999999999</v>
       </c>
-      <c r="G57" s="89">
+      <c r="G58" s="89">
         <f t="shared" si="5"/>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="H57" s="86">
+      <c r="H58" s="86">
         <v>3.54</v>
       </c>
-      <c r="I57" s="86">
+      <c r="I58" s="86">
         <v>3.38</v>
       </c>
-      <c r="J57" s="84">
+      <c r="J58" s="84">
         <f>'заказ-order'!E285</f>
-        <v>0</v>
-      </c>
-      <c r="K57" s="130">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L57" s="130">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="83">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="82">
-        <v>56</v>
-      </c>
-      <c r="B58" s="87"/>
-      <c r="C58" s="80" t="s">
-        <v>188</v>
-      </c>
-      <c r="D58" s="79">
-        <v>0.31</v>
-      </c>
-      <c r="E58" s="79">
-        <v>0.21</v>
-      </c>
-      <c r="F58" s="86">
-        <v>0.16900000000000001</v>
-      </c>
-      <c r="G58" s="89">
-        <f t="shared" si="41"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="H58" s="86">
-        <v>3.08</v>
-      </c>
-      <c r="I58" s="86">
-        <v>2.92</v>
-      </c>
-      <c r="J58" s="84">
-        <f>'заказ-order'!E289</f>
         <v>0</v>
       </c>
       <c r="K58" s="130">
@@ -15226,169 +15227,169 @@
     </row>
     <row r="59" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A59" s="82">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="87"/>
       <c r="C59" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" s="79">
+        <v>0.31</v>
+      </c>
+      <c r="E59" s="79">
+        <v>0.21</v>
+      </c>
+      <c r="F59" s="86">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="G59" s="89">
+        <f t="shared" si="45"/>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="H59" s="86">
+        <v>3.08</v>
+      </c>
+      <c r="I59" s="86">
+        <v>2.92</v>
+      </c>
+      <c r="J59" s="84">
+        <f>'заказ-order'!E289</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="130">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M59" s="83">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="82">
+        <v>57</v>
+      </c>
+      <c r="B60" s="87"/>
+      <c r="C60" s="80" t="s">
         <v>183</v>
       </c>
-      <c r="D59" s="79">
+      <c r="D60" s="79">
         <v>0.39400000000000002</v>
       </c>
-      <c r="E59" s="79">
+      <c r="E60" s="79">
         <v>0.23</v>
       </c>
-      <c r="F59" s="86">
+      <c r="F60" s="86">
         <v>0.18</v>
       </c>
-      <c r="G59" s="89">
+      <c r="G60" s="89">
         <f t="shared" si="5"/>
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="H59" s="86">
+      <c r="H60" s="86">
         <v>8.26</v>
       </c>
-      <c r="I59" s="86">
+      <c r="I60" s="86">
         <v>7.9</v>
       </c>
-      <c r="J59" s="84">
+      <c r="J60" s="84">
         <f>'заказ-order'!E294</f>
         <v>0</v>
       </c>
-      <c r="K59" s="130">
-        <f t="shared" ref="K59" si="48">H59*J59</f>
-        <v>0</v>
-      </c>
-      <c r="L59" s="130">
+      <c r="K60" s="130">
+        <f t="shared" ref="K60" si="52">H60*J60</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="130">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M59" s="83">
+      <c r="M60" s="83">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="82">
+    <row r="61" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="82">
         <v>58</v>
-      </c>
-      <c r="B60" s="87"/>
-      <c r="C60" s="80" t="s">
-        <v>429</v>
-      </c>
-      <c r="D60" s="79">
-        <v>0.27</v>
-      </c>
-      <c r="E60" s="79">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="F60" s="86">
-        <v>0.25800000000000001</v>
-      </c>
-      <c r="G60" s="89">
-        <f t="shared" si="41"/>
-        <v>1.3599999999999999E-2</v>
-      </c>
-      <c r="H60" s="86">
-        <v>7.4279999999999999</v>
-      </c>
-      <c r="I60" s="86">
-        <v>7.2560000000000002</v>
-      </c>
-      <c r="J60" s="84">
-        <f>'заказ-order'!E301</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="130">
-        <f t="shared" ref="K60" si="49">H60*J60</f>
-        <v>0</v>
-      </c>
-      <c r="L60" s="130">
-        <f t="shared" ref="L60" si="50">I60*J60</f>
-        <v>0</v>
-      </c>
-      <c r="M60" s="83">
-        <f t="shared" ref="M60" si="51">J60*D60*E60*F60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="82">
-        <v>59</v>
       </c>
       <c r="B61" s="87"/>
       <c r="C61" s="80" t="s">
+        <v>429</v>
+      </c>
+      <c r="D61" s="79">
+        <v>0.27</v>
+      </c>
+      <c r="E61" s="79">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="F61" s="86">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="G61" s="89">
+        <f t="shared" si="45"/>
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="H61" s="86">
+        <v>7.4279999999999999</v>
+      </c>
+      <c r="I61" s="86">
+        <v>7.2560000000000002</v>
+      </c>
+      <c r="J61" s="84">
+        <f>'заказ-order'!E301</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="130">
+        <f t="shared" ref="K61" si="53">H61*J61</f>
+        <v>0</v>
+      </c>
+      <c r="L61" s="130">
+        <f t="shared" ref="L61" si="54">I61*J61</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="83">
+        <f t="shared" ref="M61" si="55">J61*D61*E61*F61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="82">
+        <v>59</v>
+      </c>
+      <c r="B62" s="87"/>
+      <c r="C62" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="D61" s="79">
+      <c r="D62" s="79">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E61" s="79">
+      <c r="E62" s="79">
         <v>0.17699999999999999</v>
       </c>
-      <c r="F61" s="86">
+      <c r="F62" s="86">
         <v>0.13500000000000001</v>
       </c>
-      <c r="G61" s="89">
+      <c r="G62" s="89">
         <f t="shared" si="5"/>
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="H61" s="86">
+      <c r="H62" s="86">
         <v>6.92</v>
       </c>
-      <c r="I61" s="86">
+      <c r="I62" s="86">
         <v>6.76</v>
       </c>
-      <c r="J61" s="84">
+      <c r="J62" s="84">
         <f>'заказ-order'!E313</f>
         <v>0</v>
       </c>
-      <c r="K61" s="130">
-        <f t="shared" ref="K61:K68" si="52">H61*J61</f>
-        <v>0</v>
-      </c>
-      <c r="L61" s="130">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M61" s="83">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="82">
-        <v>60</v>
-      </c>
-      <c r="B62" s="87"/>
-      <c r="C62" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="D62" s="79">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="E62" s="79">
-        <v>0.18</v>
-      </c>
-      <c r="F62" s="86">
-        <v>0.185</v>
-      </c>
-      <c r="G62" s="89">
-        <f t="shared" si="41"/>
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="H62" s="86">
-        <v>6.9</v>
-      </c>
-      <c r="I62" s="86">
-        <v>6.74</v>
-      </c>
-      <c r="J62" s="84">
-        <f>'заказ-order'!E315</f>
-        <v>0</v>
-      </c>
       <c r="K62" s="130">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="K62:K69" si="56">H62*J62</f>
         <v>0</v>
       </c>
       <c r="L62" s="130">
@@ -15402,85 +15403,85 @@
     </row>
     <row r="63" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A63" s="82">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B63" s="87"/>
       <c r="C63" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" s="79">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="E63" s="79">
+        <v>0.18</v>
+      </c>
+      <c r="F63" s="86">
+        <v>0.185</v>
+      </c>
+      <c r="G63" s="89">
+        <f t="shared" si="45"/>
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="H63" s="86">
+        <v>6.9</v>
+      </c>
+      <c r="I63" s="86">
+        <v>6.74</v>
+      </c>
+      <c r="J63" s="84">
+        <f>'заказ-order'!E315</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="130">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="L63" s="130">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M63" s="83">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="82">
+        <v>61</v>
+      </c>
+      <c r="B64" s="87"/>
+      <c r="C64" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D63" s="79">
+      <c r="D64" s="79">
         <v>0.33500000000000002</v>
       </c>
-      <c r="E63" s="79">
+      <c r="E64" s="79">
         <v>0.2</v>
       </c>
-      <c r="F63" s="86">
+      <c r="F64" s="86">
         <v>0.15</v>
       </c>
-      <c r="G63" s="89">
+      <c r="G64" s="89">
         <f t="shared" si="5"/>
         <v>1.01E-2</v>
       </c>
-      <c r="H63" s="86">
+      <c r="H64" s="86">
         <v>6.89</v>
       </c>
-      <c r="I63" s="86">
+      <c r="I64" s="86">
         <v>6.72</v>
       </c>
-      <c r="J63" s="84">
+      <c r="J64" s="84">
         <f>'заказ-order'!E324</f>
         <v>0</v>
       </c>
-      <c r="K63" s="130">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="L63" s="130">
+      <c r="K64" s="130">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="130">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M63" s="83">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="82">
-        <v>62</v>
-      </c>
-      <c r="B64" s="87"/>
-      <c r="C64" s="80" t="s">
-        <v>77</v>
-      </c>
-      <c r="D64" s="79">
-        <v>0.35</v>
-      </c>
-      <c r="E64" s="79">
-        <v>0.21</v>
-      </c>
-      <c r="F64" s="86">
-        <v>0.153</v>
-      </c>
-      <c r="G64" s="89">
-        <f t="shared" si="41"/>
-        <v>1.12E-2</v>
-      </c>
-      <c r="H64" s="86">
-        <v>8.34</v>
-      </c>
-      <c r="I64" s="86">
-        <v>8.16</v>
-      </c>
-      <c r="J64" s="84">
-        <f>'заказ-order'!E333</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="130">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="L64" s="130">
-        <f t="shared" ref="L64:L65" si="53">I64*J64</f>
         <v>0</v>
       </c>
       <c r="M64" s="83">
@@ -15490,41 +15491,41 @@
     </row>
     <row r="65" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A65" s="82">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B65" s="87"/>
       <c r="C65" s="80" t="s">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="D65" s="79">
-        <v>0.34499999999999997</v>
+        <v>0.35</v>
       </c>
       <c r="E65" s="79">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="F65" s="86">
-        <v>0.14499999999999999</v>
+        <v>0.153</v>
       </c>
       <c r="G65" s="89">
-        <f>ROUND(D65*E65*F65,4)</f>
-        <v>0.01</v>
+        <f t="shared" si="45"/>
+        <v>1.12E-2</v>
       </c>
       <c r="H65" s="86">
-        <v>6.54</v>
+        <v>8.34</v>
       </c>
       <c r="I65" s="86">
-        <v>6.38</v>
+        <v>8.16</v>
       </c>
       <c r="J65" s="84">
-        <f>'заказ-order'!E342</f>
+        <f>'заказ-order'!E333</f>
         <v>0</v>
       </c>
       <c r="K65" s="130">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="L65" s="130">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="L65:L66" si="57">I65*J65</f>
         <v>0</v>
       </c>
       <c r="M65" s="83">
@@ -15532,127 +15533,127 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A66" s="82">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" s="87"/>
       <c r="C66" s="80" t="s">
-        <v>418</v>
+        <v>307</v>
       </c>
       <c r="D66" s="79">
-        <v>0.33400000000000002</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="E66" s="79">
-        <v>0.192</v>
+        <v>0.2</v>
       </c>
       <c r="F66" s="86">
-        <v>0.155</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="G66" s="89">
-        <f t="shared" si="41"/>
-        <v>9.9000000000000008E-3</v>
+        <f>ROUND(D66*E66*F66,4)</f>
+        <v>0.01</v>
       </c>
       <c r="H66" s="86">
-        <v>8.44</v>
+        <v>6.54</v>
       </c>
       <c r="I66" s="86">
-        <v>8.2799999999999994</v>
+        <v>6.38</v>
       </c>
       <c r="J66" s="84">
-        <f>'заказ-order'!E349</f>
+        <f>'заказ-order'!E342</f>
         <v>0</v>
       </c>
       <c r="K66" s="130">
-        <f t="shared" ref="K66" si="54">H66*J66</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="L66" s="130">
-        <f t="shared" ref="L66" si="55">I66*J66</f>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="M66" s="83">
-        <f t="shared" ref="M66" si="56">J66*D66*E66*F66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A67" s="82">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B67" s="87"/>
       <c r="C67" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="D67" s="79">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="E67" s="79">
+        <v>0.192</v>
+      </c>
+      <c r="F67" s="86">
+        <v>0.155</v>
+      </c>
+      <c r="G67" s="89">
+        <f t="shared" si="45"/>
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="H67" s="86">
+        <v>8.44</v>
+      </c>
+      <c r="I67" s="86">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="J67" s="84">
+        <f>'заказ-order'!E349</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="130">
+        <f t="shared" ref="K67" si="58">H67*J67</f>
+        <v>0</v>
+      </c>
+      <c r="L67" s="130">
+        <f t="shared" ref="L67" si="59">I67*J67</f>
+        <v>0</v>
+      </c>
+      <c r="M67" s="83">
+        <f t="shared" ref="M67" si="60">J67*D67*E67*F67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="82">
+        <v>65</v>
+      </c>
+      <c r="B68" s="87"/>
+      <c r="C68" s="80" t="s">
         <v>427</v>
       </c>
-      <c r="D67" s="79">
+      <c r="D68" s="79">
         <v>0.38200000000000001</v>
       </c>
-      <c r="E67" s="79">
+      <c r="E68" s="79">
         <v>0.25</v>
       </c>
-      <c r="F67" s="79">
+      <c r="F68" s="79">
         <v>0.17499999999999999</v>
       </c>
-      <c r="G67" s="89">
+      <c r="G68" s="89">
         <f t="shared" si="5"/>
         <v>1.67E-2</v>
       </c>
-      <c r="H67" s="86">
+      <c r="H68" s="86">
         <v>5.46</v>
       </c>
-      <c r="I67" s="86">
+      <c r="I68" s="86">
         <v>5.53</v>
       </c>
-      <c r="J67" s="84">
+      <c r="J68" s="84">
         <f>'заказ-order'!E353</f>
         <v>0</v>
       </c>
-      <c r="K67" s="130">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="L67" s="130">
-        <f>I67*J67</f>
-        <v>0</v>
-      </c>
-      <c r="M67" s="83">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="82">
-        <v>66</v>
-      </c>
-      <c r="B68" s="87"/>
-      <c r="C68" s="80" t="s">
-        <v>185</v>
-      </c>
-      <c r="D68" s="79">
-        <v>0.26</v>
-      </c>
-      <c r="E68" s="79">
-        <v>0.21</v>
-      </c>
-      <c r="F68" s="86">
-        <v>0.19</v>
-      </c>
-      <c r="G68" s="89">
-        <f t="shared" si="41"/>
-        <v>1.04E-2</v>
-      </c>
-      <c r="H68" s="86">
-        <v>5.6</v>
-      </c>
-      <c r="I68" s="86">
-        <v>5.38</v>
-      </c>
-      <c r="J68" s="84">
-        <f>'заказ-order'!E354</f>
-        <v>0</v>
-      </c>
       <c r="K68" s="130">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="L68" s="130">
@@ -15660,75 +15661,75 @@
         <v>0</v>
       </c>
       <c r="M68" s="83">
-        <f t="shared" ref="M68" si="57">J68*D68*E68*F68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A69" s="82">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69" s="87"/>
       <c r="C69" s="80" t="s">
+        <v>185</v>
+      </c>
+      <c r="D69" s="79">
+        <v>0.26</v>
+      </c>
+      <c r="E69" s="79">
+        <v>0.21</v>
+      </c>
+      <c r="F69" s="86">
+        <v>0.19</v>
+      </c>
+      <c r="G69" s="89">
+        <f t="shared" si="45"/>
+        <v>1.04E-2</v>
+      </c>
+      <c r="H69" s="86">
+        <v>5.6</v>
+      </c>
+      <c r="I69" s="86">
+        <v>5.38</v>
+      </c>
+      <c r="J69" s="84">
+        <f>'заказ-order'!E354</f>
+        <v>0</v>
+      </c>
+      <c r="K69" s="130">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="130">
+        <f>I69*J69</f>
+        <v>0</v>
+      </c>
+      <c r="M69" s="83">
+        <f t="shared" ref="M69" si="61">J69*D69*E69*F69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="82">
+        <v>67</v>
+      </c>
+      <c r="B70" s="87"/>
+      <c r="C70" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="D69" s="79">
+      <c r="D70" s="79">
         <v>0.27</v>
       </c>
-      <c r="E69" s="79">
+      <c r="E70" s="79">
         <v>0.19700000000000001</v>
       </c>
-      <c r="F69" s="86">
+      <c r="F70" s="86">
         <v>0.27</v>
       </c>
-      <c r="G69" s="89">
+      <c r="G70" s="89">
         <f t="shared" si="5"/>
         <v>1.44E-2</v>
       </c>
-      <c r="H69" s="85">
-        <v>6.64</v>
-      </c>
-      <c r="I69" s="85">
-        <v>6.44</v>
-      </c>
-      <c r="J69" s="84">
-        <f>'заказ-order'!E357</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="130">
-        <f t="shared" ref="K69:K74" si="58">H69*J69</f>
-        <v>0</v>
-      </c>
-      <c r="L69" s="130">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="83">
-        <f t="shared" ref="M69:M74" si="59">J69*D69*E69*F69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="82">
-        <v>68</v>
-      </c>
-      <c r="B70" s="87"/>
-      <c r="C70" s="80" t="s">
-        <v>63</v>
-      </c>
-      <c r="D70" s="79">
-        <v>0.27</v>
-      </c>
-      <c r="E70" s="79">
-        <v>0.19700000000000001</v>
-      </c>
-      <c r="F70" s="86">
-        <v>0.27</v>
-      </c>
-      <c r="G70" s="89">
-        <f t="shared" si="41"/>
-        <v>1.44E-2</v>
-      </c>
       <c r="H70" s="85">
         <v>6.64</v>
       </c>
@@ -15736,11 +15737,11 @@
         <v>6.44</v>
       </c>
       <c r="J70" s="84">
-        <f>'заказ-order'!E358</f>
+        <f>'заказ-order'!E357</f>
         <v>0</v>
       </c>
       <c r="K70" s="130">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="K70:K75" si="62">H70*J70</f>
         <v>0</v>
       </c>
       <c r="L70" s="130">
@@ -15748,75 +15749,75 @@
         <v>0</v>
       </c>
       <c r="M70" s="83">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="M70:M75" si="63">J70*D70*E70*F70</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A71" s="82">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B71" s="87"/>
       <c r="C71" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="D71" s="79">
+        <v>0.27</v>
+      </c>
+      <c r="E71" s="79">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="F71" s="86">
+        <v>0.27</v>
+      </c>
+      <c r="G71" s="89">
+        <f t="shared" si="45"/>
+        <v>1.44E-2</v>
+      </c>
+      <c r="H71" s="85">
+        <v>6.64</v>
+      </c>
+      <c r="I71" s="85">
+        <v>6.44</v>
+      </c>
+      <c r="J71" s="84">
+        <f>'заказ-order'!E358</f>
+        <v>0</v>
+      </c>
+      <c r="K71" s="130">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="130">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M71" s="83">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="82">
+        <v>69</v>
+      </c>
+      <c r="B72" s="87"/>
+      <c r="C72" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="79">
+      <c r="D72" s="79">
         <v>0.26500000000000001</v>
       </c>
-      <c r="E71" s="79">
+      <c r="E72" s="79">
         <v>0.2</v>
       </c>
-      <c r="F71" s="86">
+      <c r="F72" s="86">
         <v>0.22</v>
       </c>
-      <c r="G71" s="89">
+      <c r="G72" s="89">
         <f t="shared" si="5"/>
         <v>1.17E-2</v>
       </c>
-      <c r="H71" s="85">
-        <v>7.04</v>
-      </c>
-      <c r="I71" s="85">
-        <v>6.84</v>
-      </c>
-      <c r="J71" s="84">
-        <f>'заказ-order'!E359</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="130">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="L71" s="130">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M71" s="83">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="82">
-        <v>70</v>
-      </c>
-      <c r="B72" s="87"/>
-      <c r="C72" s="80" t="s">
-        <v>65</v>
-      </c>
-      <c r="D72" s="79">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="E72" s="79">
-        <v>0.2</v>
-      </c>
-      <c r="F72" s="86">
-        <v>0.22</v>
-      </c>
-      <c r="G72" s="89">
-        <f t="shared" si="41"/>
-        <v>1.17E-2</v>
-      </c>
       <c r="H72" s="85">
         <v>7.04</v>
       </c>
@@ -15824,11 +15825,11 @@
         <v>6.84</v>
       </c>
       <c r="J72" s="84">
-        <f>'заказ-order'!E360</f>
+        <f>'заказ-order'!E359</f>
         <v>0</v>
       </c>
       <c r="K72" s="130">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="L72" s="130">
@@ -15836,17 +15837,17 @@
         <v>0</v>
       </c>
       <c r="M72" s="83">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A73" s="82">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B73" s="87"/>
       <c r="C73" s="80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D73" s="79">
         <v>0.26500000000000001</v>
@@ -15858,7 +15859,7 @@
         <v>0.22</v>
       </c>
       <c r="G73" s="89">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>1.17E-2</v>
       </c>
       <c r="H73" s="85">
@@ -15872,25 +15873,25 @@
         <v>0</v>
       </c>
       <c r="K73" s="130">
-        <f t="shared" ref="K73" si="60">H73*J73</f>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="L73" s="130">
-        <f>I73*J73</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M73" s="83">
-        <f t="shared" ref="M73" si="61">J73*D73*E73*F73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A74" s="82">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B74" s="87"/>
       <c r="C74" s="80" t="s">
-        <v>336</v>
+        <v>66</v>
       </c>
       <c r="D74" s="79">
         <v>0.26500000000000001</v>
@@ -15902,21 +15903,21 @@
         <v>0.22</v>
       </c>
       <c r="G74" s="89">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>1.17E-2</v>
       </c>
       <c r="H74" s="85">
-        <v>6.58</v>
+        <v>7.04</v>
       </c>
       <c r="I74" s="85">
-        <v>6.42</v>
+        <v>6.84</v>
       </c>
       <c r="J74" s="84">
-        <f>'заказ-order'!E361</f>
+        <f>'заказ-order'!E360</f>
         <v>0</v>
       </c>
       <c r="K74" s="130">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="K74" si="64">H74*J74</f>
         <v>0</v>
       </c>
       <c r="L74" s="130">
@@ -15924,45 +15925,82 @@
         <v>0</v>
       </c>
       <c r="M74" s="83">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A75" s="82"/>
-      <c r="B75" s="81"/>
-      <c r="C75" s="80"/>
-      <c r="D75" s="79"/>
-      <c r="E75" s="79"/>
-      <c r="F75" s="79"/>
-      <c r="G75" s="78" t="s">
+        <f t="shared" ref="M74" si="65">J74*D74*E74*F74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A75" s="82">
+        <v>72</v>
+      </c>
+      <c r="B75" s="87"/>
+      <c r="C75" s="80" t="s">
+        <v>336</v>
+      </c>
+      <c r="D75" s="79">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="E75" s="79">
+        <v>0.2</v>
+      </c>
+      <c r="F75" s="86">
+        <v>0.22</v>
+      </c>
+      <c r="G75" s="89">
+        <f t="shared" si="45"/>
+        <v>1.17E-2</v>
+      </c>
+      <c r="H75" s="85">
+        <v>6.58</v>
+      </c>
+      <c r="I75" s="85">
+        <v>6.42</v>
+      </c>
+      <c r="J75" s="84">
+        <f>'заказ-order'!E361</f>
+        <v>0</v>
+      </c>
+      <c r="K75" s="130">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="L75" s="130">
+        <f>I75*J75</f>
+        <v>0</v>
+      </c>
+      <c r="M75" s="83">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="82"/>
+      <c r="B76" s="81"/>
+      <c r="C76" s="80"/>
+      <c r="D76" s="79"/>
+      <c r="E76" s="79"/>
+      <c r="F76" s="79"/>
+      <c r="G76" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="H75" s="77"/>
-      <c r="I75" s="77"/>
-      <c r="J75" s="76">
-        <f>SUM(J3:J74)</f>
-        <v>0</v>
-      </c>
-      <c r="K75" s="131">
-        <f>SUM(K3:K74)</f>
-        <v>0</v>
-      </c>
-      <c r="L75" s="131">
-        <f>SUM(L3:L74)</f>
-        <v>0</v>
-      </c>
-      <c r="M75" s="76">
-        <f>SUM(M3:M74)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F76" s="74"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="71"/>
-      <c r="I76" s="71"/>
-      <c r="M76" s="70"/>
+      <c r="H76" s="77"/>
+      <c r="I76" s="77"/>
+      <c r="J76" s="76">
+        <f>SUM(J3:J75)</f>
+        <v>0</v>
+      </c>
+      <c r="K76" s="131">
+        <f>SUM(K3:K75)</f>
+        <v>0</v>
+      </c>
+      <c r="L76" s="131">
+        <f>SUM(L3:L75)</f>
+        <v>0</v>
+      </c>
+      <c r="M76" s="76">
+        <f>SUM(M3:M75)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F77" s="74"/>
@@ -15971,22 +16009,29 @@
       <c r="I77" s="71"/>
       <c r="M77" s="70"/>
     </row>
-    <row r="78" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="F78" s="70"/>
-      <c r="G78" s="70"/>
-      <c r="H78" s="70"/>
-      <c r="I78" s="70"/>
-      <c r="J78" s="70"/>
-      <c r="K78" s="70"/>
-      <c r="L78" s="70"/>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F78" s="74"/>
+      <c r="G78" s="73"/>
+      <c r="H78" s="71"/>
+      <c r="I78" s="71"/>
       <c r="M78" s="70"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F79" s="74"/>
-      <c r="G79" s="73"/>
-      <c r="H79" s="71"/>
-      <c r="I79" s="71"/>
+    <row r="79" spans="1:13" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="70"/>
+      <c r="K79" s="70"/>
+      <c r="L79" s="70"/>
       <c r="M79" s="70"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F80" s="74"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="71"/>
+      <c r="M80" s="70"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9467FF5E-36E7-4A4C-B11C-0842AFFEB0B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A1BDE0-A2E5-440D-820A-E8946BD96B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12596,7 +12596,7 @@
       <c r="D369" s="12"/>
       <c r="E369" s="12"/>
       <c r="F369" s="4">
-        <f>D356+D352+D349+D333+D324+D315+D313+D294+D289+D285+D273+D268+D263+D226+D218+D212+D201+D179+D171+D162+D158+D121+D119+D109+D103+D96+D89+D84+D79+D47+D5+D342+D249+D242+D237+D230+D156+D125++D113+D220+D363+D165+D301+D129+D191+D185+D151+D145+D139+D134</f>
+        <f>D356+D352+D349+D333+D324+D315+D313+D294+D289+D285+D273+D268+D263+D226+D218+D212+D201+D179+D171+D162+D158+D121+D119+D109+D103+D96+D89+D84+D79+D47+D5+D342+D249+D242+D237+D230+D156+D125++D113+D220+D363+D165+D301+D129+D191+D185+D151+D145+D139+D134+D196</f>
         <v>0</v>
       </c>
       <c r="G369" s="142"/>
